--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDDB505-450D-4465-8D26-47D019EB7937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA120171-3527-4967-B8CF-816FA4FBB381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calc_rules" sheetId="1" r:id="rId1"/>
     <sheet name="ui_structure" sheetId="2" r:id="rId2"/>
+    <sheet name="frl_reference" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="393">
   <si>
     <t>system</t>
   </si>
@@ -1177,6 +1178,42 @@
   </si>
   <si>
     <t>Intumescent coating</t>
+  </si>
+  <si>
+    <t>Product Type</t>
+  </si>
+  <si>
+    <t>FRL (min)</t>
+  </si>
+  <si>
+    <t>Thickness (mm)</t>
+  </si>
+  <si>
+    <t>Layers</t>
+  </si>
+  <si>
+    <t>Density (kg/m3)</t>
+  </si>
+  <si>
+    <t>Concrete</t>
+  </si>
+  <si>
+    <t>Masonry</t>
+  </si>
+  <si>
+    <t>Speed Panel</t>
+  </si>
+  <si>
+    <t>Fire Resistant Plasterboard</t>
+  </si>
+  <si>
+    <t>16mm</t>
+  </si>
+  <si>
+    <t>13mm</t>
+  </si>
+  <si>
+    <t>Requires FRL</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1279,7 +1316,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4114,13 +4150,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Q76"/>
+  <dimension ref="A1:R76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>175</v>
       </c>
@@ -4172,8 +4208,11 @@
       <c r="Q1" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="9">
         <v>1</v>
       </c>
@@ -4202,7 +4241,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -4228,7 +4267,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>1</v>
       </c>
@@ -4254,7 +4293,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4274,7 +4313,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4294,14 +4333,14 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="D7" t="s">
         <v>206</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" t="s">
         <v>367</v>
       </c>
       <c r="F7" t="s">
@@ -4311,7 +4350,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4328,7 +4367,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>2</v>
       </c>
@@ -4351,7 +4390,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>2</v>
       </c>
@@ -4374,7 +4413,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>2</v>
       </c>
@@ -4394,7 +4433,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>2</v>
       </c>
@@ -4417,7 +4456,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>2</v>
       </c>
@@ -4437,7 +4476,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>2</v>
       </c>
@@ -4460,7 +4499,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>2</v>
       </c>
@@ -4483,7 +4522,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>2</v>
       </c>
@@ -4503,7 +4542,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>2</v>
       </c>
@@ -4523,7 +4562,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>2</v>
       </c>
@@ -4543,7 +4582,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>2</v>
       </c>
@@ -4566,7 +4605,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>2</v>
       </c>
@@ -4586,7 +4625,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>2</v>
       </c>
@@ -4609,7 +4648,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>2</v>
       </c>
@@ -4632,7 +4671,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" s="9">
         <v>4</v>
       </c>
@@ -4655,7 +4694,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>4</v>
       </c>
@@ -4675,7 +4714,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>4</v>
       </c>
@@ -4698,7 +4737,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>4</v>
       </c>
@@ -4721,7 +4760,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>4</v>
       </c>
@@ -4748,7 +4787,7 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>5</v>
       </c>
@@ -4773,8 +4812,11 @@
       <c r="P28" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="R28" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>5</v>
       </c>
@@ -4796,8 +4838,11 @@
       <c r="P29" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="R29" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>5</v>
       </c>
@@ -4819,8 +4864,11 @@
       <c r="P30" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="R30" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>5</v>
       </c>
@@ -4842,8 +4890,11 @@
       <c r="P31" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="R31" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>5</v>
       </c>
@@ -5039,13 +5090,13 @@
       <c r="C41" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" t="s">
         <v>380</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>380</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" t="s">
         <v>195</v>
       </c>
       <c r="I41" t="s">
@@ -5717,4 +5768,300 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9B6005-6F43-4EB4-8661-C70A2093261E}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" t="s">
+        <v>381</v>
+      </c>
+      <c r="C1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D1" t="s">
+        <v>383</v>
+      </c>
+      <c r="E1" t="s">
+        <v>384</v>
+      </c>
+      <c r="F1" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C2">
+        <v>30</v>
+      </c>
+      <c r="D2">
+        <v>60</v>
+      </c>
+      <c r="F2">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>80</v>
+      </c>
+      <c r="F3">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+      <c r="D4">
+        <v>100</v>
+      </c>
+      <c r="F4">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>386</v>
+      </c>
+      <c r="C5">
+        <v>120</v>
+      </c>
+      <c r="D5">
+        <v>120</v>
+      </c>
+      <c r="F5">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C6">
+        <v>180</v>
+      </c>
+      <c r="D6">
+        <v>150</v>
+      </c>
+      <c r="F6">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C7">
+        <v>240</v>
+      </c>
+      <c r="D7">
+        <v>175</v>
+      </c>
+      <c r="F7">
+        <v>2400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C8">
+        <v>30</v>
+      </c>
+      <c r="D8">
+        <v>60</v>
+      </c>
+      <c r="F8">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>387</v>
+      </c>
+      <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>90</v>
+      </c>
+      <c r="F9">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10">
+        <v>90</v>
+      </c>
+      <c r="D10">
+        <v>110</v>
+      </c>
+      <c r="F10">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>387</v>
+      </c>
+      <c r="C11">
+        <v>120</v>
+      </c>
+      <c r="D11">
+        <v>130</v>
+      </c>
+      <c r="F11">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12">
+        <v>180</v>
+      </c>
+      <c r="D12">
+        <v>160</v>
+      </c>
+      <c r="F12">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13">
+        <v>240</v>
+      </c>
+      <c r="D13">
+        <v>180</v>
+      </c>
+      <c r="F13">
+        <v>1900</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14">
+        <v>60</v>
+      </c>
+      <c r="D14">
+        <v>51</v>
+      </c>
+      <c r="F14">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C15">
+        <v>90</v>
+      </c>
+      <c r="D15">
+        <v>64</v>
+      </c>
+      <c r="F15">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>388</v>
+      </c>
+      <c r="C16">
+        <v>120</v>
+      </c>
+      <c r="D16">
+        <v>78</v>
+      </c>
+      <c r="F16">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>389</v>
+      </c>
+      <c r="B17" t="s">
+        <v>390</v>
+      </c>
+      <c r="C17">
+        <v>60</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>389</v>
+      </c>
+      <c r="B18" t="s">
+        <v>390</v>
+      </c>
+      <c r="C18">
+        <v>120</v>
+      </c>
+      <c r="E18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>389</v>
+      </c>
+      <c r="B19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C19">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>389</v>
+      </c>
+      <c r="B20" t="s">
+        <v>391</v>
+      </c>
+      <c r="C20">
+        <v>90</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA120171-3527-4967-B8CF-816FA4FBB381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BABC4F-4E5B-42D8-A082-9B6033764322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1153" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="392">
   <si>
     <t>system</t>
   </si>
@@ -968,9 +968,6 @@
   </si>
   <si>
     <t>Smoke Exhaust Fans</t>
-  </si>
-  <si>
-    <t>fans</t>
   </si>
   <si>
     <t>Fire Resistant Ductwork</t>
@@ -1241,7 +1238,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1290,6 +1287,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF66FF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1303,7 +1306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -1316,12 +1319,19 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF66FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -4209,7 +4219,7 @@
         <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
@@ -4303,14 +4313,14 @@
       <c r="D5" t="s">
         <v>202</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>202</v>
       </c>
       <c r="F5" t="s">
         <v>195</v>
       </c>
-      <c r="I5" t="s">
-        <v>203</v>
+      <c r="I5" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -4341,7 +4351,7 @@
         <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F7" t="s">
         <v>195</v>
@@ -4573,7 +4583,7 @@
         <v>230</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F18" t="s">
         <v>195</v>
@@ -4616,7 +4626,7 @@
         <v>232</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F20" t="s">
         <v>195</v>
@@ -4685,7 +4695,7 @@
         <v>238</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F23" t="s">
         <v>195</v>
@@ -4768,13 +4778,13 @@
         <v>236</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>351</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>195</v>
@@ -4801,12 +4811,12 @@
         <v>248</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F28" t="s">
         <v>195</v>
       </c>
-      <c r="I28" t="s">
+      <c r="I28" s="12" t="s">
         <v>74</v>
       </c>
       <c r="P28" t="s">
@@ -4827,13 +4837,13 @@
         <v>250</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F29" t="s">
         <v>195</v>
       </c>
-      <c r="I29" t="s">
-        <v>74</v>
+      <c r="I29" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="P29" t="s">
         <v>249</v>
@@ -4853,13 +4863,13 @@
         <v>251</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F30" t="s">
         <v>195</v>
       </c>
-      <c r="I30" t="s">
-        <v>74</v>
+      <c r="I30" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="P30" t="s">
         <v>249</v>
@@ -4879,13 +4889,13 @@
         <v>252</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F31" t="s">
         <v>195</v>
       </c>
-      <c r="I31" t="s">
-        <v>74</v>
+      <c r="I31" s="12" t="s">
+        <v>255</v>
       </c>
       <c r="P31" t="s">
         <v>249</v>
@@ -4899,7 +4909,7 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D32" t="s">
         <v>253</v>
@@ -4910,7 +4920,7 @@
       <c r="F32" t="s">
         <v>195</v>
       </c>
-      <c r="I32" t="s">
+      <c r="I32" s="12" t="s">
         <v>255</v>
       </c>
     </row>
@@ -4919,7 +4929,7 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D33" t="s">
         <v>256</v>
@@ -4931,7 +4941,7 @@
         <v>195</v>
       </c>
       <c r="I33" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
@@ -4939,7 +4949,7 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D34" t="s">
         <v>259</v>
@@ -4959,7 +4969,7 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D35" t="s">
         <v>261</v>
@@ -4979,7 +4989,7 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D36" t="s">
         <v>263</v>
@@ -4991,7 +5001,7 @@
         <v>195</v>
       </c>
       <c r="I36" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
@@ -4999,7 +5009,7 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D37" t="s">
         <v>265</v>
@@ -5031,7 +5041,7 @@
         <v>195</v>
       </c>
       <c r="I38" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
       <c r="P38" t="s">
         <v>269</v>
@@ -5088,19 +5098,19 @@
         <v>5</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="D41" t="s">
         <v>379</v>
       </c>
-      <c r="D41" t="s">
-        <v>380</v>
-      </c>
       <c r="E41" s="5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F41" t="s">
         <v>195</v>
       </c>
-      <c r="I41" t="s">
-        <v>255</v>
+      <c r="I41" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
@@ -5170,8 +5180,8 @@
       <c r="F45" t="s">
         <v>195</v>
       </c>
-      <c r="I45" t="s">
-        <v>6</v>
+      <c r="I45" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -5190,7 +5200,7 @@
       <c r="F46" t="s">
         <v>195</v>
       </c>
-      <c r="I46" t="s">
+      <c r="I46" s="12" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5239,6 +5249,9 @@
       <c r="G48" t="s">
         <v>291</v>
       </c>
+      <c r="I48" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="J48" t="s">
         <v>287</v>
       </c>
@@ -5385,36 +5398,42 @@
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>6</v>
+      </c>
       <c r="C55" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F55" t="s">
         <v>195</v>
       </c>
-      <c r="I55" t="s">
+      <c r="I55" s="12" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>6</v>
+      </c>
       <c r="C56" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F56" t="s">
         <v>195</v>
       </c>
-      <c r="I56" t="s">
+      <c r="I56" s="12" t="s">
         <v>255</v>
       </c>
     </row>
@@ -5429,13 +5448,13 @@
         <v>310</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F57" t="s">
         <v>195</v>
       </c>
-      <c r="I57" t="s">
-        <v>311</v>
+      <c r="I57" s="12" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -5443,19 +5462,19 @@
         <v>7</v>
       </c>
       <c r="D58" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E58" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F58" t="s">
         <v>195</v>
       </c>
-      <c r="I58" t="s">
-        <v>109</v>
+      <c r="I58" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="P58" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
@@ -5463,19 +5482,19 @@
         <v>7</v>
       </c>
       <c r="D59" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F59" t="s">
         <v>195</v>
       </c>
-      <c r="I59" t="s">
-        <v>109</v>
+      <c r="I59" s="12" t="s">
+        <v>74</v>
       </c>
       <c r="P59" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
@@ -5483,19 +5502,19 @@
         <v>8</v>
       </c>
       <c r="B60" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="D60" t="s">
         <v>315</v>
       </c>
-      <c r="D60" t="s">
-        <v>316</v>
-      </c>
       <c r="E60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F60" t="s">
         <v>195</v>
       </c>
       <c r="I60" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -5503,19 +5522,19 @@
         <v>9</v>
       </c>
       <c r="B61" t="s">
+        <v>317</v>
+      </c>
+      <c r="D61" t="s">
         <v>318</v>
       </c>
-      <c r="D61" t="s">
-        <v>319</v>
-      </c>
       <c r="E61" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F61" t="s">
         <v>195</v>
       </c>
       <c r="I61" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
@@ -5523,10 +5542,10 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E62" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F62" t="s">
         <v>195</v>
@@ -5537,13 +5556,13 @@
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E63" t="s">
+        <v>372</v>
+      </c>
+      <c r="F63" t="s">
         <v>373</v>
-      </c>
-      <c r="F63" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
@@ -5551,16 +5570,16 @@
         <v>9</v>
       </c>
       <c r="D64" t="s">
+        <v>320</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="F64" t="s">
         <v>195</v>
       </c>
       <c r="I64" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
@@ -5568,16 +5587,16 @@
         <v>9</v>
       </c>
       <c r="D65" t="s">
+        <v>323</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" t="s">
         <v>325</v>
       </c>
-      <c r="F65" t="s">
+      <c r="O65" t="s">
         <v>326</v>
-      </c>
-      <c r="O65" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
@@ -5585,13 +5604,13 @@
         <v>3</v>
       </c>
       <c r="B66" t="s">
+        <v>327</v>
+      </c>
+      <c r="D66" t="s">
         <v>328</v>
       </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>329</v>
-      </c>
-      <c r="E66" t="s">
-        <v>330</v>
       </c>
       <c r="F66" t="s">
         <v>195</v>
@@ -5605,19 +5624,19 @@
         <v>3</v>
       </c>
       <c r="D67" t="s">
+        <v>330</v>
+      </c>
+      <c r="E67" t="s">
         <v>331</v>
-      </c>
-      <c r="E67" t="s">
-        <v>332</v>
       </c>
       <c r="F67" t="s">
         <v>195</v>
       </c>
       <c r="G67" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I67" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
@@ -5625,19 +5644,19 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
+        <v>333</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="F68" t="s">
         <v>195</v>
       </c>
       <c r="G68" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I68" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
@@ -5645,13 +5664,13 @@
         <v>10</v>
       </c>
       <c r="B69" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D69" t="s">
         <v>336</v>
       </c>
-      <c r="D69" t="s">
+      <c r="F69" t="s">
         <v>337</v>
-      </c>
-      <c r="F69" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
@@ -5659,10 +5678,10 @@
         <v>10</v>
       </c>
       <c r="D70" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F70" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
@@ -5670,10 +5689,10 @@
         <v>10</v>
       </c>
       <c r="D71" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F71" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -5681,10 +5700,10 @@
         <v>10</v>
       </c>
       <c r="D72" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F72" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
@@ -5692,10 +5711,10 @@
         <v>10</v>
       </c>
       <c r="D73" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F73" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.35">
@@ -5703,22 +5722,22 @@
         <v>5</v>
       </c>
       <c r="C74" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D74" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F74" t="s">
         <v>195</v>
       </c>
       <c r="I74" t="s">
-        <v>255</v>
+        <v>203</v>
       </c>
       <c r="P74" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.35">
@@ -5726,42 +5745,42 @@
         <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D75" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F75" t="s">
         <v>195</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I75" s="12" t="s">
         <v>255</v>
       </c>
       <c r="P75" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A76" s="6">
+      <c r="A76" s="13">
         <v>5</v>
       </c>
-      <c r="B76" s="6"/>
-      <c r="C76" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="D76" s="6" t="s">
+      <c r="B76" s="13"/>
+      <c r="C76" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="E76" s="13" t="s">
         <v>346</v>
       </c>
-      <c r="E76" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="F76" s="6" t="s">
+      <c r="F76" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I76" s="13" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5780,24 +5799,24 @@
         <v>179</v>
       </c>
       <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
         <v>381</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>382</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>383</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>384</v>
-      </c>
-      <c r="F1" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5811,7 +5830,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5825,7 +5844,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5839,7 +5858,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5853,7 +5872,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5867,7 +5886,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5881,7 +5900,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5895,7 +5914,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5909,7 +5928,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5923,7 +5942,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5937,7 +5956,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5951,7 +5970,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5965,7 +5984,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5979,7 +5998,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -5993,7 +6012,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -6007,10 +6026,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B17" t="s">
         <v>389</v>
-      </c>
-      <c r="B17" t="s">
-        <v>390</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -6021,10 +6040,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>388</v>
+      </c>
+      <c r="B18" t="s">
         <v>389</v>
-      </c>
-      <c r="B18" t="s">
-        <v>390</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -6035,10 +6054,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B19" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -6049,10 +6068,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B20" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C20">
         <v>90</v>

--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BABC4F-4E5B-42D8-A082-9B6033764322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53A83EC-F070-4258-9E69-E55BD2213754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="382">
   <si>
     <t>system</t>
   </si>
@@ -763,18 +763,6 @@
     <t>Pipework</t>
   </si>
   <si>
-    <t>Hose Reel Cabinets</t>
-  </si>
-  <si>
-    <t>Cabinet</t>
-  </si>
-  <si>
-    <t>Hose Reel Valves</t>
-  </si>
-  <si>
-    <t>Valve</t>
-  </si>
-  <si>
     <t>Means of Restricting Fire Spread / Structural Protection</t>
   </si>
   <si>
@@ -925,15 +913,6 @@
     <t>Sprinkler Valve</t>
   </si>
   <si>
-    <t>Sprinkler Pumps</t>
-  </si>
-  <si>
-    <t>Sprinkler Pump</t>
-  </si>
-  <si>
-    <t>pumps</t>
-  </si>
-  <si>
     <t>Hydrants</t>
   </si>
   <si>
@@ -958,12 +937,6 @@
     <t>Typically 1 booster assembly per hydrant system - confirm against site layout and AS2419.1.</t>
   </si>
   <si>
-    <t>Hydrant Pumps</t>
-  </si>
-  <si>
-    <t>Hydrant Pump</t>
-  </si>
-  <si>
     <t>Means of Smoke Hazard Management</t>
   </si>
   <si>
@@ -989,9 +962,6 @@
   </si>
   <si>
     <t>Fire Safety Management</t>
-  </si>
-  <si>
-    <t>Fire Safety Signage</t>
   </si>
   <si>
     <t>signs</t>
@@ -1217,16 +1187,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1238,7 +1202,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1254,12 +1218,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1306,21 +1264,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4160,7 +4115,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R76"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="17" width="20" customWidth="1"/>
@@ -4219,11 +4174,11 @@
         <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="9">
+      <c r="A2" s="7">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -4319,8 +4274,8 @@
       <c r="F5" t="s">
         <v>195</v>
       </c>
-      <c r="I5" s="12" t="s">
-        <v>255</v>
+      <c r="I5" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
@@ -4351,7 +4306,7 @@
         <v>206</v>
       </c>
       <c r="E7" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="F7" t="s">
         <v>195</v>
@@ -4378,7 +4333,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="9">
+      <c r="A9" s="7">
         <v>2</v>
       </c>
       <c r="B9" t="s">
@@ -4582,8 +4537,8 @@
       <c r="D18" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="9" t="s">
-        <v>364</v>
+      <c r="E18" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="F18" t="s">
         <v>195</v>
@@ -4625,8 +4580,8 @@
       <c r="D20" t="s">
         <v>232</v>
       </c>
-      <c r="E20" s="9" t="s">
-        <v>365</v>
+      <c r="E20" s="7" t="s">
+        <v>355</v>
       </c>
       <c r="F20" t="s">
         <v>195</v>
@@ -4682,7 +4637,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="9">
+      <c r="A23" s="7">
         <v>4</v>
       </c>
       <c r="B23" t="s">
@@ -4695,7 +4650,7 @@
         <v>238</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="F23" t="s">
         <v>195</v>
@@ -4725,105 +4680,111 @@
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25">
+      <c r="A25" s="3">
         <v>4</v>
       </c>
-      <c r="C25" t="s">
-        <v>237</v>
-      </c>
-      <c r="D25" t="s">
-        <v>242</v>
+      <c r="B25" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>339</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F25" t="s">
-        <v>216</v>
-      </c>
-      <c r="J25" t="s">
-        <v>238</v>
-      </c>
-      <c r="K25" t="s">
-        <v>226</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>242</v>
       </c>
       <c r="C26" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="D26" t="s">
         <v>244</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="E26" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="F26" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P26" t="s">
         <v>245</v>
       </c>
-      <c r="F26" t="s">
-        <v>216</v>
-      </c>
-      <c r="J26" t="s">
-        <v>238</v>
-      </c>
-      <c r="K26" t="s">
-        <v>226</v>
+      <c r="R26" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A27" s="4">
-        <v>4</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="A27">
+        <v>5</v>
+      </c>
+      <c r="C27" t="s">
+        <v>243</v>
+      </c>
+      <c r="D27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="F27" t="s">
         <v>195</v>
       </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="I27" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="P27" t="s">
+        <v>245</v>
+      </c>
+      <c r="R27" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>5</v>
       </c>
-      <c r="B28" t="s">
-        <v>246</v>
-      </c>
       <c r="C28" t="s">
+        <v>243</v>
+      </c>
+      <c r="D28" t="s">
         <v>247</v>
       </c>
-      <c r="D28" t="s">
-        <v>248</v>
-      </c>
       <c r="E28" s="1" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="F28" t="s">
         <v>195</v>
       </c>
-      <c r="I28" s="12" t="s">
-        <v>74</v>
+      <c r="I28" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R28" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
@@ -4831,25 +4792,25 @@
         <v>5</v>
       </c>
       <c r="C29" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="D29" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="F29" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="12" t="s">
-        <v>255</v>
+      <c r="I29" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="P29" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="R29" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
@@ -4857,25 +4818,19 @@
         <v>5</v>
       </c>
       <c r="C30" t="s">
-        <v>247</v>
+        <v>345</v>
       </c>
       <c r="D30" t="s">
-        <v>251</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>353</v>
+        <v>249</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>250</v>
       </c>
       <c r="F30" t="s">
         <v>195</v>
       </c>
-      <c r="I30" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="P30" t="s">
-        <v>249</v>
-      </c>
-      <c r="R30" t="s">
-        <v>289</v>
+      <c r="I30" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
@@ -4883,25 +4838,19 @@
         <v>5</v>
       </c>
       <c r="C31" t="s">
-        <v>247</v>
+        <v>346</v>
       </c>
       <c r="D31" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>354</v>
+      <c r="E31" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="F31" t="s">
         <v>195</v>
       </c>
-      <c r="I31" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="P31" t="s">
-        <v>249</v>
-      </c>
-      <c r="R31" t="s">
-        <v>289</v>
+      <c r="I31" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
@@ -4909,19 +4858,19 @@
         <v>5</v>
       </c>
       <c r="C32" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D32" t="s">
-        <v>253</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>254</v>
+        <v>255</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>256</v>
       </c>
       <c r="F32" t="s">
         <v>195</v>
       </c>
-      <c r="I32" s="12" t="s">
-        <v>255</v>
+      <c r="I32" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
@@ -4929,19 +4878,19 @@
         <v>5</v>
       </c>
       <c r="C33" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D33" t="s">
-        <v>256</v>
-      </c>
-      <c r="E33" s="5" t="s">
         <v>257</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="F33" t="s">
         <v>195</v>
       </c>
       <c r="I33" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
@@ -4949,19 +4898,19 @@
         <v>5</v>
       </c>
       <c r="C34" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D34" t="s">
         <v>259</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" s="4" t="s">
         <v>260</v>
       </c>
       <c r="F34" t="s">
         <v>195</v>
       </c>
       <c r="I34" t="s">
-        <v>258</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
@@ -4969,19 +4918,19 @@
         <v>5</v>
       </c>
       <c r="C35" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="D35" t="s">
         <v>261</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F35" t="s">
         <v>195</v>
       </c>
       <c r="I35" t="s">
-        <v>258</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
@@ -4989,12 +4938,12 @@
         <v>5</v>
       </c>
       <c r="C36" t="s">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="D36" t="s">
         <v>263</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="4" t="s">
         <v>264</v>
       </c>
       <c r="F36" t="s">
@@ -5002,6 +4951,9 @@
       </c>
       <c r="I36" t="s">
         <v>203</v>
+      </c>
+      <c r="P36" t="s">
+        <v>265</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
@@ -5009,19 +4961,22 @@
         <v>5</v>
       </c>
       <c r="C37" t="s">
-        <v>358</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F37" t="s">
         <v>195</v>
       </c>
       <c r="I37" t="s">
-        <v>74</v>
+        <v>268</v>
+      </c>
+      <c r="P37" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
@@ -5029,88 +4984,76 @@
         <v>5</v>
       </c>
       <c r="C38" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>267</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>268</v>
+        <v>270</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="F38" t="s">
         <v>195</v>
       </c>
       <c r="I38" t="s">
-        <v>203</v>
+        <v>109</v>
       </c>
       <c r="P38" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>5</v>
       </c>
-      <c r="C39" t="s">
-        <v>266</v>
+      <c r="C39" s="8" t="s">
+        <v>368</v>
       </c>
       <c r="D39" t="s">
-        <v>270</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>271</v>
+        <v>369</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>369</v>
       </c>
       <c r="F39" t="s">
         <v>195</v>
       </c>
-      <c r="I39" t="s">
-        <v>272</v>
-      </c>
-      <c r="P39" t="s">
-        <v>273</v>
+      <c r="I39" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>5</v>
       </c>
-      <c r="C40" t="s">
-        <v>266</v>
-      </c>
       <c r="D40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F40" t="s">
         <v>195</v>
       </c>
       <c r="I40" t="s">
-        <v>109</v>
-      </c>
-      <c r="P40" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>5</v>
       </c>
-      <c r="C41" s="10" t="s">
-        <v>378</v>
-      </c>
       <c r="D41" t="s">
-        <v>379</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>379</v>
+        <v>275</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="F41" t="s">
         <v>195</v>
       </c>
-      <c r="I41" s="12" t="s">
-        <v>74</v>
+      <c r="I41" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
@@ -5118,154 +5061,166 @@
         <v>5</v>
       </c>
       <c r="D42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F42" t="s">
         <v>195</v>
       </c>
       <c r="I42" t="s">
-        <v>278</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>5</v>
       </c>
+      <c r="C43" t="s">
+        <v>278</v>
+      </c>
       <c r="D43" t="s">
-        <v>279</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>278</v>
       </c>
       <c r="F43" t="s">
         <v>195</v>
       </c>
-      <c r="I43" t="s">
-        <v>278</v>
+      <c r="I43" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>5</v>
       </c>
+      <c r="C44" t="s">
+        <v>280</v>
+      </c>
       <c r="D44" t="s">
-        <v>280</v>
-      </c>
-      <c r="E44" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>280</v>
       </c>
       <c r="F44" t="s">
         <v>195</v>
       </c>
-      <c r="I44" t="s">
+      <c r="I44" s="10" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A45">
-        <v>5</v>
+      <c r="A45" s="7">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>281</v>
       </c>
       <c r="C45" t="s">
         <v>282</v>
       </c>
       <c r="D45" t="s">
-        <v>281</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
+      </c>
+      <c r="E45" t="s">
+        <v>284</v>
       </c>
       <c r="F45" t="s">
         <v>195</v>
       </c>
-      <c r="I45" s="12" t="s">
-        <v>74</v>
+      <c r="G45" t="s">
+        <v>213</v>
+      </c>
+      <c r="H45" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D46" t="s">
-        <v>283</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>284</v>
+        <v>286</v>
+      </c>
+      <c r="E46" t="s">
+        <v>286</v>
       </c>
       <c r="F46" t="s">
         <v>195</v>
       </c>
-      <c r="I46" s="12" t="s">
-        <v>74</v>
+      <c r="G46" t="s">
+        <v>287</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="J46" t="s">
+        <v>283</v>
+      </c>
+      <c r="L46" t="s">
+        <v>8</v>
+      </c>
+      <c r="M46" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" t="s">
+        <v>288</v>
+      </c>
+      <c r="P46" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A47" s="9">
+      <c r="A47">
         <v>6</v>
       </c>
-      <c r="B47" t="s">
-        <v>285</v>
-      </c>
       <c r="C47" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D47" t="s">
-        <v>287</v>
-      </c>
-      <c r="E47" t="s">
-        <v>288</v>
+        <v>290</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="F47" t="s">
-        <v>195</v>
-      </c>
-      <c r="G47" t="s">
-        <v>213</v>
-      </c>
-      <c r="H47" t="s">
-        <v>289</v>
+        <v>216</v>
+      </c>
+      <c r="J47" t="s">
+        <v>283</v>
+      </c>
+      <c r="K47" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>6</v>
       </c>
-      <c r="C48" t="s">
-        <v>286</v>
-      </c>
-      <c r="D48" t="s">
-        <v>290</v>
-      </c>
-      <c r="E48" t="s">
-        <v>290</v>
+      <c r="C48" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>292</v>
       </c>
       <c r="F48" t="s">
         <v>195</v>
       </c>
-      <c r="G48" t="s">
-        <v>291</v>
-      </c>
-      <c r="I48" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="J48" t="s">
-        <v>287</v>
-      </c>
-      <c r="L48" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" t="s">
-        <v>22</v>
-      </c>
-      <c r="N48" t="s">
-        <v>292</v>
+      <c r="I48" t="s">
+        <v>293</v>
       </c>
       <c r="P48" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
@@ -5273,22 +5228,19 @@
         <v>6</v>
       </c>
       <c r="C49" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D49" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>295</v>
       </c>
       <c r="F49" t="s">
-        <v>216</v>
-      </c>
-      <c r="J49" t="s">
-        <v>287</v>
-      </c>
-      <c r="K49" t="s">
-        <v>226</v>
+        <v>195</v>
+      </c>
+      <c r="I49" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
@@ -5296,12 +5248,12 @@
         <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="D50" t="s">
         <v>296</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="2" t="s">
         <v>297</v>
       </c>
       <c r="F50" t="s">
@@ -5309,217 +5261,199 @@
       </c>
       <c r="I50" t="s">
         <v>298</v>
+      </c>
+      <c r="P50" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>6</v>
       </c>
-      <c r="C51" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>299</v>
+      <c r="C51" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>358</v>
       </c>
       <c r="F51" t="s">
         <v>195</v>
       </c>
-      <c r="I51" t="s">
-        <v>300</v>
-      </c>
-      <c r="P51" t="s">
-        <v>301</v>
+      <c r="I51" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>6</v>
       </c>
-      <c r="C52" t="s">
-        <v>299</v>
-      </c>
-      <c r="D52" t="s">
-        <v>302</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>302</v>
+      <c r="C52" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>357</v>
       </c>
       <c r="F52" t="s">
         <v>195</v>
       </c>
-      <c r="I52" t="s">
-        <v>109</v>
+      <c r="I52" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53">
-        <v>6</v>
-      </c>
-      <c r="C53" t="s">
-        <v>299</v>
+      <c r="A53" s="7">
+        <v>7</v>
+      </c>
+      <c r="B53" t="s">
+        <v>300</v>
       </c>
       <c r="D53" t="s">
-        <v>303</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>350</v>
       </c>
       <c r="F53" t="s">
         <v>195</v>
       </c>
-      <c r="I53" t="s">
-        <v>305</v>
-      </c>
-      <c r="P53" t="s">
-        <v>306</v>
+      <c r="I53" s="10" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54">
-        <v>6</v>
-      </c>
-      <c r="C54" t="s">
-        <v>299</v>
+        <v>7</v>
       </c>
       <c r="D54" t="s">
-        <v>307</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>308</v>
+        <v>302</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>353</v>
       </c>
       <c r="F54" t="s">
         <v>195</v>
       </c>
-      <c r="I54" t="s">
-        <v>298</v>
+      <c r="I54" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P54" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55">
-        <v>6</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E55" s="11" t="s">
-        <v>368</v>
+        <v>7</v>
+      </c>
+      <c r="D55" t="s">
+        <v>304</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>352</v>
       </c>
       <c r="F55" t="s">
         <v>195</v>
       </c>
-      <c r="I55" s="12" t="s">
-        <v>255</v>
+      <c r="I55" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="P55" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56">
-        <v>6</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="E56" s="11" t="s">
-        <v>367</v>
+      <c r="A56" s="7">
+        <v>8</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D56" t="s">
+        <v>306</v>
+      </c>
+      <c r="E56" t="s">
+        <v>306</v>
       </c>
       <c r="F56" t="s">
         <v>195</v>
       </c>
-      <c r="I56" s="12" t="s">
-        <v>255</v>
+      <c r="I56" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A57" s="9">
-        <v>7</v>
+      <c r="A57" s="7">
+        <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D57" t="s">
-        <v>310</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>360</v>
+        <v>364</v>
+      </c>
+      <c r="E57" t="s">
+        <v>361</v>
       </c>
       <c r="F57" t="s">
         <v>195</v>
       </c>
-      <c r="I57" s="12" t="s">
-        <v>255</v>
-      </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>311</v>
-      </c>
-      <c r="E58" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E58" t="s">
+        <v>362</v>
+      </c>
+      <c r="F58" t="s">
         <v>363</v>
-      </c>
-      <c r="F58" t="s">
-        <v>195</v>
-      </c>
-      <c r="I58" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P58" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>313</v>
-      </c>
-      <c r="E59" s="9" t="s">
-        <v>362</v>
+        <v>310</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="F59" t="s">
         <v>195</v>
       </c>
-      <c r="I59" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="P59" t="s">
+      <c r="I59" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60" s="9">
-        <v>8</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="A60">
+        <v>9</v>
+      </c>
+      <c r="D60" t="s">
+        <v>313</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D60" t="s">
+      <c r="F60" t="s">
         <v>315</v>
       </c>
-      <c r="E60" t="s">
-        <v>315</v>
-      </c>
-      <c r="F60" t="s">
-        <v>195</v>
-      </c>
-      <c r="I60" t="s">
+      <c r="O60" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A61" s="9">
-        <v>9</v>
+      <c r="A61" s="7">
+        <v>3</v>
       </c>
       <c r="B61" t="s">
         <v>317</v>
@@ -5527,260 +5461,177 @@
       <c r="D61" t="s">
         <v>318</v>
       </c>
-      <c r="E61" s="6" t="s">
-        <v>318</v>
+      <c r="E61" t="s">
+        <v>319</v>
       </c>
       <c r="F61" t="s">
         <v>195</v>
       </c>
-      <c r="I61" t="s">
-        <v>319</v>
+      <c r="G61" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>374</v>
+        <v>320</v>
       </c>
       <c r="E62" t="s">
-        <v>371</v>
+        <v>321</v>
       </c>
       <c r="F62" t="s">
         <v>195</v>
       </c>
+      <c r="G62" t="s">
+        <v>322</v>
+      </c>
+      <c r="I62" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>375</v>
-      </c>
-      <c r="E63" t="s">
-        <v>372</v>
+        <v>323</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>324</v>
       </c>
       <c r="F63" t="s">
-        <v>373</v>
+        <v>195</v>
+      </c>
+      <c r="G63" t="s">
+        <v>322</v>
+      </c>
+      <c r="I63" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A64">
-        <v>9</v>
+      <c r="A64" s="7">
+        <v>10</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="D64" t="s">
-        <v>320</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F64" t="s">
-        <v>195</v>
-      </c>
-      <c r="I64" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="F65" t="s">
-        <v>325</v>
-      </c>
-      <c r="O65" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A66" s="9">
-        <v>3</v>
-      </c>
-      <c r="B66" t="s">
+      <c r="A66">
+        <v>10</v>
+      </c>
+      <c r="D66" t="s">
+        <v>329</v>
+      </c>
+      <c r="F66" t="s">
         <v>327</v>
-      </c>
-      <c r="D66" t="s">
-        <v>328</v>
-      </c>
-      <c r="E66" t="s">
-        <v>329</v>
-      </c>
-      <c r="F66" t="s">
-        <v>195</v>
-      </c>
-      <c r="G66" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A67">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D67" t="s">
         <v>330</v>
       </c>
-      <c r="E67" t="s">
-        <v>331</v>
-      </c>
       <c r="F67" t="s">
-        <v>195</v>
-      </c>
-      <c r="G67" t="s">
-        <v>332</v>
-      </c>
-      <c r="I67" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A68">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D68" t="s">
+        <v>331</v>
+      </c>
+      <c r="F68" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="C69" t="s">
+        <v>351</v>
+      </c>
+      <c r="D69" t="s">
+        <v>366</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F69" t="s">
+        <v>195</v>
+      </c>
+      <c r="I69" t="s">
+        <v>203</v>
+      </c>
+      <c r="P69" t="s">
         <v>333</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="F68" t="s">
-        <v>195</v>
-      </c>
-      <c r="G68" t="s">
-        <v>332</v>
-      </c>
-      <c r="I68" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A69" s="9">
-        <v>10</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D69" t="s">
-        <v>336</v>
-      </c>
-      <c r="F69" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A70">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="C70" t="s">
+        <v>351</v>
       </c>
       <c r="D70" t="s">
-        <v>338</v>
+        <v>367</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>334</v>
       </c>
       <c r="F70" t="s">
-        <v>337</v>
+        <v>195</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>251</v>
+      </c>
+      <c r="P70" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A71">
-        <v>10</v>
+        <v>5</v>
+      </c>
+      <c r="C71" t="s">
+        <v>347</v>
       </c>
       <c r="D71" t="s">
-        <v>339</v>
+        <v>335</v>
+      </c>
+      <c r="E71" t="s">
+        <v>336</v>
       </c>
       <c r="F71" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A72">
-        <v>10</v>
-      </c>
-      <c r="D72" t="s">
-        <v>340</v>
-      </c>
-      <c r="F72" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A73">
-        <v>10</v>
-      </c>
-      <c r="D73" t="s">
-        <v>341</v>
-      </c>
-      <c r="F73" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A74">
-        <v>5</v>
-      </c>
-      <c r="C74" t="s">
-        <v>361</v>
-      </c>
-      <c r="D74" t="s">
-        <v>376</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="F74" t="s">
         <v>195</v>
       </c>
-      <c r="I74" t="s">
-        <v>203</v>
-      </c>
-      <c r="P74" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A75">
-        <v>5</v>
-      </c>
-      <c r="C75" t="s">
-        <v>361</v>
-      </c>
-      <c r="D75" t="s">
-        <v>377</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="F75" t="s">
-        <v>195</v>
-      </c>
-      <c r="I75" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="P75" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A76" s="13">
-        <v>5</v>
-      </c>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="D76" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="E76" s="13" t="s">
-        <v>346</v>
-      </c>
-      <c r="F76" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="I76" s="13" t="s">
+      <c r="I71" t="s">
         <v>74</v>
       </c>
     </row>
@@ -5799,24 +5650,24 @@
         <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="C1" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="D1" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="E1" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="F1" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5830,7 +5681,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5844,7 +5695,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5858,7 +5709,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5872,7 +5723,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5886,7 +5737,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5900,7 +5751,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5914,7 +5765,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5928,7 +5779,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5942,7 +5793,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5956,7 +5807,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5970,7 +5821,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5984,7 +5835,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5998,7 +5849,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -6012,7 +5863,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -6026,10 +5877,10 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B17" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -6040,10 +5891,10 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B18" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -6054,10 +5905,10 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B19" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -6068,10 +5919,10 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B20" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C20">
         <v>90</v>

--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D53A83EC-F070-4258-9E69-E55BD2213754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39AFB3E-7675-41F9-A01C-C96ACD46C40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4752,7 +4752,7 @@
         <v>195</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="P27" t="s">
         <v>245</v>
@@ -4778,7 +4778,7 @@
         <v>195</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="P28" t="s">
         <v>245</v>
@@ -4804,7 +4804,7 @@
         <v>195</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>251</v>
+        <v>74</v>
       </c>
       <c r="P29" t="s">
         <v>245</v>
@@ -5644,6 +5644,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9B6005-6F43-4EB4-8661-C70A2093261E}">
   <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="23.6328125" customWidth="1"/>
+    <col min="2" max="7" width="13.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">

--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30318"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\JFC\04_Software\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39AFB3E-7675-41F9-A01C-C96ACD46C40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{803E6AE5-E07B-4584-9E25-782BE1E59D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="calc_rules" sheetId="1" r:id="rId1"/>
     <sheet name="ui_structure" sheetId="2" r:id="rId2"/>
     <sheet name="frl_reference" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1128" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1109" uniqueCount="365">
   <si>
     <t>system</t>
   </si>
@@ -613,9 +616,15 @@
     <t>Info</t>
   </si>
   <si>
+    <t>Requires FRL</t>
+  </si>
+  <si>
     <t>Means of Detection</t>
   </si>
   <si>
+    <t>Smoke detection system</t>
+  </si>
+  <si>
     <t>Smoke Detectors</t>
   </si>
   <si>
@@ -628,36 +637,42 @@
     <t>Total Quantity,Grid Spacing,Coverage Area,Formula</t>
   </si>
   <si>
+    <t>units</t>
+  </si>
+  <si>
+    <t>Heat detection system</t>
+  </si>
+  <si>
     <t>Heat Detectors</t>
   </si>
   <si>
     <t>Heat Detector</t>
   </si>
   <si>
-    <t>Aspirating Units</t>
+    <t>Aspirating smoke detection system</t>
+  </si>
+  <si>
+    <t>Aspirating Detectors</t>
   </si>
   <si>
     <t>Aspirating Unit</t>
   </si>
   <si>
-    <t>Sampling</t>
+    <t>Aspirating Detector Pipework</t>
   </si>
   <si>
     <t>Sampling Pipework</t>
   </si>
   <si>
-    <t>units</t>
-  </si>
-  <si>
-    <t>Sampling Points</t>
-  </si>
-  <si>
-    <t>Sampling Point</t>
+    <t>kg</t>
   </si>
   <si>
     <t>Manual Call Points</t>
   </si>
   <si>
+    <t>Manual call point</t>
+  </si>
+  <si>
     <t>Fire Indicator Panels</t>
   </si>
   <si>
@@ -667,7 +682,25 @@
     <t>Means of Warning</t>
   </si>
   <si>
-    <t>Audio</t>
+    <t>Visual warning system</t>
+  </si>
+  <si>
+    <t>Visual Alarm Devices</t>
+  </si>
+  <si>
+    <t>Visual alarm device</t>
+  </si>
+  <si>
+    <t>Total Quantity,Grid Spacing,Coverage Area</t>
+  </si>
+  <si>
+    <t>EWIS / voice alarm system</t>
+  </si>
+  <si>
+    <t>EWIS Panels</t>
+  </si>
+  <si>
+    <t>EWIS panel</t>
   </si>
   <si>
     <t>Speakers</t>
@@ -676,241 +709,292 @@
     <t>Speaker</t>
   </si>
   <si>
-    <t>Total Quantity,Grid Spacing,Coverage Area</t>
-  </si>
-  <si>
-    <t>Speaker Batteries</t>
-  </si>
-  <si>
-    <t>Battery</t>
+    <t>Amplifiers</t>
+  </si>
+  <si>
+    <t>Amplifier</t>
+  </si>
+  <si>
+    <t>Audible Warning System</t>
+  </si>
+  <si>
+    <t>Sounders</t>
+  </si>
+  <si>
+    <t>Sounder</t>
+  </si>
+  <si>
+    <t>Cabling</t>
+  </si>
+  <si>
+    <t>Fire-Rated Cabling</t>
+  </si>
+  <si>
+    <t>Non-Fire-Rated Cabling</t>
+  </si>
+  <si>
+    <t>Means of Egress</t>
+  </si>
+  <si>
+    <t>Emergency lighting system</t>
+  </si>
+  <si>
+    <t>Emergency Luminaires</t>
+  </si>
+  <si>
+    <t>Emergency Luminaire</t>
+  </si>
+  <si>
+    <t>Exit signage system</t>
+  </si>
+  <si>
+    <t>Illuminated Exit Signs</t>
+  </si>
+  <si>
+    <t>Illuminated Exit Sign</t>
+  </si>
+  <si>
+    <t>Total Quantity</t>
+  </si>
+  <si>
+    <t>Means of First Aid Fire-Fighting</t>
+  </si>
+  <si>
+    <t>Portable Extinguisher System</t>
+  </si>
+  <si>
+    <t>Extinguishers</t>
+  </si>
+  <si>
+    <t>Fire extinguishers</t>
+  </si>
+  <si>
+    <t>Hose Reels</t>
+  </si>
+  <si>
+    <t>Hose Reel Assembly</t>
+  </si>
+  <si>
+    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
+  </si>
+  <si>
+    <t>reels</t>
+  </si>
+  <si>
+    <t>Hose Reel Pipework</t>
+  </si>
+  <si>
+    <t>Pipework</t>
+  </si>
+  <si>
+    <t>Means of Restricting Fire Spread / Structural Protection</t>
+  </si>
+  <si>
+    <t>Fire-rated Wall Assembly</t>
+  </si>
+  <si>
+    <t>Plasterboard Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fire Resistant Plasterboard </t>
+  </si>
+  <si>
+    <t>Required FRL is a direct user override (no NCC lookup is performed) - select the Product Type matching the required FRL and construction thickness. Carbon factors assume a standard reference density to convert the manufacturer's per-kg factor to a per-m² wall rate, since no project-specific density was supplied.</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Speed Panel Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed Panel </t>
+  </si>
+  <si>
+    <t>Masonry Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Masonry </t>
+  </si>
+  <si>
+    <t>Concrete Wall Assembly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete </t>
+  </si>
+  <si>
+    <t>Doors and Glazing</t>
+  </si>
+  <si>
+    <t>Fire Doors</t>
+  </si>
+  <si>
+    <t>Fire Door</t>
+  </si>
+  <si>
+    <t>Fire Doors (Steel with Glazing)</t>
+  </si>
+  <si>
+    <t>Fire Door(Steel with Glazing)</t>
+  </si>
+  <si>
+    <t>Fire Resistant Glazing</t>
+  </si>
+  <si>
+    <t>Glass Glazing</t>
+  </si>
+  <si>
+    <t>Shutters, Curtains and Dampers</t>
+  </si>
+  <si>
+    <t>Fire Shutters</t>
+  </si>
+  <si>
+    <t>Fire Shutter</t>
+  </si>
+  <si>
+    <t>Fire Curtains</t>
+  </si>
+  <si>
+    <t>Fire Curtain</t>
+  </si>
+  <si>
+    <t>Fusible link damper</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual duct size being protected.</t>
+  </si>
+  <si>
+    <t>Penetration and Joint Fire-Stopping</t>
+  </si>
+  <si>
+    <t>Fire Batts</t>
+  </si>
+  <si>
+    <t>Mastic Fire batt</t>
+  </si>
+  <si>
+    <t>Intumescent Collars</t>
+  </si>
+  <si>
+    <t>Fire collar</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual pipe diameter being protected.</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Joint Seals</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Joint Seal</t>
+  </si>
+  <si>
+    <t>seals</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual joint/pipe size being protected.</t>
+  </si>
+  <si>
+    <t>Intumescent Pipe Wraps</t>
+  </si>
+  <si>
+    <t>Intumescent Pipe Wrap</t>
+  </si>
+  <si>
+    <t>Ensure the selected product's size is suitable for the actual pipe diameter being wrapped.</t>
+  </si>
+  <si>
+    <t>Fire-Resistant Mastic</t>
+  </si>
+  <si>
+    <t>kg,L</t>
+  </si>
+  <si>
+    <t>Structural Fire Protection</t>
+  </si>
+  <si>
+    <t>Intumescent coating</t>
+  </si>
+  <si>
+    <t>Spray-Applied Fire Protection</t>
+  </si>
+  <si>
+    <t>Spray</t>
+  </si>
+  <si>
+    <t>Means of Suppression</t>
+  </si>
+  <si>
+    <t>Sprinklers</t>
+  </si>
+  <si>
+    <t>Sprinkler Heads</t>
+  </si>
+  <si>
+    <t>Sprinkler Head</t>
+  </si>
+  <si>
+    <t>Sprinkler Pipework</t>
+  </si>
+  <si>
+    <t>Total Quantity,Formula</t>
+  </si>
+  <si>
+    <t>vertical_riser_formula,horizontal_pipe_formula</t>
+  </si>
+  <si>
+    <t>The Formula option is an early-stage geometric approximation, not a cited AS clause - verify before relying on it for design.</t>
+  </si>
+  <si>
+    <t>Sprinkler Valves</t>
+  </si>
+  <si>
+    <t>Sprinkler Valve</t>
   </si>
   <si>
     <t>Linked Child</t>
   </si>
   <si>
-    <t>Override Only</t>
-  </si>
-  <si>
-    <t>Amplifiers</t>
-  </si>
-  <si>
-    <t>Amplifier</t>
-  </si>
-  <si>
-    <t>Amplifier Batteries</t>
-  </si>
-  <si>
-    <t>Sounders</t>
-  </si>
-  <si>
-    <t>Sounder</t>
-  </si>
-  <si>
-    <t>Sounder Batteries</t>
-  </si>
-  <si>
-    <t>Sounder Bases</t>
-  </si>
-  <si>
-    <t>Sounder Base</t>
-  </si>
-  <si>
     <t>Choice</t>
   </si>
   <si>
-    <t>Cabling</t>
-  </si>
-  <si>
-    <t>Fire-Rated Cabling</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Cabling</t>
-  </si>
-  <si>
-    <t>EWIS Panels</t>
-  </si>
-  <si>
-    <t>EWIS Panel Batteries</t>
-  </si>
-  <si>
-    <t>Visual Alarm Devices</t>
-  </si>
-  <si>
-    <t>Visual Alarm Device Batteries</t>
-  </si>
-  <si>
-    <t>Mounting Bases</t>
-  </si>
-  <si>
-    <t>Mounting Base</t>
-  </si>
-  <si>
-    <t>Means of First Aid Fire-Fighting</t>
-  </si>
-  <si>
-    <t>Hose Reels</t>
-  </si>
-  <si>
-    <t>Hose Reel Assembly</t>
-  </si>
-  <si>
-    <t>reels</t>
-  </si>
-  <si>
-    <t>Hose Reel Pipework</t>
-  </si>
-  <si>
-    <t>Pipework</t>
-  </si>
-  <si>
-    <t>Means of Restricting Fire Spread / Structural Protection</t>
-  </si>
-  <si>
-    <t>Wall Assemblies</t>
-  </si>
-  <si>
-    <t>Plasterboard Wall Assembly</t>
-  </si>
-  <si>
-    <t>Required FRL is a direct user override (no NCC lookup is performed) - select the Product Type matching the required FRL and construction thickness. Carbon factors assume a standard reference density to convert the manufacturer's per-kg factor to a per-m² wall rate, since no project-specific density was supplied.</t>
-  </si>
-  <si>
-    <t>Speed Panel Wall Assembly</t>
-  </si>
-  <si>
-    <t>Masonry Wall Assembly</t>
-  </si>
-  <si>
-    <t>Concrete Wall Assembly</t>
-  </si>
-  <si>
-    <t>Fire Batts</t>
-  </si>
-  <si>
-    <t>Mastic Fire batt</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Fire Doors</t>
-  </si>
-  <si>
-    <t>Fire Door</t>
+    <t>Water Supply Equipments</t>
+  </si>
+  <si>
+    <t>Pump sets</t>
+  </si>
+  <si>
+    <t>Means of Smoke Hazard Management</t>
+  </si>
+  <si>
+    <t>Smoke Exhaust Fan</t>
+  </si>
+  <si>
+    <t>Smoke Exhaust Fan (notional - 1000mm)</t>
+  </si>
+  <si>
+    <t>Smoke Subducts</t>
+  </si>
+  <si>
+    <t>Ensure the selected product matches the desired duct size.</t>
+  </si>
+  <si>
+    <t>Motorized Smoke Dampers</t>
+  </si>
+  <si>
+    <t>Motorized Dampers</t>
+  </si>
+  <si>
+    <t>Smoke Doors</t>
+  </si>
+  <si>
+    <t>Smoke Door</t>
   </si>
   <si>
     <t>doors</t>
   </si>
   <si>
-    <t>Smoke Doors</t>
-  </si>
-  <si>
-    <t>Smoke Door</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Doors</t>
-  </si>
-  <si>
-    <t>Non-Fire-Rated Door</t>
-  </si>
-  <si>
-    <t>Fire Resistant Glazing</t>
-  </si>
-  <si>
-    <t>Glass Glazing</t>
-  </si>
-  <si>
-    <t>Heat Strengthened Glazing</t>
-  </si>
-  <si>
-    <t>Pipework Protection</t>
-  </si>
-  <si>
-    <t>Intumescent Collars</t>
-  </si>
-  <si>
-    <t>Fire collar</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual pipe diameter being protected.</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Joint Seals</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Joint Seal</t>
-  </si>
-  <si>
-    <t>seals</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual joint/pipe size being protected.</t>
-  </si>
-  <si>
-    <t>Intumescent Pipe Wraps</t>
-  </si>
-  <si>
-    <t>Intumescent Pipe Wrap</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual pipe diameter being wrapped.</t>
-  </si>
-  <si>
-    <t>Fire-Resistant Mastic</t>
-  </si>
-  <si>
-    <t>kg,L</t>
-  </si>
-  <si>
-    <t>Fire-Stop Mortar</t>
-  </si>
-  <si>
-    <t>Applied Structural Fire Protection</t>
-  </si>
-  <si>
-    <t>Fire Shutters</t>
-  </si>
-  <si>
-    <t>Fire Shutter</t>
-  </si>
-  <si>
-    <t>Fire Curtains</t>
-  </si>
-  <si>
-    <t>Fire Curtain</t>
-  </si>
-  <si>
-    <t>Means of Suppression</t>
-  </si>
-  <si>
-    <t>Sprinklers</t>
-  </si>
-  <si>
-    <t>Sprinkler Heads</t>
-  </si>
-  <si>
-    <t>Sprinkler Head</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Sprinkler Pipework</t>
-  </si>
-  <si>
-    <t>Total Quantity,Formula</t>
-  </si>
-  <si>
-    <t>vertical_riser_formula,horizontal_pipe_formula</t>
-  </si>
-  <si>
-    <t>The Formula option is an early-stage geometric approximation, not a cited AS clause - verify before relying on it for design.</t>
-  </si>
-  <si>
-    <t>Sprinkler Valves</t>
-  </si>
-  <si>
-    <t>Sprinkler Valve</t>
+    <t>Means of Fire Brigade Access and Intervention</t>
   </si>
   <si>
     <t>Hydrants</t>
@@ -937,34 +1021,10 @@
     <t>Typically 1 booster assembly per hydrant system - confirm against site layout and AS2419.1.</t>
   </si>
   <si>
-    <t>Means of Smoke Hazard Management</t>
-  </si>
-  <si>
-    <t>Smoke Exhaust Fans</t>
-  </si>
-  <si>
-    <t>Fire Resistant Ductwork</t>
-  </si>
-  <si>
-    <t>Ensure the selected product matches the desired duct size.</t>
-  </si>
-  <si>
-    <t>Regular Sheet Metal Ductwork</t>
-  </si>
-  <si>
-    <t>Means of Fire Brigade Access and Intervention</t>
-  </si>
-  <si>
-    <t>Fire Control Centre</t>
-  </si>
-  <si>
-    <t>centres</t>
-  </si>
-  <si>
     <t>Fire Safety Management</t>
   </si>
   <si>
-    <t>signs</t>
+    <t>Fire safety signage system</t>
   </si>
   <si>
     <t>Evacuation Diagram Systems</t>
@@ -988,30 +1048,6 @@
     <t>Portable Extinguishers,Hose Reel Assembly,Hydrant Valves,Hydrant Boosters</t>
   </si>
   <si>
-    <t>Means of Egress</t>
-  </si>
-  <si>
-    <t>Emergency Luminaires</t>
-  </si>
-  <si>
-    <t>Emergency Luminaire</t>
-  </si>
-  <si>
-    <t>Illuminated Exit Signs</t>
-  </si>
-  <si>
-    <t>Illuminated Exit Sign</t>
-  </si>
-  <si>
-    <t>Total Quantity</t>
-  </si>
-  <si>
-    <t>Directional Exit Signs</t>
-  </si>
-  <si>
-    <t>Directional Exit Sign</t>
-  </si>
-  <si>
     <t>Special Hazards</t>
   </si>
   <si>
@@ -1033,118 +1069,37 @@
     <t>Atrium Fire and Smoke-Control Systems</t>
   </si>
   <si>
-    <t>Motorized Dampers</t>
-  </si>
-  <si>
-    <t>Ensure the selected product's size is suitable for the actual duct size being protected.</t>
-  </si>
-  <si>
-    <t>Fusible link damper</t>
-  </si>
-  <si>
-    <t>Fire Doors (Steel with Glazing)</t>
-  </si>
-  <si>
-    <t>Fire Door(Steel with Glazing)</t>
-  </si>
-  <si>
-    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
-  </si>
-  <si>
-    <t>Portable Extinguisher</t>
-  </si>
-  <si>
-    <t>Extinguishers</t>
-  </si>
-  <si>
-    <t>Fire extinguishers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fire Resistant Plasterboard </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speed Panel </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Masonry </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete </t>
-  </si>
-  <si>
-    <t>Penetration Fire-Stopping</t>
-  </si>
-  <si>
-    <t>Doors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Doors </t>
-  </si>
-  <si>
-    <t>Fire-Resistant Glazing</t>
-  </si>
-  <si>
-    <t>Water Supply Equipments</t>
-  </si>
-  <si>
-    <t>Smoke Exhaust Fan (notional - 1000mm)</t>
-  </si>
-  <si>
-    <t>Fire/Smoke Damper</t>
-  </si>
-  <si>
-    <t>Smoke Subducts 1</t>
-  </si>
-  <si>
-    <t>Smoke Subducts 2</t>
-  </si>
-  <si>
-    <t>EWIS panel</t>
-  </si>
-  <si>
-    <t>Visual alarm device</t>
-  </si>
-  <si>
-    <t>Manual call point</t>
-  </si>
-  <si>
-    <t>End-Suction Centrifugal Pumpset</t>
-  </si>
-  <si>
-    <t>Vertical Multistage Jacking Pumpset</t>
-  </si>
-  <si>
-    <t>Pumpset 1</t>
-  </si>
-  <si>
-    <t>Pumpset 2</t>
-  </si>
-  <si>
-    <t>Small Signs</t>
-  </si>
-  <si>
-    <t>Medium Signs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input </t>
-  </si>
-  <si>
-    <t>Fire Safety Signage 1</t>
-  </si>
-  <si>
-    <t>Fire Safety Signage 2</t>
-  </si>
-  <si>
-    <t>Fire Damper 1</t>
-  </si>
-  <si>
-    <t>Fire Damper 2</t>
-  </si>
-  <si>
-    <t>Intumescent Coating</t>
-  </si>
-  <si>
-    <t>Intumescent coating</t>
+    <t>Things to do</t>
+  </si>
+  <si>
+    <t>Colour</t>
+  </si>
+  <si>
+    <t>1. Check which one exclude</t>
+  </si>
+  <si>
+    <t>Things to work on</t>
+  </si>
+  <si>
+    <t>2. Check which one for future implementation (Think how we show this)</t>
+  </si>
+  <si>
+    <t>Exclude</t>
+  </si>
+  <si>
+    <t>3. Check which one we need to put but not on the list (Future implementation)</t>
+  </si>
+  <si>
+    <t>Future Implementation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Are they in right group? Naming correct? </t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed </t>
   </si>
   <si>
     <t>Product Type</t>
@@ -1178,16 +1133,13 @@
   </si>
   <si>
     <t>13mm</t>
-  </si>
-  <si>
-    <t>Requires FRL</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1201,8 +1153,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1217,42 +1180,60 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor rgb="FFFF66FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF7C80"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF66FF"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1260,22 +1241,81 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,9 +1624,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1612,7 +1652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1678,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -1664,7 +1704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -1690,7 +1730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1716,7 +1756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1742,7 +1782,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1768,7 +1808,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -1794,7 +1834,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
         <v>32</v>
       </c>
@@ -1820,7 +1860,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -1846,7 +1886,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
         <v>32</v>
       </c>
@@ -1872,7 +1912,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1898,7 +1938,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -1924,7 +1964,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>42</v>
       </c>
@@ -1950,7 +1990,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1976,7 +2016,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2002,7 +2042,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>59</v>
       </c>
@@ -2028,7 +2068,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>59</v>
       </c>
@@ -2054,7 +2094,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -2080,7 +2120,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>59</v>
       </c>
@@ -2106,7 +2146,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>59</v>
       </c>
@@ -2132,7 +2172,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>59</v>
       </c>
@@ -2158,7 +2198,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -2184,7 +2224,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -2210,7 +2250,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -2236,7 +2276,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>59</v>
       </c>
@@ -2262,7 +2302,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>59</v>
       </c>
@@ -2288,7 +2328,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>59</v>
       </c>
@@ -2314,7 +2354,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -2340,7 +2380,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>59</v>
       </c>
@@ -2366,7 +2406,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -2392,7 +2432,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>59</v>
       </c>
@@ -2418,7 +2458,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
         <v>59</v>
       </c>
@@ -2444,7 +2484,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8">
       <c r="A34" t="s">
         <v>59</v>
       </c>
@@ -2470,7 +2510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
         <v>59</v>
       </c>
@@ -2496,7 +2536,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8">
       <c r="A36" t="s">
         <v>59</v>
       </c>
@@ -2522,7 +2562,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8">
       <c r="A37" t="s">
         <v>59</v>
       </c>
@@ -2548,7 +2588,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8">
       <c r="A38" t="s">
         <v>59</v>
       </c>
@@ -2574,7 +2614,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8">
       <c r="A39" t="s">
         <v>59</v>
       </c>
@@ -2600,7 +2640,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8">
       <c r="A40" t="s">
         <v>59</v>
       </c>
@@ -2626,7 +2666,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
         <v>59</v>
       </c>
@@ -2652,7 +2692,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -2678,7 +2718,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -2704,7 +2744,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
         <v>59</v>
       </c>
@@ -2730,7 +2770,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
         <v>59</v>
       </c>
@@ -2756,7 +2796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8">
       <c r="A46" t="s">
         <v>59</v>
       </c>
@@ -2782,7 +2822,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -2808,7 +2848,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8">
       <c r="A48" t="s">
         <v>59</v>
       </c>
@@ -2834,7 +2874,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8">
       <c r="A49" t="s">
         <v>59</v>
       </c>
@@ -2860,7 +2900,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8">
       <c r="A50" t="s">
         <v>59</v>
       </c>
@@ -2886,7 +2926,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8">
       <c r="A51" t="s">
         <v>59</v>
       </c>
@@ -2912,7 +2952,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -2938,7 +2978,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8">
       <c r="A53" t="s">
         <v>59</v>
       </c>
@@ -2964,7 +3004,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8">
       <c r="A54" t="s">
         <v>59</v>
       </c>
@@ -2990,7 +3030,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
         <v>59</v>
       </c>
@@ -3016,7 +3056,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -3042,7 +3082,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -3068,7 +3108,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -3094,7 +3134,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8">
       <c r="A59" t="s">
         <v>59</v>
       </c>
@@ -3120,7 +3160,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8">
       <c r="A60" t="s">
         <v>59</v>
       </c>
@@ -3146,7 +3186,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8">
       <c r="A61" t="s">
         <v>59</v>
       </c>
@@ -3172,7 +3212,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8">
       <c r="A62" t="s">
         <v>59</v>
       </c>
@@ -3198,7 +3238,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8">
       <c r="A63" t="s">
         <v>59</v>
       </c>
@@ -3224,7 +3264,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8">
       <c r="A64" t="s">
         <v>59</v>
       </c>
@@ -3250,7 +3290,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8">
       <c r="A65" t="s">
         <v>59</v>
       </c>
@@ -3276,7 +3316,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8">
       <c r="A66" t="s">
         <v>59</v>
       </c>
@@ -3302,7 +3342,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
         <v>59</v>
       </c>
@@ -3328,7 +3368,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8">
       <c r="A68" t="s">
         <v>59</v>
       </c>
@@ -3354,7 +3394,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8">
       <c r="A69" t="s">
         <v>59</v>
       </c>
@@ -3380,7 +3420,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8">
       <c r="A70" t="s">
         <v>59</v>
       </c>
@@ -3406,7 +3446,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8">
       <c r="A71" t="s">
         <v>59</v>
       </c>
@@ -3432,7 +3472,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8">
       <c r="A72" t="s">
         <v>59</v>
       </c>
@@ -3458,7 +3498,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>59</v>
       </c>
@@ -3484,7 +3524,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8">
       <c r="A74" t="s">
         <v>59</v>
       </c>
@@ -3510,7 +3550,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
         <v>59</v>
       </c>
@@ -3536,7 +3576,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
         <v>59</v>
       </c>
@@ -3562,7 +3602,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>118</v>
       </c>
@@ -3588,7 +3628,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8">
       <c r="A78" t="s">
         <v>118</v>
       </c>
@@ -3614,7 +3654,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8">
       <c r="A79" t="s">
         <v>118</v>
       </c>
@@ -3640,7 +3680,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8">
       <c r="A80" t="s">
         <v>118</v>
       </c>
@@ -3666,7 +3706,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8">
       <c r="A81" t="s">
         <v>131</v>
       </c>
@@ -3692,7 +3732,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8">
       <c r="A82" t="s">
         <v>131</v>
       </c>
@@ -3718,7 +3758,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8">
       <c r="A83" t="s">
         <v>131</v>
       </c>
@@ -3744,7 +3784,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8">
       <c r="A84" t="s">
         <v>131</v>
       </c>
@@ -3770,7 +3810,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8">
       <c r="A85" t="s">
         <v>131</v>
       </c>
@@ -3796,7 +3836,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8">
       <c r="A86" t="s">
         <v>147</v>
       </c>
@@ -3822,7 +3862,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8">
       <c r="A87" t="s">
         <v>147</v>
       </c>
@@ -3848,7 +3888,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>147</v>
       </c>
@@ -3874,7 +3914,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8">
       <c r="A89" t="s">
         <v>147</v>
       </c>
@@ -3900,7 +3940,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
         <v>160</v>
       </c>
@@ -3926,7 +3966,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8">
       <c r="A91" t="s">
         <v>160</v>
       </c>
@@ -3952,7 +3992,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8">
       <c r="A92" t="s">
         <v>160</v>
       </c>
@@ -3978,7 +4018,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8">
       <c r="A93" t="s">
         <v>160</v>
       </c>
@@ -4004,7 +4044,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
         <v>160</v>
       </c>
@@ -4030,7 +4070,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8">
       <c r="A95" t="s">
         <v>42</v>
       </c>
@@ -4056,7 +4096,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8">
       <c r="A96" t="s">
         <v>42</v>
       </c>
@@ -4082,7 +4122,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8">
       <c r="A97" t="s">
         <v>42</v>
       </c>
@@ -4115,26 +4155,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:R71"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:R81"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="17" width="20" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>175</v>
       </c>
       <c r="B1" t="s">
         <v>176</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="5" t="s">
         <v>179</v>
       </c>
       <c r="F1" t="s">
@@ -4174,27 +4218,33 @@
         <v>191</v>
       </c>
       <c r="R1" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A2" s="7">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15">
+      <c r="A2" s="22">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="D2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G2" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="I2" t="s">
+        <v>199</v>
       </c>
       <c r="L2" t="s">
         <v>42</v>
@@ -4206,21 +4256,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3" spans="1:18" ht="15">
+      <c r="A3" s="22">
         <v>1</v>
       </c>
+      <c r="B3" t="s">
+        <v>193</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>200</v>
+      </c>
       <c r="D3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" t="s">
         <v>197</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>198</v>
       </c>
-      <c r="F3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G3" t="s">
-        <v>196</v>
+      <c r="I3" t="s">
+        <v>199</v>
       </c>
       <c r="L3" t="s">
         <v>42</v>
@@ -4232,21 +4291,30 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:18" ht="15">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
+      <c r="B4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>203</v>
+      </c>
       <c r="D4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E4" t="s">
+        <v>205</v>
+      </c>
+      <c r="F4" t="s">
+        <v>197</v>
+      </c>
+      <c r="G4" t="s">
+        <v>198</v>
+      </c>
+      <c r="I4" t="s">
         <v>199</v>
-      </c>
-      <c r="E4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G4" t="s">
-        <v>196</v>
       </c>
       <c r="L4" t="s">
         <v>42</v>
@@ -4258,1384 +4326,1247 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A5" s="22">
         <v>1</v>
       </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" t="s">
-        <v>202</v>
-      </c>
-      <c r="F5" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="B5" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="15">
+      <c r="A6" s="22">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15">
+      <c r="A7" s="22">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="9"/>
+      <c r="D7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15">
+      <c r="A8" s="23">
+        <v>2</v>
+      </c>
+      <c r="B8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="D8" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
+        <v>197</v>
+      </c>
+      <c r="G8" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15">
+      <c r="A9" s="23">
+        <v>2</v>
+      </c>
+      <c r="B9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="D9" t="s">
+        <v>219</v>
+      </c>
+      <c r="E9" t="s">
+        <v>220</v>
+      </c>
+      <c r="F9" t="s">
+        <v>197</v>
+      </c>
+      <c r="I9" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A10" s="23">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A11" s="23">
+        <v>2</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A12" s="23">
+        <v>2</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A13" s="23">
+        <v>2</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A14" s="23">
+        <v>2</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15">
+      <c r="A15" s="22">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" t="s">
+        <v>232</v>
+      </c>
+      <c r="D15" t="s">
+        <v>233</v>
+      </c>
+      <c r="E15" t="s">
+        <v>234</v>
+      </c>
+      <c r="F15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" t="s">
+        <v>217</v>
+      </c>
+      <c r="I15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15">
+      <c r="A16" s="22">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" t="s">
+        <v>236</v>
+      </c>
+      <c r="E16" t="s">
+        <v>237</v>
+      </c>
+      <c r="F16" t="s">
+        <v>197</v>
+      </c>
+      <c r="G16" t="s">
+        <v>238</v>
+      </c>
+      <c r="I16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="21" customFormat="1" ht="15">
+      <c r="A17" s="23">
+        <v>4</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15">
+      <c r="A18" s="23">
+        <v>4</v>
+      </c>
+      <c r="B18" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" t="s">
+        <v>197</v>
+      </c>
+      <c r="I18" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A19" s="23">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15">
+      <c r="A20" s="22">
+        <v>5</v>
+      </c>
+      <c r="B20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="D20" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>1</v>
-      </c>
-      <c r="C6" t="s">
-        <v>201</v>
-      </c>
-      <c r="D6" t="s">
-        <v>204</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="F6" t="s">
-        <v>195</v>
-      </c>
-      <c r="I6" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F7" t="s">
-        <v>195</v>
-      </c>
-      <c r="I7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>207</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="E20" t="s">
+        <v>252</v>
+      </c>
+      <c r="F20" t="s">
+        <v>197</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P20" t="s">
+        <v>253</v>
+      </c>
+      <c r="R20" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="15">
+      <c r="A21" s="22">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>249</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D21" t="s">
+        <v>255</v>
+      </c>
+      <c r="E21" t="s">
+        <v>256</v>
+      </c>
+      <c r="F21" t="s">
+        <v>197</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P21" t="s">
+        <v>253</v>
+      </c>
+      <c r="R21" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15">
+      <c r="A22" s="22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" t="s">
+        <v>257</v>
+      </c>
+      <c r="E22" t="s">
+        <v>258</v>
+      </c>
+      <c r="F22" t="s">
+        <v>197</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P22" t="s">
+        <v>253</v>
+      </c>
+      <c r="R22" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15">
+      <c r="A23" s="22">
+        <v>5</v>
+      </c>
+      <c r="B23" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" t="s">
+        <v>260</v>
+      </c>
+      <c r="F23" t="s">
+        <v>197</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P23" t="s">
+        <v>253</v>
+      </c>
+      <c r="R23" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15">
+      <c r="A24" s="22">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="D24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E24" t="s">
+        <v>263</v>
+      </c>
+      <c r="F24" t="s">
+        <v>197</v>
+      </c>
+      <c r="I24" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15">
+      <c r="A25" s="22">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D25" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" t="s">
+        <v>197</v>
+      </c>
+      <c r="I25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="15">
+      <c r="A26" s="22">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="D26" t="s">
+        <v>266</v>
+      </c>
+      <c r="E26" t="s">
+        <v>267</v>
+      </c>
+      <c r="F26" t="s">
+        <v>197</v>
+      </c>
+      <c r="I26" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15">
+      <c r="A27" s="22">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>249</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D27" t="s">
+        <v>269</v>
+      </c>
+      <c r="E27" t="s">
+        <v>270</v>
+      </c>
+      <c r="F27" t="s">
+        <v>197</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15">
+      <c r="A28" s="22">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D28" t="s">
+        <v>271</v>
+      </c>
+      <c r="E28" t="s">
+        <v>272</v>
+      </c>
+      <c r="F28" t="s">
+        <v>197</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15">
+      <c r="A29" s="22">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" t="s">
+        <v>273</v>
+      </c>
+      <c r="E29" t="s">
+        <v>273</v>
+      </c>
+      <c r="F29" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F8" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A9" s="7">
-        <v>2</v>
-      </c>
-      <c r="B9" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" t="s">
-        <v>210</v>
-      </c>
-      <c r="D9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F9" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>210</v>
-      </c>
-      <c r="D10" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F10" t="s">
-        <v>216</v>
-      </c>
-      <c r="J10" t="s">
-        <v>211</v>
-      </c>
-      <c r="K10" t="s">
+      <c r="P29" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15">
+      <c r="A30" s="22">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>249</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D30" t="s">
+        <v>276</v>
+      </c>
+      <c r="E30" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" t="s">
+        <v>197</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="15">
+      <c r="A31" s="22">
+        <v>5</v>
+      </c>
+      <c r="B31" t="s">
+        <v>249</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="D31" t="s">
+        <v>278</v>
+      </c>
+      <c r="E31" t="s">
+        <v>279</v>
+      </c>
+      <c r="F31" t="s">
+        <v>197</v>
+      </c>
+      <c r="I31" t="s">
+        <v>199</v>
+      </c>
+      <c r="P31" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="6" customFormat="1" ht="15">
+      <c r="A32" s="22">
+        <v>5</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="P32" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A33" s="22">
+        <v>5</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A34" s="22">
+        <v>5</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" ht="15">
+      <c r="A35" s="22">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>249</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>290</v>
+      </c>
+      <c r="D35" t="s">
+        <v>291</v>
+      </c>
+      <c r="E35" t="s">
+        <v>291</v>
+      </c>
+      <c r="F35" t="s">
+        <v>197</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A36" s="22">
+        <v>5</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" ht="15">
+      <c r="A37" s="23">
+        <v>6</v>
+      </c>
+      <c r="B37" t="s">
+        <v>294</v>
+      </c>
+      <c r="C37" t="s">
+        <v>295</v>
+      </c>
+      <c r="D37" t="s">
+        <v>296</v>
+      </c>
+      <c r="E37" t="s">
+        <v>297</v>
+      </c>
+      <c r="F37" t="s">
+        <v>197</v>
+      </c>
+      <c r="G37" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>2</v>
-      </c>
-      <c r="C11" t="s">
-        <v>210</v>
-      </c>
-      <c r="D11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="F11" t="s">
-        <v>195</v>
-      </c>
-      <c r="I11" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="C12" t="s">
-        <v>210</v>
-      </c>
-      <c r="D12" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F12" t="s">
-        <v>216</v>
-      </c>
-      <c r="J12" t="s">
-        <v>218</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>2</v>
-      </c>
-      <c r="C13" t="s">
-        <v>210</v>
-      </c>
-      <c r="D13" t="s">
-        <v>221</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="F13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G13" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>2</v>
-      </c>
-      <c r="C14" t="s">
-        <v>210</v>
-      </c>
-      <c r="D14" t="s">
-        <v>223</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F14" t="s">
-        <v>216</v>
-      </c>
-      <c r="J14" t="s">
-        <v>221</v>
-      </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>2</v>
-      </c>
-      <c r="C15" t="s">
-        <v>210</v>
-      </c>
-      <c r="D15" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="F15" t="s">
-        <v>216</v>
-      </c>
-      <c r="J15" t="s">
-        <v>221</v>
-      </c>
-      <c r="K15" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>227</v>
-      </c>
-      <c r="D16" t="s">
-        <v>228</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F16" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="C17" t="s">
-        <v>227</v>
-      </c>
-      <c r="D17" t="s">
-        <v>229</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="C18" t="s">
-        <v>230</v>
-      </c>
-      <c r="D18" t="s">
-        <v>230</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="F18" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>2</v>
-      </c>
-      <c r="C19" t="s">
-        <v>230</v>
-      </c>
-      <c r="D19" t="s">
-        <v>231</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F19" t="s">
-        <v>216</v>
-      </c>
-      <c r="J19" t="s">
-        <v>230</v>
-      </c>
-      <c r="K19" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>232</v>
-      </c>
-      <c r="D20" t="s">
-        <v>232</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>355</v>
-      </c>
-      <c r="F20" t="s">
-        <v>195</v>
-      </c>
-      <c r="G20" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>2</v>
-      </c>
-      <c r="C21" t="s">
-        <v>232</v>
-      </c>
-      <c r="D21" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F21" t="s">
-        <v>216</v>
-      </c>
-      <c r="J21" t="s">
-        <v>232</v>
-      </c>
-      <c r="K21" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>2</v>
-      </c>
-      <c r="C22" t="s">
-        <v>232</v>
-      </c>
-      <c r="D22" t="s">
-        <v>234</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="F22" t="s">
-        <v>216</v>
-      </c>
-      <c r="J22" t="s">
-        <v>232</v>
-      </c>
-      <c r="K22" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A23" s="7">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>236</v>
-      </c>
-      <c r="C23" t="s">
-        <v>237</v>
-      </c>
-      <c r="D23" t="s">
-        <v>238</v>
-      </c>
-      <c r="E23" s="1" t="s">
+      <c r="H37" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" ht="15">
+      <c r="A38" s="23">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>294</v>
+      </c>
+      <c r="C38" t="s">
+        <v>295</v>
+      </c>
+      <c r="D38" t="s">
+        <v>298</v>
+      </c>
+      <c r="E38" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" t="s">
+        <v>197</v>
+      </c>
+      <c r="G38" t="s">
+        <v>299</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J38" t="s">
+        <v>296</v>
+      </c>
+      <c r="L38" t="s">
+        <v>8</v>
+      </c>
+      <c r="M38" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" t="s">
+        <v>300</v>
+      </c>
+      <c r="P38" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A39" s="23">
+        <v>6</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" ht="15">
+      <c r="A40" s="23">
+        <v>6</v>
+      </c>
+      <c r="B40" t="s">
+        <v>294</v>
+      </c>
+      <c r="C40" t="s">
+        <v>306</v>
+      </c>
+      <c r="D40" t="s">
+        <v>307</v>
+      </c>
+      <c r="E40" t="s">
+        <v>307</v>
+      </c>
+      <c r="F40" t="s">
+        <v>197</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" ht="15">
+      <c r="A41" s="22">
+        <v>7</v>
+      </c>
+      <c r="B41" t="s">
+        <v>308</v>
+      </c>
+      <c r="D41" t="s">
+        <v>309</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F41" t="s">
+        <v>197</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" ht="15">
+      <c r="A42" s="22">
+        <v>7</v>
+      </c>
+      <c r="B42" t="s">
+        <v>308</v>
+      </c>
+      <c r="D42" t="s">
+        <v>311</v>
+      </c>
+      <c r="E42" t="s">
+        <v>311</v>
+      </c>
+      <c r="F42" t="s">
+        <v>197</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="P42" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A43" s="22">
+        <v>7</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="P43" s="16" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" s="6" customFormat="1" ht="15">
+      <c r="A44" s="22">
+        <v>7</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="C44" s="14"/>
+      <c r="D44" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A45" s="23">
+        <v>8</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="P45" s="16" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A46" s="23">
+        <v>8</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A47" s="23">
+        <v>8</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>325</v>
+      </c>
+      <c r="P47" s="16" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" s="16" customFormat="1" ht="15">
+      <c r="A48" s="22">
+        <v>9</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A49" s="22">
+        <v>9</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="I49" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A50" s="22">
+        <v>9</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A51" s="23">
+        <v>10</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F23" t="s">
-        <v>195</v>
-      </c>
-      <c r="I23" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D24" t="s">
-        <v>240</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="F24" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A25" s="3">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="F51" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D25" s="3" t="s">
+    </row>
+    <row r="52" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A52" s="23">
+        <v>10</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F52" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A53" s="23">
+        <v>10</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A26">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>242</v>
-      </c>
-      <c r="C26" t="s">
-        <v>243</v>
-      </c>
-      <c r="D26" t="s">
-        <v>244</v>
-      </c>
-      <c r="E26" s="1" t="s">
+      <c r="F53" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A54" s="23">
+        <v>10</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D54" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="F26" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P26" t="s">
-        <v>245</v>
-      </c>
-      <c r="R26" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A27">
-        <v>5</v>
-      </c>
-      <c r="C27" t="s">
-        <v>243</v>
-      </c>
-      <c r="D27" t="s">
-        <v>246</v>
-      </c>
-      <c r="E27" s="1" t="s">
+      <c r="F54" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="6" customFormat="1" ht="15">
+      <c r="A55" s="23">
+        <v>10</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="F27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P27" t="s">
-        <v>245</v>
-      </c>
-      <c r="R27" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A28">
-        <v>5</v>
-      </c>
-      <c r="C28" t="s">
-        <v>243</v>
-      </c>
-      <c r="D28" t="s">
-        <v>247</v>
-      </c>
-      <c r="E28" s="1" t="s">
+      <c r="F55" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="B58" t="s">
         <v>343</v>
       </c>
-      <c r="F28" t="s">
-        <v>195</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P28" t="s">
-        <v>245</v>
-      </c>
-      <c r="R28" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A29">
-        <v>5</v>
-      </c>
-      <c r="C29" t="s">
-        <v>243</v>
-      </c>
-      <c r="D29" t="s">
-        <v>248</v>
-      </c>
-      <c r="E29" s="1" t="s">
+      <c r="F58" t="s">
         <v>344</v>
       </c>
-      <c r="F29" t="s">
-        <v>195</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P29" t="s">
-        <v>245</v>
-      </c>
-      <c r="R29" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A30">
-        <v>5</v>
-      </c>
-      <c r="C30" t="s">
+    </row>
+    <row r="59" spans="1:15">
+      <c r="B59" t="s">
         <v>345</v>
       </c>
-      <c r="D30" t="s">
-        <v>249</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="F30" t="s">
-        <v>195</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A31">
-        <v>5</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="F59" s="1"/>
+      <c r="G59" t="s">
         <v>346</v>
       </c>
-      <c r="D31" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="F31" t="s">
-        <v>195</v>
-      </c>
-      <c r="I31" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A32">
-        <v>5</v>
-      </c>
-      <c r="C32" t="s">
+    </row>
+    <row r="60" spans="1:15">
+      <c r="B60" t="s">
         <v>347</v>
       </c>
-      <c r="D32" t="s">
-        <v>255</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F32" t="s">
-        <v>195</v>
-      </c>
-      <c r="I32" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A33">
-        <v>5</v>
-      </c>
-      <c r="C33" t="s">
-        <v>347</v>
-      </c>
-      <c r="D33" t="s">
-        <v>257</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F33" t="s">
-        <v>195</v>
-      </c>
-      <c r="I33" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <v>5</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="F60" s="4"/>
+      <c r="G60" t="s">
         <v>348</v>
       </c>
-      <c r="D34" t="s">
-        <v>259</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="F34" t="s">
-        <v>195</v>
-      </c>
-      <c r="I34" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A35">
-        <v>5</v>
-      </c>
-      <c r="C35" t="s">
-        <v>348</v>
-      </c>
-      <c r="D35" t="s">
-        <v>261</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F35" t="s">
-        <v>195</v>
-      </c>
-      <c r="I35" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A36">
-        <v>5</v>
-      </c>
-      <c r="C36" t="s">
-        <v>262</v>
-      </c>
-      <c r="D36" t="s">
-        <v>263</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="F36" t="s">
-        <v>195</v>
-      </c>
-      <c r="I36" t="s">
-        <v>203</v>
-      </c>
-      <c r="P36" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <v>5</v>
-      </c>
-      <c r="C37" t="s">
-        <v>262</v>
-      </c>
-      <c r="D37" t="s">
-        <v>266</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="F37" t="s">
-        <v>195</v>
-      </c>
-      <c r="I37" t="s">
-        <v>268</v>
-      </c>
-      <c r="P37" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A38">
-        <v>5</v>
-      </c>
-      <c r="C38" t="s">
-        <v>262</v>
-      </c>
-      <c r="D38" t="s">
-        <v>270</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F38" t="s">
-        <v>195</v>
-      </c>
-      <c r="I38" t="s">
-        <v>109</v>
-      </c>
-      <c r="P38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A39">
-        <v>5</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>368</v>
-      </c>
-      <c r="D39" t="s">
-        <v>369</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="F39" t="s">
-        <v>195</v>
-      </c>
-      <c r="I39" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A40">
-        <v>5</v>
-      </c>
-      <c r="D40" t="s">
-        <v>273</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F40" t="s">
-        <v>195</v>
-      </c>
-      <c r="I40" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A41">
-        <v>5</v>
-      </c>
-      <c r="D41" t="s">
-        <v>275</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F41" t="s">
-        <v>195</v>
-      </c>
-      <c r="I41" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A42">
-        <v>5</v>
-      </c>
-      <c r="D42" t="s">
-        <v>276</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F42" t="s">
-        <v>195</v>
-      </c>
-      <c r="I42" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A43">
-        <v>5</v>
-      </c>
-      <c r="C43" t="s">
-        <v>278</v>
-      </c>
-      <c r="D43" t="s">
-        <v>277</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="F43" t="s">
-        <v>195</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A44">
-        <v>5</v>
-      </c>
-      <c r="C44" t="s">
-        <v>280</v>
-      </c>
-      <c r="D44" t="s">
-        <v>279</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="F44" t="s">
-        <v>195</v>
-      </c>
-      <c r="I44" s="10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A45" s="7">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>281</v>
-      </c>
-      <c r="C45" t="s">
-        <v>282</v>
-      </c>
-      <c r="D45" t="s">
-        <v>283</v>
-      </c>
-      <c r="E45" t="s">
-        <v>284</v>
-      </c>
-      <c r="F45" t="s">
-        <v>195</v>
-      </c>
-      <c r="G45" t="s">
-        <v>213</v>
-      </c>
-      <c r="H45" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A46">
-        <v>6</v>
-      </c>
-      <c r="C46" t="s">
-        <v>282</v>
-      </c>
-      <c r="D46" t="s">
-        <v>286</v>
-      </c>
-      <c r="E46" t="s">
-        <v>286</v>
-      </c>
-      <c r="F46" t="s">
-        <v>195</v>
-      </c>
-      <c r="G46" t="s">
-        <v>287</v>
-      </c>
-      <c r="I46" s="10" t="s">
-        <v>109</v>
-      </c>
-      <c r="J46" t="s">
-        <v>283</v>
-      </c>
-      <c r="L46" t="s">
-        <v>8</v>
-      </c>
-      <c r="M46" t="s">
-        <v>22</v>
-      </c>
-      <c r="N46" t="s">
-        <v>288</v>
-      </c>
-      <c r="P46" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A47">
-        <v>6</v>
-      </c>
-      <c r="C47" t="s">
-        <v>282</v>
-      </c>
-      <c r="D47" t="s">
-        <v>290</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="F47" t="s">
-        <v>216</v>
-      </c>
-      <c r="J47" t="s">
-        <v>283</v>
-      </c>
-      <c r="K47" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A48">
-        <v>6</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="F48" t="s">
-        <v>195</v>
-      </c>
-      <c r="I48" t="s">
-        <v>293</v>
-      </c>
-      <c r="P48" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A49">
-        <v>6</v>
-      </c>
-      <c r="C49" t="s">
-        <v>292</v>
-      </c>
-      <c r="D49" t="s">
-        <v>295</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F49" t="s">
-        <v>195</v>
-      </c>
-      <c r="I49" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A50">
-        <v>6</v>
-      </c>
-      <c r="C50" t="s">
-        <v>292</v>
-      </c>
-      <c r="D50" t="s">
-        <v>296</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="F50" t="s">
-        <v>195</v>
-      </c>
-      <c r="I50" t="s">
-        <v>298</v>
-      </c>
-      <c r="P50" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A51">
-        <v>6</v>
-      </c>
-      <c r="C51" s="5" t="s">
+    </row>
+    <row r="61" spans="1:15">
+      <c r="B61" t="s">
         <v>349</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="F51" t="s">
-        <v>195</v>
-      </c>
-      <c r="I51" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A52">
-        <v>6</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>357</v>
-      </c>
-      <c r="F52" t="s">
-        <v>195</v>
-      </c>
-      <c r="I52" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A53" s="7">
-        <v>7</v>
-      </c>
-      <c r="B53" t="s">
-        <v>300</v>
-      </c>
-      <c r="D53" t="s">
-        <v>301</v>
-      </c>
-      <c r="E53" s="6" t="s">
+      <c r="F61" s="6"/>
+      <c r="G61" t="s">
         <v>350</v>
       </c>
-      <c r="F53" t="s">
-        <v>195</v>
-      </c>
-      <c r="I53" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A54">
-        <v>7</v>
-      </c>
-      <c r="D54" t="s">
-        <v>302</v>
-      </c>
-      <c r="E54" s="7" t="s">
+    </row>
+    <row r="62" spans="1:15">
+      <c r="B62" t="s">
+        <v>351</v>
+      </c>
+      <c r="F62" s="8"/>
+      <c r="G62" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="F63" s="7"/>
+      <c r="G63" t="s">
         <v>353</v>
       </c>
-      <c r="F54" t="s">
-        <v>195</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P54" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A55">
-        <v>7</v>
-      </c>
-      <c r="D55" t="s">
-        <v>304</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="F55" t="s">
-        <v>195</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="P55" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A56" s="7">
-        <v>8</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="D56" t="s">
-        <v>306</v>
-      </c>
-      <c r="E56" t="s">
-        <v>306</v>
-      </c>
-      <c r="F56" t="s">
-        <v>195</v>
-      </c>
-      <c r="I56" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A57" s="7">
-        <v>9</v>
-      </c>
-      <c r="B57" t="s">
-        <v>308</v>
-      </c>
-      <c r="D57" t="s">
-        <v>364</v>
-      </c>
-      <c r="E57" t="s">
-        <v>361</v>
-      </c>
-      <c r="F57" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A58">
-        <v>9</v>
-      </c>
-      <c r="D58" t="s">
-        <v>365</v>
-      </c>
-      <c r="E58" t="s">
-        <v>362</v>
-      </c>
-      <c r="F58" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A59">
-        <v>9</v>
-      </c>
-      <c r="D59" t="s">
-        <v>310</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F59" t="s">
-        <v>195</v>
-      </c>
-      <c r="I59" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A60">
-        <v>9</v>
-      </c>
-      <c r="D60" t="s">
-        <v>313</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F60" t="s">
-        <v>315</v>
-      </c>
-      <c r="O60" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A61" s="7">
-        <v>3</v>
-      </c>
-      <c r="B61" t="s">
-        <v>317</v>
-      </c>
-      <c r="D61" t="s">
-        <v>318</v>
-      </c>
-      <c r="E61" t="s">
-        <v>319</v>
-      </c>
-      <c r="F61" t="s">
-        <v>195</v>
-      </c>
-      <c r="G61" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A62">
-        <v>3</v>
-      </c>
-      <c r="D62" t="s">
-        <v>320</v>
-      </c>
-      <c r="E62" t="s">
-        <v>321</v>
-      </c>
-      <c r="F62" t="s">
-        <v>195</v>
-      </c>
-      <c r="G62" t="s">
-        <v>322</v>
-      </c>
-      <c r="I62" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A63">
-        <v>3</v>
-      </c>
-      <c r="D63" t="s">
-        <v>323</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F63" t="s">
-        <v>195</v>
-      </c>
-      <c r="G63" t="s">
-        <v>322</v>
-      </c>
-      <c r="I63" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A64" s="7">
-        <v>10</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="D64" t="s">
-        <v>326</v>
-      </c>
-      <c r="F64" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A65">
-        <v>10</v>
-      </c>
-      <c r="D65" t="s">
-        <v>328</v>
-      </c>
-      <c r="F65" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A66">
-        <v>10</v>
-      </c>
-      <c r="D66" t="s">
-        <v>329</v>
-      </c>
-      <c r="F66" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A67">
-        <v>10</v>
-      </c>
-      <c r="D67" t="s">
-        <v>330</v>
-      </c>
-      <c r="F67" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A68">
-        <v>10</v>
-      </c>
-      <c r="D68" t="s">
-        <v>331</v>
-      </c>
-      <c r="F68" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A69">
-        <v>5</v>
-      </c>
-      <c r="C69" t="s">
-        <v>351</v>
-      </c>
-      <c r="D69" t="s">
-        <v>366</v>
-      </c>
-      <c r="E69" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="F69" t="s">
-        <v>195</v>
-      </c>
-      <c r="I69" t="s">
-        <v>203</v>
-      </c>
-      <c r="P69" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A70">
-        <v>5</v>
-      </c>
-      <c r="C70" t="s">
-        <v>351</v>
-      </c>
-      <c r="D70" t="s">
-        <v>367</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="F70" t="s">
-        <v>195</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="P70" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A71">
-        <v>5</v>
-      </c>
-      <c r="C71" t="s">
-        <v>347</v>
-      </c>
-      <c r="D71" t="s">
-        <v>335</v>
-      </c>
-      <c r="E71" t="s">
-        <v>336</v>
-      </c>
-      <c r="F71" t="s">
-        <v>195</v>
-      </c>
-      <c r="I71" t="s">
-        <v>74</v>
-      </c>
-    </row>
+    </row>
+    <row r="64" spans="1:15" ht="15"/>
+    <row r="68" ht="15"/>
+    <row r="70" ht="15"/>
+    <row r="74" ht="15"/>
+    <row r="75" ht="15"/>
+    <row r="81" ht="15"/>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R55">
+    <sortCondition ref="A2:A55"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5643,35 +5574,31 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9B6005-6F43-4EB4-8661-C70A2093261E}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="23.6328125" customWidth="1"/>
-    <col min="2" max="7" width="13.6328125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>179</v>
       </c>
       <c r="B1" t="s">
-        <v>370</v>
+        <v>354</v>
       </c>
       <c r="C1" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D1" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="E1" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="F1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5683,9 +5610,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5697,9 +5624,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5711,9 +5638,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5725,9 +5652,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5739,9 +5666,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>375</v>
+        <v>359</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5753,9 +5680,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5767,9 +5694,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5781,9 +5708,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5795,9 +5722,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5809,9 +5736,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5823,9 +5750,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>376</v>
+        <v>360</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5837,9 +5764,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5851,9 +5778,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -5865,9 +5792,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -5879,12 +5806,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B17" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -5893,12 +5820,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B18" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -5907,12 +5834,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B19" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -5921,12 +5848,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="B20" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="C20">
         <v>90</v>
@@ -5938,4 +5865,207 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5712268625b41a295c1c13b9cc08810">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2284d5a418b13d67f420d8f33de3453b" ns2:_="">
+    <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9a4568ba-f362-4e84-99d7-dc60d25416b3" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="4148a701-fb1a-48b4-b8a8-71c004994da9" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C309B-A406-4F09-B9ED-A6A4D616E23D}"/>
 </file>
--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30317"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\JFC\04_Software\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ADFC0594-0FAF-4F96-9C6F-90C20928A5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7138E96E-2F5F-463F-811E-A68081B52E70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="385">
   <si>
     <t>Category</t>
   </si>
@@ -608,9 +608,6 @@
   </si>
   <si>
     <t>Fire Equipment Identification Sign</t>
-  </si>
-  <si>
-    <t>Cross-Category Counter</t>
   </si>
   <si>
     <t>Extinguishers,Hose Reel Assembly,Hydrants,Hydrant Boosters</t>
@@ -1202,7 +1199,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1736,17 +1733,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AR102"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="37.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="17" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1802,7 +1799,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="18" customFormat="1">
+    <row r="2" spans="1:31" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A2" s="16">
         <v>1</v>
       </c>
@@ -1840,7 +1837,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:31" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
         <v>1</v>
       </c>
@@ -1878,7 +1875,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:31" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
         <v>1</v>
       </c>
@@ -1901,7 +1898,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:31" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
         <v>1</v>
       </c>
@@ -1924,7 +1921,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:31" s="5" customFormat="1">
+    <row r="6" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A6" s="11">
         <v>1</v>
       </c>
@@ -1945,7 +1942,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:31" s="5" customFormat="1">
+    <row r="7" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A7" s="11">
         <v>1</v>
       </c>
@@ -1966,7 +1963,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:31" s="5" customFormat="1">
+    <row r="8" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A8" s="11">
         <v>1</v>
       </c>
@@ -1990,7 +1987,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:31" s="5" customFormat="1">
+    <row r="9" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A9" s="11">
         <v>1</v>
       </c>
@@ -2011,7 +2008,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:31" s="5" customFormat="1">
+    <row r="10" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A10" s="11">
         <v>1</v>
       </c>
@@ -2032,7 +2029,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:31" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A11" s="17">
         <v>1</v>
       </c>
@@ -2067,7 +2064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:31" s="5" customFormat="1">
+    <row r="12" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A12" s="17">
         <v>1</v>
       </c>
@@ -2114,7 +2111,7 @@
       <c r="AD12" s="12"/>
       <c r="AE12" s="12"/>
     </row>
-    <row r="13" spans="1:31" s="5" customFormat="1">
+    <row r="13" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A13" s="11">
         <v>1</v>
       </c>
@@ -2138,7 +2135,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:31" s="5" customFormat="1">
+    <row r="14" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A14" s="11">
         <v>1</v>
       </c>
@@ -2162,7 +2159,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:31" s="5" customFormat="1">
+    <row r="15" spans="1:31" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A15" s="11">
         <v>1</v>
       </c>
@@ -2186,7 +2183,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:31" s="22" customFormat="1">
+    <row r="16" spans="1:31" s="22" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A16" s="10">
         <v>1</v>
       </c>
@@ -2211,7 +2208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A17" s="25">
         <v>2</v>
       </c>
@@ -2234,7 +2231,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="1" customFormat="1">
+    <row r="18" spans="1:18" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A18" s="25">
         <v>2</v>
       </c>
@@ -2263,7 +2260,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="5" customFormat="1">
+    <row r="19" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="25">
         <v>2</v>
       </c>
@@ -2283,7 +2280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="18" customFormat="1">
+    <row r="20" spans="1:18" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="24">
         <v>2</v>
       </c>
@@ -2309,7 +2306,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="5" customFormat="1">
+    <row r="21" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="45">
         <v>2</v>
       </c>
@@ -2332,7 +2329,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="5" customFormat="1">
+    <row r="22" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="25">
         <v>2</v>
       </c>
@@ -2361,7 +2358,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="22" customFormat="1">
+    <row r="23" spans="1:18" s="22" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="26">
         <v>2</v>
       </c>
@@ -2385,7 +2382,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="17">
         <v>3</v>
       </c>
@@ -2411,7 +2408,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="17">
         <v>3</v>
       </c>
@@ -2440,7 +2437,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="18" customFormat="1">
+    <row r="26" spans="1:18" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="24">
         <v>4</v>
       </c>
@@ -2466,7 +2463,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="1" customFormat="1">
+    <row r="27" spans="1:18" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="25">
         <v>4</v>
       </c>
@@ -2483,7 +2480,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="25">
         <v>4</v>
       </c>
@@ -2509,7 +2506,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="23" customFormat="1">
+    <row r="29" spans="1:18" s="23" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="26">
         <v>4</v>
       </c>
@@ -2535,7 +2532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="12" customFormat="1">
+    <row r="30" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="17">
         <v>5</v>
       </c>
@@ -2564,7 +2561,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="12" customFormat="1">
+    <row r="31" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="27">
         <v>5</v>
       </c>
@@ -2593,7 +2590,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="12" customFormat="1">
+    <row r="32" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="27">
         <v>5</v>
       </c>
@@ -2622,7 +2619,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="12" customFormat="1">
+    <row r="33" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="27">
         <v>5</v>
       </c>
@@ -2651,7 +2648,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="12" customFormat="1">
+    <row r="34" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="12">
         <v>5</v>
       </c>
@@ -2674,7 +2671,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="12" customFormat="1">
+    <row r="35" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="12">
         <v>5</v>
       </c>
@@ -2697,7 +2694,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="12" customFormat="1">
+    <row r="36" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="14">
         <v>5</v>
       </c>
@@ -2720,7 +2717,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="5" customFormat="1">
+    <row r="37" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="14">
         <v>5</v>
       </c>
@@ -2743,7 +2740,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="12" customFormat="1">
+    <row r="38" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="14">
         <v>5</v>
       </c>
@@ -2766,7 +2763,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="12" customFormat="1">
+    <row r="39" spans="1:18" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="14">
         <v>5</v>
       </c>
@@ -2789,7 +2786,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="17">
         <v>5</v>
       </c>
@@ -2815,7 +2812,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="17">
         <v>5</v>
       </c>
@@ -2838,7 +2835,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="17">
         <v>5</v>
       </c>
@@ -2864,7 +2861,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="5" customFormat="1">
+    <row r="43" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="17">
         <v>5</v>
       </c>
@@ -2887,7 +2884,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="5" customFormat="1">
+    <row r="44" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="17">
         <v>5</v>
       </c>
@@ -2910,7 +2907,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="5" customFormat="1">
+    <row r="45" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="17">
         <v>5</v>
       </c>
@@ -2930,7 +2927,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="17">
         <v>5</v>
       </c>
@@ -2953,7 +2950,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="5" customFormat="1">
+    <row r="47" spans="1:18" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="17">
         <v>5</v>
       </c>
@@ -2973,7 +2970,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="18" customFormat="1">
+    <row r="48" spans="1:18" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="24">
         <v>6</v>
       </c>
@@ -3002,7 +2999,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="1:44" s="12" customFormat="1">
+    <row r="49" spans="1:44" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="25">
         <v>6</v>
       </c>
@@ -3043,7 +3040,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:44" s="5" customFormat="1">
+    <row r="50" spans="1:44" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="25">
         <v>6</v>
       </c>
@@ -3063,7 +3060,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="51" spans="1:44" s="5" customFormat="1">
+    <row r="51" spans="1:44" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="25">
         <v>6</v>
       </c>
@@ -3086,7 +3083,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="52" spans="1:44" s="21" customFormat="1">
+    <row r="52" spans="1:44" s="21" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="26">
         <v>6</v>
       </c>
@@ -3112,7 +3109,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="53" spans="1:44" s="5" customFormat="1">
+    <row r="53" spans="1:44" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="10">
         <v>6</v>
       </c>
@@ -3129,7 +3126,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="54" spans="1:44">
+    <row r="54" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="17">
         <v>7</v>
       </c>
@@ -3152,7 +3149,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="55" spans="1:44">
+    <row r="55" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A55" s="17">
         <v>7</v>
       </c>
@@ -3178,7 +3175,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="56" spans="1:44">
+    <row r="56" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A56" s="17">
         <v>7</v>
       </c>
@@ -3204,7 +3201,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:44" s="18" customFormat="1">
+    <row r="57" spans="1:44" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A57" s="24">
         <v>8</v>
       </c>
@@ -3231,7 +3228,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="58" spans="1:44" s="12" customFormat="1">
+    <row r="58" spans="1:44" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A58" s="25">
         <v>8</v>
       </c>
@@ -3254,7 +3251,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="59" spans="1:44" s="21" customFormat="1">
+    <row r="59" spans="1:44" s="21" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A59" s="26">
         <v>8</v>
       </c>
@@ -3314,7 +3311,7 @@
       <c r="AQ59" s="22"/>
       <c r="AR59" s="22"/>
     </row>
-    <row r="60" spans="1:44">
+    <row r="60" spans="1:44" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A60" s="17">
         <v>9</v>
       </c>
@@ -3340,7 +3337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="61" spans="1:44" s="1" customFormat="1">
+    <row r="61" spans="1:44" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A61" s="30">
         <v>9</v>
       </c>
@@ -3360,13 +3357,13 @@
         <v>185</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="62" spans="1:44" s="1" customFormat="1">
+    <row r="62" spans="1:44" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A62" s="30">
         <v>9</v>
       </c>
@@ -3386,154 +3383,154 @@
         <v>189</v>
       </c>
       <c r="G62" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q62" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="Q62" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="63" spans="1:44" s="29" customFormat="1">
+    </row>
+    <row r="63" spans="1:44" s="29" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A63" s="24">
         <v>10</v>
       </c>
       <c r="B63" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="D63" s="29" t="s">
         <v>192</v>
-      </c>
-      <c r="D63" s="29" t="s">
-        <v>193</v>
       </c>
       <c r="G63" s="29" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="64" spans="1:44" s="5" customFormat="1">
+    <row r="64" spans="1:44" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A64" s="25">
         <v>10</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G64" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="65" spans="1:10" s="5" customFormat="1">
+    <row r="65" spans="1:10" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A65" s="25">
         <v>10</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="66" spans="1:10" s="5" customFormat="1">
+    <row r="66" spans="1:10" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A66" s="25">
         <v>10</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="67" spans="1:10" s="22" customFormat="1">
+    <row r="67" spans="1:10" s="22" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A67" s="26">
         <v>10</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G67" s="22" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:10"/>
-    <row r="70" spans="1:10">
+    <row r="68" spans="1:10" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="70" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
+        <v>197</v>
+      </c>
+      <c r="G70" t="s">
         <v>198</v>
       </c>
-      <c r="G70" t="s">
+    </row>
+    <row r="71" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B71" t="s">
         <v>199</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10">
-      <c r="B71" t="s">
-        <v>200</v>
       </c>
       <c r="G71" s="1"/>
       <c r="I71" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B72" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10">
-      <c r="B72" t="s">
-        <v>202</v>
       </c>
       <c r="G72" s="3"/>
       <c r="I72" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="B73" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10">
-      <c r="B73" t="s">
-        <v>204</v>
       </c>
       <c r="G73" s="31"/>
       <c r="I73" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="J73" s="32"/>
+    </row>
+    <row r="74" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B74" t="s">
         <v>205</v>
-      </c>
-      <c r="J73" s="32"/>
-    </row>
-    <row r="74" spans="1:10" ht="14.45" customHeight="1">
-      <c r="B74" t="s">
-        <v>206</v>
       </c>
       <c r="G74" s="33"/>
       <c r="I74" s="32" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="J74" s="32"/>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G75" s="34"/>
       <c r="I75" s="32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="J75" s="32"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" ht="14.5" x14ac:dyDescent="0.35">
       <c r="G76" s="6"/>
       <c r="I76" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="77" spans="1:10"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="14.5" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="14.5" x14ac:dyDescent="0.35"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R67">
     <sortCondition ref="A2:A67"/>
@@ -3545,145 +3542,145 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H97"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>209</v>
+      </c>
+      <c r="B1" t="s">
         <v>210</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>211</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>212</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>213</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>214</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>215</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>216</v>
       </c>
-      <c r="H1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>151</v>
       </c>
       <c r="B2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C2" t="s">
         <v>218</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>219</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>220</v>
-      </c>
-      <c r="E2" t="s">
-        <v>221</v>
       </c>
       <c r="F2">
         <v>21</v>
       </c>
       <c r="G2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" t="s">
         <v>222</v>
       </c>
-      <c r="H2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>151</v>
       </c>
       <c r="B3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C3" t="s">
         <v>218</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>219</v>
       </c>
-      <c r="D3" t="s">
-        <v>220</v>
-      </c>
       <c r="E3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3" t="s">
+        <v>221</v>
+      </c>
+      <c r="H3" t="s">
         <v>222</v>
       </c>
-      <c r="H3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>151</v>
       </c>
       <c r="B4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" t="s">
         <v>218</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>219</v>
       </c>
-      <c r="D4" t="s">
-        <v>220</v>
-      </c>
       <c r="E4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F4">
         <v>9</v>
       </c>
       <c r="G4" t="s">
+        <v>221</v>
+      </c>
+      <c r="H4" t="s">
         <v>222</v>
       </c>
-      <c r="H4" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>151</v>
       </c>
       <c r="B5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C5" t="s">
         <v>28</v>
       </c>
       <c r="D5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
       </c>
-      <c r="E5" t="s">
-        <v>226</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>227</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>228</v>
       </c>
-      <c r="H5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>151</v>
       </c>
@@ -3691,25 +3688,25 @@
         <v>152</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>230</v>
+      </c>
+      <c r="H6" t="s">
         <v>231</v>
       </c>
-      <c r="H6" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>151</v>
       </c>
@@ -3717,25 +3714,25 @@
         <v>152</v>
       </c>
       <c r="C7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" t="s">
         <v>233</v>
       </c>
-      <c r="D7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E7" t="s">
-        <v>226</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>227</v>
+      </c>
+      <c r="H7" t="s">
         <v>234</v>
       </c>
-      <c r="G7" t="s">
-        <v>228</v>
-      </c>
-      <c r="H7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>151</v>
       </c>
@@ -3743,103 +3740,103 @@
         <v>152</v>
       </c>
       <c r="C8" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" t="s">
         <v>236</v>
       </c>
-      <c r="D8" t="s">
-        <v>226</v>
-      </c>
-      <c r="E8" t="s">
-        <v>226</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>227</v>
+      </c>
+      <c r="H8" t="s">
         <v>237</v>
       </c>
-      <c r="G8" t="s">
-        <v>228</v>
-      </c>
-      <c r="H8" t="s">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
+      <c r="B9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C9" t="s">
         <v>239</v>
       </c>
-      <c r="B9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C9" t="s">
-        <v>240</v>
-      </c>
       <c r="D9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F9">
         <v>400</v>
       </c>
       <c r="G9" t="s">
+        <v>240</v>
+      </c>
+      <c r="H9" t="s">
         <v>241</v>
       </c>
-      <c r="H9" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C10" t="s">
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F10" t="s">
+        <v>242</v>
+      </c>
+      <c r="G10" t="s">
+        <v>227</v>
+      </c>
+      <c r="H10" t="s">
         <v>243</v>
       </c>
-      <c r="G10" t="s">
-        <v>228</v>
-      </c>
-      <c r="H10" t="s">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>245</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>225</v>
+      </c>
+      <c r="E11" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" t="s">
         <v>246</v>
       </c>
-      <c r="D11" t="s">
-        <v>226</v>
-      </c>
-      <c r="E11" t="s">
-        <v>226</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>227</v>
+      </c>
+      <c r="H11" t="s">
         <v>247</v>
       </c>
-      <c r="G11" t="s">
-        <v>228</v>
-      </c>
-      <c r="H11" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>26</v>
       </c>
@@ -3847,25 +3844,25 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F12">
         <v>104.04</v>
       </c>
       <c r="G12" t="s">
+        <v>249</v>
+      </c>
+      <c r="H12" t="s">
         <v>250</v>
       </c>
-      <c r="H12" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>26</v>
       </c>
@@ -3873,25 +3870,25 @@
         <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E13" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F13">
         <v>51.84</v>
       </c>
       <c r="G13" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H13" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3899,195 +3896,195 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14" t="s">
+        <v>252</v>
+      </c>
+      <c r="H14" t="s">
         <v>253</v>
       </c>
-      <c r="H14" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>26</v>
       </c>
       <c r="B15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C15" t="s">
         <v>255</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E15" t="s">
+        <v>225</v>
+      </c>
+      <c r="F15" t="s">
         <v>256</v>
       </c>
-      <c r="D15" t="s">
-        <v>226</v>
-      </c>
-      <c r="E15" t="s">
-        <v>226</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>227</v>
+      </c>
+      <c r="H15" t="s">
         <v>257</v>
       </c>
-      <c r="G15" t="s">
-        <v>228</v>
-      </c>
-      <c r="H15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>26</v>
       </c>
       <c r="B16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C16" t="s">
+        <v>255</v>
+      </c>
+      <c r="D16" t="s">
+        <v>225</v>
+      </c>
+      <c r="E16" t="s">
+        <v>225</v>
+      </c>
+      <c r="F16" t="s">
         <v>259</v>
       </c>
-      <c r="C16" t="s">
-        <v>256</v>
-      </c>
-      <c r="D16" t="s">
-        <v>226</v>
-      </c>
-      <c r="E16" t="s">
-        <v>226</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>227</v>
+      </c>
+      <c r="H16" t="s">
         <v>260</v>
       </c>
-      <c r="G16" t="s">
-        <v>228</v>
-      </c>
-      <c r="H16" t="s">
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" t="s">
+      <c r="B17" t="s">
         <v>262</v>
-      </c>
-      <c r="B17" t="s">
-        <v>263</v>
       </c>
       <c r="C17" t="s">
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F17" t="s">
+        <v>263</v>
+      </c>
+      <c r="G17" t="s">
+        <v>227</v>
+      </c>
+      <c r="H17" t="s">
         <v>264</v>
       </c>
-      <c r="G17" t="s">
-        <v>228</v>
-      </c>
-      <c r="H17" t="s">
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>261</v>
+      </c>
+      <c r="B18" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" t="s">
+      <c r="D18" t="s">
+        <v>219</v>
+      </c>
+      <c r="E18" t="s">
+        <v>266</v>
+      </c>
+      <c r="F18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" t="s">
+        <v>268</v>
+      </c>
+      <c r="H18" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>261</v>
+      </c>
+      <c r="B19" t="s">
         <v>262</v>
       </c>
-      <c r="B18" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" t="s">
-        <v>266</v>
-      </c>
-      <c r="D18" t="s">
-        <v>220</v>
-      </c>
-      <c r="E18" t="s">
-        <v>267</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="C19" t="s">
+        <v>265</v>
+      </c>
+      <c r="D19" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" t="s">
+        <v>270</v>
+      </c>
+      <c r="F19" t="s">
+        <v>271</v>
+      </c>
+      <c r="G19" t="s">
         <v>268</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H19" t="s">
         <v>269</v>
       </c>
-      <c r="H18" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>261</v>
+      </c>
+      <c r="B20" t="s">
         <v>262</v>
       </c>
-      <c r="B19" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" t="s">
-        <v>266</v>
-      </c>
-      <c r="D19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="C20" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" t="s">
+        <v>219</v>
+      </c>
+      <c r="E20" t="s">
+        <v>272</v>
+      </c>
+      <c r="F20" t="s">
         <v>271</v>
       </c>
-      <c r="F19" t="s">
-        <v>272</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="G20" t="s">
+        <v>268</v>
+      </c>
+      <c r="H20" t="s">
         <v>269</v>
       </c>
-      <c r="H19" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" t="s">
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B21" t="s">
         <v>262</v>
       </c>
-      <c r="B20" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" t="s">
-        <v>266</v>
-      </c>
-      <c r="D20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="C21" t="s">
         <v>273</v>
       </c>
-      <c r="F20" t="s">
-        <v>272</v>
-      </c>
-      <c r="G20" t="s">
-        <v>269</v>
-      </c>
-      <c r="H20" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
-      <c r="A21" t="s">
-        <v>262</v>
-      </c>
-      <c r="B21" t="s">
-        <v>263</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>274</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>275</v>
-      </c>
-      <c r="E21" t="s">
-        <v>276</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4096,24 +4093,24 @@
         <v>105</v>
       </c>
       <c r="H21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>261</v>
+      </c>
+      <c r="B22" t="s">
+        <v>262</v>
+      </c>
+      <c r="C22" t="s">
+        <v>273</v>
+      </c>
+      <c r="D22" t="s">
+        <v>274</v>
+      </c>
+      <c r="E22" t="s">
         <v>277</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" t="s">
-        <v>262</v>
-      </c>
-      <c r="B22" t="s">
-        <v>263</v>
-      </c>
-      <c r="C22" t="s">
-        <v>274</v>
-      </c>
-      <c r="D22" t="s">
-        <v>275</v>
-      </c>
-      <c r="E22" t="s">
-        <v>278</v>
       </c>
       <c r="F22">
         <v>300</v>
@@ -4122,24 +4119,24 @@
         <v>105</v>
       </c>
       <c r="H22" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>261</v>
+      </c>
+      <c r="B23" t="s">
         <v>262</v>
       </c>
-      <c r="B23" t="s">
-        <v>263</v>
-      </c>
       <c r="C23" t="s">
+        <v>273</v>
+      </c>
+      <c r="D23" t="s">
         <v>274</v>
       </c>
-      <c r="D23" t="s">
-        <v>275</v>
-      </c>
       <c r="E23" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F23">
         <v>450</v>
@@ -4148,24 +4145,24 @@
         <v>105</v>
       </c>
       <c r="H23" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>261</v>
+      </c>
+      <c r="B24" t="s">
         <v>262</v>
       </c>
-      <c r="B24" t="s">
-        <v>263</v>
-      </c>
       <c r="C24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D24" t="s">
         <v>274</v>
       </c>
-      <c r="D24" t="s">
-        <v>275</v>
-      </c>
       <c r="E24" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F24">
         <v>675</v>
@@ -4174,24 +4171,24 @@
         <v>105</v>
       </c>
       <c r="H24" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" t="s">
         <v>262</v>
       </c>
-      <c r="B25" t="s">
-        <v>263</v>
-      </c>
       <c r="C25" t="s">
+        <v>273</v>
+      </c>
+      <c r="D25" t="s">
         <v>274</v>
       </c>
-      <c r="D25" t="s">
-        <v>275</v>
-      </c>
       <c r="E25" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4200,24 +4197,24 @@
         <v>105</v>
       </c>
       <c r="H25" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>261</v>
+      </c>
+      <c r="B26" t="s">
         <v>262</v>
       </c>
-      <c r="B26" t="s">
-        <v>263</v>
-      </c>
       <c r="C26" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" t="s">
         <v>274</v>
       </c>
-      <c r="D26" t="s">
-        <v>275</v>
-      </c>
       <c r="E26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F26">
         <v>300</v>
@@ -4226,24 +4223,24 @@
         <v>105</v>
       </c>
       <c r="H26" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" t="s">
         <v>262</v>
       </c>
-      <c r="B27" t="s">
-        <v>263</v>
-      </c>
       <c r="C27" t="s">
+        <v>273</v>
+      </c>
+      <c r="D27" t="s">
         <v>274</v>
       </c>
-      <c r="D27" t="s">
-        <v>275</v>
-      </c>
       <c r="E27" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F27">
         <v>450</v>
@@ -4252,24 +4249,24 @@
         <v>105</v>
       </c>
       <c r="H27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>261</v>
+      </c>
+      <c r="B28" t="s">
         <v>262</v>
       </c>
-      <c r="B28" t="s">
-        <v>263</v>
-      </c>
       <c r="C28" t="s">
+        <v>273</v>
+      </c>
+      <c r="D28" t="s">
         <v>274</v>
       </c>
-      <c r="D28" t="s">
-        <v>275</v>
-      </c>
       <c r="E28" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F28">
         <v>675</v>
@@ -4278,24 +4275,24 @@
         <v>105</v>
       </c>
       <c r="H28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" t="s">
         <v>262</v>
       </c>
-      <c r="B29" t="s">
-        <v>263</v>
-      </c>
       <c r="C29" t="s">
+        <v>273</v>
+      </c>
+      <c r="D29" t="s">
         <v>274</v>
       </c>
-      <c r="D29" t="s">
-        <v>275</v>
-      </c>
       <c r="E29" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F29">
         <v>150</v>
@@ -4304,24 +4301,24 @@
         <v>105</v>
       </c>
       <c r="H29" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B30" t="s">
         <v>262</v>
       </c>
-      <c r="B30" t="s">
-        <v>263</v>
-      </c>
       <c r="C30" t="s">
+        <v>273</v>
+      </c>
+      <c r="D30" t="s">
         <v>274</v>
       </c>
-      <c r="D30" t="s">
-        <v>275</v>
-      </c>
       <c r="E30" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F30">
         <v>200</v>
@@ -4330,24 +4327,24 @@
         <v>105</v>
       </c>
       <c r="H30" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>261</v>
+      </c>
+      <c r="B31" t="s">
         <v>262</v>
       </c>
-      <c r="B31" t="s">
-        <v>263</v>
-      </c>
       <c r="C31" t="s">
+        <v>273</v>
+      </c>
+      <c r="D31" t="s">
         <v>274</v>
       </c>
-      <c r="D31" t="s">
-        <v>275</v>
-      </c>
       <c r="E31" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F31">
         <v>300</v>
@@ -4356,24 +4353,24 @@
         <v>105</v>
       </c>
       <c r="H31" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>261</v>
+      </c>
+      <c r="B32" t="s">
         <v>262</v>
       </c>
-      <c r="B32" t="s">
-        <v>263</v>
-      </c>
       <c r="C32" t="s">
+        <v>273</v>
+      </c>
+      <c r="D32" t="s">
         <v>274</v>
       </c>
-      <c r="D32" t="s">
-        <v>275</v>
-      </c>
       <c r="E32" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F32">
         <v>450</v>
@@ -4382,24 +4379,24 @@
         <v>105</v>
       </c>
       <c r="H32" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>261</v>
+      </c>
+      <c r="B33" t="s">
         <v>262</v>
       </c>
-      <c r="B33" t="s">
-        <v>263</v>
-      </c>
       <c r="C33" t="s">
+        <v>273</v>
+      </c>
+      <c r="D33" t="s">
         <v>274</v>
       </c>
-      <c r="D33" t="s">
-        <v>275</v>
-      </c>
       <c r="E33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F33">
         <v>675</v>
@@ -4408,24 +4405,24 @@
         <v>105</v>
       </c>
       <c r="H33" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>261</v>
+      </c>
+      <c r="B34" t="s">
         <v>262</v>
       </c>
-      <c r="B34" t="s">
-        <v>263</v>
-      </c>
       <c r="C34" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D34" t="s">
+        <v>274</v>
+      </c>
+      <c r="E34" t="s">
         <v>275</v>
-      </c>
-      <c r="E34" t="s">
-        <v>276</v>
       </c>
       <c r="F34">
         <v>150</v>
@@ -4434,24 +4431,24 @@
         <v>105</v>
       </c>
       <c r="H34" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>261</v>
+      </c>
+      <c r="B35" t="s">
+        <v>262</v>
+      </c>
+      <c r="C35" t="s">
+        <v>289</v>
+      </c>
+      <c r="D35" t="s">
+        <v>274</v>
+      </c>
+      <c r="E35" t="s">
         <v>277</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
-      <c r="A35" t="s">
-        <v>262</v>
-      </c>
-      <c r="B35" t="s">
-        <v>263</v>
-      </c>
-      <c r="C35" t="s">
-        <v>290</v>
-      </c>
-      <c r="D35" t="s">
-        <v>275</v>
-      </c>
-      <c r="E35" t="s">
-        <v>278</v>
       </c>
       <c r="F35">
         <v>450</v>
@@ -4460,24 +4457,24 @@
         <v>105</v>
       </c>
       <c r="H35" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" t="s">
         <v>262</v>
       </c>
-      <c r="B36" t="s">
-        <v>263</v>
-      </c>
       <c r="C36" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D36" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E36" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F36">
         <v>675</v>
@@ -4486,24 +4483,24 @@
         <v>105</v>
       </c>
       <c r="H36" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" t="s">
         <v>262</v>
       </c>
-      <c r="B37" t="s">
-        <v>263</v>
-      </c>
       <c r="C37" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E37" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F37">
         <v>1000</v>
@@ -4512,24 +4509,24 @@
         <v>105</v>
       </c>
       <c r="H37" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>261</v>
+      </c>
+      <c r="B38" t="s">
         <v>262</v>
       </c>
-      <c r="B38" t="s">
-        <v>263</v>
-      </c>
       <c r="C38" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D38" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F38">
         <v>150</v>
@@ -4538,24 +4535,24 @@
         <v>105</v>
       </c>
       <c r="H38" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>261</v>
+      </c>
+      <c r="B39" t="s">
         <v>262</v>
       </c>
-      <c r="B39" t="s">
-        <v>263</v>
-      </c>
       <c r="C39" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D39" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E39" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F39">
         <v>450</v>
@@ -4564,24 +4561,24 @@
         <v>105</v>
       </c>
       <c r="H39" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>261</v>
+      </c>
+      <c r="B40" t="s">
         <v>262</v>
       </c>
-      <c r="B40" t="s">
-        <v>263</v>
-      </c>
       <c r="C40" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E40" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="F40">
         <v>675</v>
@@ -4590,24 +4587,24 @@
         <v>105</v>
       </c>
       <c r="H40" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>261</v>
+      </c>
+      <c r="B41" t="s">
         <v>262</v>
       </c>
-      <c r="B41" t="s">
-        <v>263</v>
-      </c>
       <c r="C41" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D41" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E41" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F41">
         <v>1000</v>
@@ -4616,24 +4613,24 @@
         <v>105</v>
       </c>
       <c r="H41" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>261</v>
+      </c>
+      <c r="B42" t="s">
         <v>262</v>
       </c>
-      <c r="B42" t="s">
-        <v>263</v>
-      </c>
       <c r="C42" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E42" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F42">
         <v>225</v>
@@ -4642,24 +4639,24 @@
         <v>105</v>
       </c>
       <c r="H42" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>261</v>
+      </c>
+      <c r="B43" t="s">
         <v>262</v>
       </c>
-      <c r="B43" t="s">
-        <v>263</v>
-      </c>
       <c r="C43" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D43" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E43" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F43">
         <v>300</v>
@@ -4668,24 +4665,24 @@
         <v>105</v>
       </c>
       <c r="H43" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" t="s">
         <v>262</v>
       </c>
-      <c r="B44" t="s">
-        <v>263</v>
-      </c>
       <c r="C44" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E44" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F44">
         <v>450</v>
@@ -4694,24 +4691,24 @@
         <v>105</v>
       </c>
       <c r="H44" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>261</v>
+      </c>
+      <c r="B45" t="s">
         <v>262</v>
       </c>
-      <c r="B45" t="s">
-        <v>263</v>
-      </c>
       <c r="C45" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D45" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E45" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="F45">
         <v>675</v>
@@ -4720,24 +4717,24 @@
         <v>105</v>
       </c>
       <c r="H45" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>261</v>
+      </c>
+      <c r="B46" t="s">
         <v>262</v>
       </c>
-      <c r="B46" t="s">
-        <v>263</v>
-      </c>
       <c r="C46" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D46" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E46" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F46">
         <v>1000</v>
@@ -4746,102 +4743,102 @@
         <v>105</v>
       </c>
       <c r="H46" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>261</v>
+      </c>
+      <c r="B47" t="s">
         <v>262</v>
       </c>
-      <c r="B47" t="s">
-        <v>263</v>
-      </c>
       <c r="C47" t="s">
+        <v>290</v>
+      </c>
+      <c r="D47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E47" t="s">
+        <v>266</v>
+      </c>
+      <c r="F47" t="s">
         <v>291</v>
       </c>
-      <c r="D47" t="s">
-        <v>220</v>
-      </c>
-      <c r="E47" t="s">
-        <v>267</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
+        <v>268</v>
+      </c>
+      <c r="H47" t="s">
         <v>292</v>
       </c>
-      <c r="G47" t="s">
-        <v>269</v>
-      </c>
-      <c r="H47" t="s">
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>261</v>
+      </c>
+      <c r="B48" t="s">
+        <v>262</v>
+      </c>
+      <c r="C48" t="s">
+        <v>290</v>
+      </c>
+      <c r="D48" t="s">
+        <v>219</v>
+      </c>
+      <c r="E48" t="s">
+        <v>270</v>
+      </c>
+      <c r="F48" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="A48" t="s">
+      <c r="G48" t="s">
+        <v>268</v>
+      </c>
+      <c r="H48" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" t="s">
         <v>262</v>
       </c>
-      <c r="B48" t="s">
-        <v>263</v>
-      </c>
-      <c r="C48" t="s">
-        <v>291</v>
-      </c>
-      <c r="D48" t="s">
-        <v>220</v>
-      </c>
-      <c r="E48" t="s">
-        <v>271</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="C49" t="s">
+        <v>290</v>
+      </c>
+      <c r="D49" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" t="s">
+        <v>272</v>
+      </c>
+      <c r="F49" t="s">
         <v>294</v>
       </c>
-      <c r="G48" t="s">
-        <v>269</v>
-      </c>
-      <c r="H48" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
-      <c r="A49" t="s">
+      <c r="G49" t="s">
+        <v>268</v>
+      </c>
+      <c r="H49" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>261</v>
+      </c>
+      <c r="B50" t="s">
         <v>262</v>
       </c>
-      <c r="B49" t="s">
-        <v>263</v>
-      </c>
-      <c r="C49" t="s">
-        <v>291</v>
-      </c>
-      <c r="D49" t="s">
-        <v>220</v>
-      </c>
-      <c r="E49" t="s">
-        <v>273</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="C50" t="s">
         <v>295</v>
       </c>
-      <c r="G49" t="s">
-        <v>269</v>
-      </c>
-      <c r="H49" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8">
-      <c r="A50" t="s">
-        <v>262</v>
-      </c>
-      <c r="B50" t="s">
-        <v>263</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
+        <v>274</v>
+      </c>
+      <c r="E50" t="s">
         <v>296</v>
-      </c>
-      <c r="D50" t="s">
-        <v>275</v>
-      </c>
-      <c r="E50" t="s">
-        <v>297</v>
       </c>
       <c r="F50">
         <v>15</v>
@@ -4850,24 +4847,24 @@
         <v>105</v>
       </c>
       <c r="H50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>261</v>
+      </c>
+      <c r="B51" t="s">
+        <v>262</v>
+      </c>
+      <c r="C51" t="s">
+        <v>295</v>
+      </c>
+      <c r="D51" t="s">
+        <v>274</v>
+      </c>
+      <c r="E51" t="s">
         <v>298</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8">
-      <c r="A51" t="s">
-        <v>262</v>
-      </c>
-      <c r="B51" t="s">
-        <v>263</v>
-      </c>
-      <c r="C51" t="s">
-        <v>296</v>
-      </c>
-      <c r="D51" t="s">
-        <v>275</v>
-      </c>
-      <c r="E51" t="s">
-        <v>299</v>
       </c>
       <c r="F51">
         <v>45</v>
@@ -4876,24 +4873,24 @@
         <v>105</v>
       </c>
       <c r="H51" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>261</v>
+      </c>
+      <c r="B52" t="s">
         <v>262</v>
       </c>
-      <c r="B52" t="s">
-        <v>263</v>
-      </c>
       <c r="C52" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E52" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F52">
         <v>80</v>
@@ -4902,24 +4899,24 @@
         <v>105</v>
       </c>
       <c r="H52" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>261</v>
+      </c>
+      <c r="B53" t="s">
         <v>262</v>
       </c>
-      <c r="B53" t="s">
-        <v>263</v>
-      </c>
       <c r="C53" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D53" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E53" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F53">
         <v>80</v>
@@ -4928,24 +4925,24 @@
         <v>105</v>
       </c>
       <c r="H53" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>261</v>
+      </c>
+      <c r="B54" t="s">
         <v>262</v>
       </c>
-      <c r="B54" t="s">
-        <v>263</v>
-      </c>
       <c r="C54" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D54" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E54" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F54">
         <v>115</v>
@@ -4954,24 +4951,24 @@
         <v>105</v>
       </c>
       <c r="H54" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" t="s">
         <v>262</v>
       </c>
-      <c r="B55" t="s">
-        <v>263</v>
-      </c>
       <c r="C55" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D55" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E55" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F55">
         <v>150</v>
@@ -4980,24 +4977,24 @@
         <v>105</v>
       </c>
       <c r="H55" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>261</v>
+      </c>
+      <c r="B56" t="s">
         <v>262</v>
       </c>
-      <c r="B56" t="s">
-        <v>263</v>
-      </c>
       <c r="C56" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D56" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F56">
         <v>150</v>
@@ -5006,24 +5003,24 @@
         <v>105</v>
       </c>
       <c r="H56" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>261</v>
+      </c>
+      <c r="B57" t="s">
         <v>262</v>
       </c>
-      <c r="B57" t="s">
-        <v>263</v>
-      </c>
       <c r="C57" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E57" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F57">
         <v>225</v>
@@ -5032,24 +5029,24 @@
         <v>105</v>
       </c>
       <c r="H57" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>261</v>
+      </c>
+      <c r="B58" t="s">
         <v>262</v>
       </c>
-      <c r="B58" t="s">
-        <v>263</v>
-      </c>
       <c r="C58" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D58" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E58" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F58">
         <v>300</v>
@@ -5058,24 +5055,24 @@
         <v>105</v>
       </c>
       <c r="H58" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>261</v>
+      </c>
+      <c r="B59" t="s">
         <v>262</v>
       </c>
-      <c r="B59" t="s">
-        <v>263</v>
-      </c>
       <c r="C59" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D59" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E59" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F59">
         <v>80</v>
@@ -5084,24 +5081,24 @@
         <v>105</v>
       </c>
       <c r="H59" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>261</v>
+      </c>
+      <c r="B60" t="s">
         <v>262</v>
       </c>
-      <c r="B60" t="s">
-        <v>263</v>
-      </c>
       <c r="C60" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E60" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F60">
         <v>115</v>
@@ -5110,24 +5107,24 @@
         <v>105</v>
       </c>
       <c r="H60" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>261</v>
+      </c>
+      <c r="B61" t="s">
         <v>262</v>
       </c>
-      <c r="B61" t="s">
-        <v>263</v>
-      </c>
       <c r="C61" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D61" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E61" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F61">
         <v>150</v>
@@ -5136,24 +5133,24 @@
         <v>105</v>
       </c>
       <c r="H61" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>261</v>
+      </c>
+      <c r="B62" t="s">
         <v>262</v>
       </c>
-      <c r="B62" t="s">
-        <v>263</v>
-      </c>
       <c r="C62" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D62" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E62" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F62">
         <v>150</v>
@@ -5162,24 +5159,24 @@
         <v>105</v>
       </c>
       <c r="H62" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" t="s">
         <v>262</v>
       </c>
-      <c r="B63" t="s">
-        <v>263</v>
-      </c>
       <c r="C63" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D63" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E63" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F63">
         <v>225</v>
@@ -5188,24 +5185,24 @@
         <v>105</v>
       </c>
       <c r="H63" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" t="s">
         <v>262</v>
       </c>
-      <c r="B64" t="s">
-        <v>263</v>
-      </c>
       <c r="C64" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D64" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E64" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F64">
         <v>300</v>
@@ -5214,24 +5211,24 @@
         <v>105</v>
       </c>
       <c r="H64" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>261</v>
+      </c>
+      <c r="B65" t="s">
         <v>262</v>
       </c>
-      <c r="B65" t="s">
-        <v>263</v>
-      </c>
       <c r="C65" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D65" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E65" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F65">
         <v>150</v>
@@ -5240,24 +5237,24 @@
         <v>105</v>
       </c>
       <c r="H65" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>261</v>
+      </c>
+      <c r="B66" t="s">
         <v>262</v>
       </c>
-      <c r="B66" t="s">
-        <v>263</v>
-      </c>
       <c r="C66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E66" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F66">
         <v>225</v>
@@ -5266,24 +5263,24 @@
         <v>105</v>
       </c>
       <c r="H66" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>261</v>
+      </c>
+      <c r="B67" t="s">
         <v>262</v>
       </c>
-      <c r="B67" t="s">
-        <v>263</v>
-      </c>
       <c r="C67" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E67" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F67">
         <v>300</v>
@@ -5292,712 +5289,712 @@
         <v>105</v>
       </c>
       <c r="H67" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>261</v>
+      </c>
+      <c r="B68" t="s">
+        <v>262</v>
+      </c>
+      <c r="C68" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
-      <c r="A68" t="s">
-        <v>262</v>
-      </c>
-      <c r="B68" t="s">
-        <v>263</v>
-      </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
+        <v>274</v>
+      </c>
+      <c r="E68" t="s">
+        <v>296</v>
+      </c>
+      <c r="F68" t="s">
         <v>309</v>
-      </c>
-      <c r="D68" t="s">
-        <v>275</v>
-      </c>
-      <c r="E68" t="s">
-        <v>297</v>
-      </c>
-      <c r="F68" t="s">
-        <v>310</v>
       </c>
       <c r="G68" t="s">
         <v>42</v>
       </c>
       <c r="H68" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>261</v>
+      </c>
+      <c r="B69" t="s">
+        <v>262</v>
+      </c>
+      <c r="C69" t="s">
+        <v>308</v>
+      </c>
+      <c r="D69" t="s">
+        <v>274</v>
+      </c>
+      <c r="E69" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="69" spans="1:8">
-      <c r="A69" t="s">
-        <v>262</v>
-      </c>
-      <c r="B69" t="s">
-        <v>263</v>
-      </c>
-      <c r="C69" t="s">
-        <v>309</v>
-      </c>
-      <c r="D69" t="s">
-        <v>275</v>
-      </c>
-      <c r="E69" t="s">
-        <v>299</v>
-      </c>
       <c r="F69" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G69" t="s">
         <v>42</v>
       </c>
       <c r="H69" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>261</v>
+      </c>
+      <c r="B70" t="s">
         <v>262</v>
       </c>
-      <c r="B70" t="s">
-        <v>263</v>
-      </c>
       <c r="C70" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E70" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F70" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G70" t="s">
         <v>42</v>
       </c>
       <c r="H70" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>261</v>
+      </c>
+      <c r="B71" t="s">
         <v>262</v>
       </c>
-      <c r="B71" t="s">
-        <v>263</v>
-      </c>
       <c r="C71" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D71" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F71" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="G71" t="s">
         <v>42</v>
       </c>
       <c r="H71" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>261</v>
+      </c>
+      <c r="B72" t="s">
         <v>262</v>
       </c>
-      <c r="B72" t="s">
-        <v>263</v>
-      </c>
       <c r="C72" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D72" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E72" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F72" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="G72" t="s">
         <v>42</v>
       </c>
       <c r="H72" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>261</v>
+      </c>
+      <c r="B73" t="s">
         <v>262</v>
       </c>
-      <c r="B73" t="s">
-        <v>263</v>
-      </c>
       <c r="C73" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E73" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F73" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G73" t="s">
         <v>42</v>
       </c>
       <c r="H73" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>261</v>
+      </c>
+      <c r="B74" t="s">
         <v>262</v>
       </c>
-      <c r="B74" t="s">
-        <v>263</v>
-      </c>
       <c r="C74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D74" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F74" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="G74" t="s">
         <v>42</v>
       </c>
       <c r="H74" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>261</v>
+      </c>
+      <c r="B75" t="s">
         <v>262</v>
       </c>
-      <c r="B75" t="s">
-        <v>263</v>
-      </c>
       <c r="C75" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E75" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F75" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="G75" t="s">
         <v>42</v>
       </c>
       <c r="H75" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>261</v>
+      </c>
+      <c r="B76" t="s">
         <v>262</v>
       </c>
-      <c r="B76" t="s">
-        <v>263</v>
-      </c>
       <c r="C76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D76" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E76" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F76" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G76" t="s">
         <v>42</v>
       </c>
       <c r="H76" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>318</v>
+      </c>
+      <c r="B77" t="s">
         <v>319</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>320</v>
       </c>
-      <c r="C77" t="s">
-        <v>321</v>
-      </c>
       <c r="D77" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E77" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H77" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>318</v>
+      </c>
+      <c r="B78" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="78" spans="1:8">
-      <c r="A78" t="s">
-        <v>319</v>
-      </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>323</v>
       </c>
-      <c r="C78" t="s">
-        <v>324</v>
-      </c>
       <c r="D78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E78" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
+        <v>324</v>
+      </c>
+      <c r="H78" t="s">
         <v>325</v>
       </c>
-      <c r="H78" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8">
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B79" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C79" t="s">
         <v>28</v>
       </c>
       <c r="D79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E79" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F79" t="s">
+        <v>326</v>
+      </c>
+      <c r="G79" t="s">
+        <v>227</v>
+      </c>
+      <c r="H79" t="s">
         <v>327</v>
       </c>
-      <c r="G79" t="s">
-        <v>228</v>
-      </c>
-      <c r="H79" t="s">
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>318</v>
+      </c>
+      <c r="B80" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="80" spans="1:8">
-      <c r="A80" t="s">
-        <v>319</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>329</v>
       </c>
-      <c r="C80" t="s">
-        <v>330</v>
-      </c>
       <c r="D80" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E80" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H80" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="81" spans="1:8">
-      <c r="A81" t="s">
+      <c r="B81" t="s">
         <v>332</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>333</v>
       </c>
-      <c r="C81" t="s">
-        <v>334</v>
-      </c>
       <c r="D81" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E81" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F81">
         <v>100</v>
       </c>
       <c r="G81" t="s">
+        <v>334</v>
+      </c>
+      <c r="H81" t="s">
         <v>335</v>
       </c>
-      <c r="H81" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8">
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>331</v>
+      </c>
+      <c r="B82" t="s">
         <v>332</v>
-      </c>
-      <c r="B82" t="s">
-        <v>333</v>
       </c>
       <c r="C82" t="s">
         <v>28</v>
       </c>
       <c r="D82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E82" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F82" t="s">
+        <v>336</v>
+      </c>
+      <c r="G82" t="s">
+        <v>227</v>
+      </c>
+      <c r="H82" t="s">
         <v>337</v>
       </c>
-      <c r="G82" t="s">
-        <v>228</v>
-      </c>
-      <c r="H82" t="s">
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>331</v>
+      </c>
+      <c r="B83" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="83" spans="1:8">
-      <c r="A83" t="s">
-        <v>332</v>
-      </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>339</v>
       </c>
-      <c r="C83" t="s">
-        <v>340</v>
-      </c>
       <c r="D83" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E83" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
+        <v>340</v>
+      </c>
+      <c r="H83" t="s">
         <v>341</v>
       </c>
-      <c r="H83" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8">
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B84" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C84" t="s">
         <v>28</v>
       </c>
       <c r="D84" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E84" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F84" t="s">
+        <v>342</v>
+      </c>
+      <c r="G84" t="s">
+        <v>227</v>
+      </c>
+      <c r="H84" t="s">
         <v>343</v>
       </c>
-      <c r="G84" t="s">
-        <v>228</v>
-      </c>
-      <c r="H84" t="s">
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>331</v>
+      </c>
+      <c r="B85" t="s">
+        <v>332</v>
+      </c>
+      <c r="C85" t="s">
         <v>344</v>
       </c>
-    </row>
-    <row r="85" spans="1:8">
-      <c r="A85" t="s">
-        <v>332</v>
-      </c>
-      <c r="B85" t="s">
-        <v>333</v>
-      </c>
-      <c r="C85" t="s">
-        <v>345</v>
-      </c>
       <c r="D85" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E85" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F85">
         <v>10</v>
       </c>
       <c r="G85" t="s">
+        <v>345</v>
+      </c>
+      <c r="H85" t="s">
         <v>346</v>
       </c>
-      <c r="H85" t="s">
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>347</v>
       </c>
-    </row>
-    <row r="86" spans="1:8">
-      <c r="A86" t="s">
+      <c r="B86" t="s">
         <v>348</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>349</v>
       </c>
-      <c r="C86" t="s">
-        <v>350</v>
-      </c>
       <c r="D86" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E86" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
+        <v>350</v>
+      </c>
+      <c r="H86" t="s">
         <v>351</v>
       </c>
-      <c r="H86" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8">
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>347</v>
+      </c>
+      <c r="B87" t="s">
         <v>348</v>
-      </c>
-      <c r="B87" t="s">
-        <v>349</v>
       </c>
       <c r="C87" t="s">
         <v>28</v>
       </c>
       <c r="D87" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E87" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F87" t="s">
+        <v>352</v>
+      </c>
+      <c r="G87" t="s">
+        <v>227</v>
+      </c>
+      <c r="H87" t="s">
         <v>353</v>
       </c>
-      <c r="G87" t="s">
-        <v>228</v>
-      </c>
-      <c r="H87" t="s">
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>347</v>
+      </c>
+      <c r="B88" t="s">
         <v>354</v>
       </c>
-    </row>
-    <row r="88" spans="1:8">
-      <c r="A88" t="s">
-        <v>348</v>
-      </c>
-      <c r="B88" t="s">
+      <c r="C88" t="s">
         <v>355</v>
       </c>
-      <c r="C88" t="s">
-        <v>356</v>
-      </c>
       <c r="D88" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E88" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F88">
         <v>500</v>
       </c>
       <c r="G88" t="s">
+        <v>356</v>
+      </c>
+      <c r="H88" t="s">
         <v>357</v>
       </c>
-      <c r="H88" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8">
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B89" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C89" t="s">
         <v>28</v>
       </c>
       <c r="D89" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E89" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F89" t="s">
+        <v>358</v>
+      </c>
+      <c r="G89" t="s">
+        <v>227</v>
+      </c>
+      <c r="H89" t="s">
         <v>359</v>
       </c>
-      <c r="G89" t="s">
-        <v>228</v>
-      </c>
-      <c r="H89" t="s">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>360</v>
       </c>
-    </row>
-    <row r="90" spans="1:8">
-      <c r="A90" t="s">
+      <c r="B90" t="s">
         <v>361</v>
       </c>
-      <c r="B90" t="s">
-        <v>362</v>
-      </c>
       <c r="C90" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E90" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F90">
         <v>250</v>
       </c>
       <c r="G90" t="s">
+        <v>362</v>
+      </c>
+      <c r="H90" t="s">
         <v>363</v>
       </c>
-      <c r="H90" t="s">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>360</v>
+      </c>
+      <c r="B91" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="91" spans="1:8">
-      <c r="A91" t="s">
-        <v>361</v>
-      </c>
-      <c r="B91" t="s">
-        <v>365</v>
-      </c>
       <c r="C91" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D91" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E91" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F91">
         <v>200</v>
       </c>
       <c r="G91" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H91" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>360</v>
+      </c>
+      <c r="B92" t="s">
         <v>366</v>
       </c>
-    </row>
-    <row r="92" spans="1:8">
-      <c r="A92" t="s">
-        <v>361</v>
-      </c>
-      <c r="B92" t="s">
-        <v>367</v>
-      </c>
       <c r="C92" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E92" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F92">
         <v>250</v>
       </c>
       <c r="G92" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H92" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>360</v>
+      </c>
+      <c r="B93" t="s">
         <v>368</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8">
-      <c r="A93" t="s">
-        <v>361</v>
-      </c>
-      <c r="B93" t="s">
-        <v>369</v>
       </c>
       <c r="C93" t="s">
         <v>28</v>
       </c>
       <c r="D93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E93" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F93" t="s">
+        <v>369</v>
+      </c>
+      <c r="G93" t="s">
+        <v>227</v>
+      </c>
+      <c r="H93" t="s">
         <v>370</v>
       </c>
-      <c r="G93" t="s">
-        <v>228</v>
-      </c>
-      <c r="H93" t="s">
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>360</v>
+      </c>
+      <c r="B94" t="s">
         <v>371</v>
       </c>
-    </row>
-    <row r="94" spans="1:8">
-      <c r="A94" t="s">
-        <v>361</v>
-      </c>
-      <c r="B94" t="s">
+      <c r="C94" t="s">
+        <v>255</v>
+      </c>
+      <c r="D94" t="s">
+        <v>225</v>
+      </c>
+      <c r="E94" t="s">
+        <v>225</v>
+      </c>
+      <c r="F94" t="s">
         <v>372</v>
       </c>
-      <c r="C94" t="s">
-        <v>256</v>
-      </c>
-      <c r="D94" t="s">
-        <v>226</v>
-      </c>
-      <c r="E94" t="s">
-        <v>226</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
+        <v>227</v>
+      </c>
+      <c r="H94" t="s">
         <v>373</v>
       </c>
-      <c r="G94" t="s">
-        <v>228</v>
-      </c>
-      <c r="H94" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>26</v>
       </c>
@@ -6008,22 +6005,22 @@
         <v>28</v>
       </c>
       <c r="D95" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E95" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F95" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G95" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H95" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>26</v>
       </c>
@@ -6034,22 +6031,22 @@
         <v>28</v>
       </c>
       <c r="D96" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E96" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F96" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G96" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H96" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>26</v>
       </c>
@@ -6060,19 +6057,19 @@
         <v>28</v>
       </c>
       <c r="D97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E97" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G97" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H97" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -6083,14 +6080,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A9B6005-6F43-4EB4-8661-C70A2093261E}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -6098,21 +6095,21 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1" t="s">
         <v>376</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>377</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>378</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>379</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>380</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -6124,9 +6121,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -6138,9 +6135,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -6152,9 +6149,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -6166,9 +6163,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -6180,9 +6177,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -6194,9 +6191,9 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -6208,9 +6205,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -6222,9 +6219,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -6236,9 +6233,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -6250,9 +6247,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -6264,9 +6261,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -6278,9 +6275,9 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -6292,9 +6289,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -6306,9 +6303,9 @@
         <v>600</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -6320,12 +6317,12 @@
         <v>600</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>382</v>
+      </c>
+      <c r="B17" t="s">
         <v>383</v>
-      </c>
-      <c r="B17" t="s">
-        <v>384</v>
       </c>
       <c r="C17">
         <v>60</v>
@@ -6334,12 +6331,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>382</v>
+      </c>
+      <c r="B18" t="s">
         <v>383</v>
-      </c>
-      <c r="B18" t="s">
-        <v>384</v>
       </c>
       <c r="C18">
         <v>120</v>
@@ -6348,12 +6345,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B19" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C19">
         <v>30</v>
@@ -6362,12 +6359,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B20" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C20">
         <v>90</v>
@@ -6382,25 +6379,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c5712268625b41a295c1c13b9cc08810">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2284d5a418b13d67f420d8f33de3453b" ns2:_="">
     <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
@@ -6572,14 +6550,57 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C309B-A406-4F09-B9ED-A6A4D616E23D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1D5C309B-A406-4F09-B9ED-A6A4D616E23D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE46D7A-83F4-4278-8F92-EA280F30E64E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C261B1-545A-4F6E-B711-231B43BEE1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="414">
   <si>
     <t>Category</t>
   </si>
@@ -347,9 +347,6 @@
   </si>
   <si>
     <t>19 mm hose reel, 25 mm hose reel</t>
-  </si>
-  <si>
-    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
   </si>
   <si>
     <t>NCC E1D3(2) / E1D3(1)(a) exemption Cl 2,3,5 / AS 1221</t>
@@ -2430,7 +2427,7 @@
         <v>69</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G20" s="18" t="s">
         <v>70</v>
@@ -2653,16 +2650,16 @@
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
         <v>21</v>
       </c>
       <c r="J27" t="s">
+        <v>102</v>
+      </c>
+      <c r="M27" t="s">
         <v>103</v>
-      </c>
-      <c r="M27" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:15" s="23" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2676,20 +2673,20 @@
         <v>99</v>
       </c>
       <c r="D28" s="23" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" s="6" t="s">
         <v>105</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>106</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H28" s="23" t="s">
         <v>38</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K28" s="23" t="s">
         <v>33</v>
@@ -2703,28 +2700,28 @@
         <v>5</v>
       </c>
       <c r="B29" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="D29" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="G29" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>112</v>
       </c>
       <c r="H29" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I29" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="M29" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M29" s="2" t="s">
+      <c r="O29" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="O29" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="30" spans="1:15" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2732,28 +2729,28 @@
         <v>5</v>
       </c>
       <c r="B30" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>110</v>
-      </c>
       <c r="D30" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" s="12" t="s">
         <v>116</v>
-      </c>
-      <c r="G30" s="12" t="s">
-        <v>117</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I30" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="M30" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M30" s="2" t="s">
+      <c r="O30" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="31" spans="1:15" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2761,28 +2758,28 @@
         <v>5</v>
       </c>
       <c r="B31" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>110</v>
-      </c>
       <c r="D31" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="G31" s="12" t="s">
-        <v>119</v>
       </c>
       <c r="H31" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I31" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="M31" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M31" s="2" t="s">
+      <c r="O31" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="O31" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="32" spans="1:15" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2790,28 +2787,28 @@
         <v>5</v>
       </c>
       <c r="B32" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="C32" s="15" t="s">
-        <v>110</v>
-      </c>
       <c r="D32" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="G32" s="12" t="s">
         <v>120</v>
-      </c>
-      <c r="G32" s="12" t="s">
-        <v>121</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I32" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="M32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="M32" s="2" t="s">
+      <c r="O32" s="12" t="s">
         <v>114</v>
-      </c>
-      <c r="O32" s="12" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2819,22 +2816,22 @@
         <v>5</v>
       </c>
       <c r="B33" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="G33" s="12" t="s">
         <v>123</v>
-      </c>
-      <c r="G33" s="12" t="s">
-        <v>124</v>
       </c>
       <c r="H33" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M33" s="12" t="s">
         <v>24</v>
@@ -2845,25 +2842,25 @@
         <v>5</v>
       </c>
       <c r="B34" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D34" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="G34" s="12" t="s">
         <v>126</v>
-      </c>
-      <c r="G34" s="12" t="s">
-        <v>127</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M34" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2871,25 +2868,25 @@
         <v>5</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G35" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="G35" s="12" t="s">
-        <v>130</v>
       </c>
       <c r="H35" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M35" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2897,13 +2894,13 @@
         <v>5</v>
       </c>
       <c r="B36" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D36" s="22" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H36" s="5" t="s">
         <v>38</v>
@@ -2912,7 +2909,7 @@
         <v>39</v>
       </c>
       <c r="M36" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2920,25 +2917,25 @@
         <v>5</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D37" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" s="12" t="s">
         <v>134</v>
-      </c>
-      <c r="G37" s="12" t="s">
-        <v>135</v>
       </c>
       <c r="H37" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="M37" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2946,22 +2943,22 @@
         <v>5</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D38" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>138</v>
       </c>
       <c r="H38" s="12" t="s">
         <v>21</v>
       </c>
       <c r="M38" s="12" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="14.5" x14ac:dyDescent="0.35">
@@ -2969,26 +2966,26 @@
         <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C39" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="12" t="s">
         <v>139</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>140</v>
       </c>
       <c r="F39" s="12"/>
       <c r="G39" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>21</v>
       </c>
       <c r="I39" t="s">
+        <v>141</v>
+      </c>
+      <c r="J39" t="s">
         <v>142</v>
-      </c>
-      <c r="J39" t="s">
-        <v>143</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>24</v>
@@ -2999,17 +2996,17 @@
         <v>5</v>
       </c>
       <c r="B40" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C40" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>144</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>145</v>
       </c>
       <c r="F40" s="12"/>
       <c r="G40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H40" t="s">
         <v>21</v>
@@ -3023,23 +3020,23 @@
         <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F41" s="12"/>
       <c r="G41" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>21</v>
       </c>
       <c r="I41" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M41" s="7" t="s">
         <v>24</v>
@@ -3050,13 +3047,13 @@
         <v>5</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H42" s="5" t="s">
         <v>38</v>
@@ -3073,13 +3070,13 @@
         <v>5</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H43" s="5" t="s">
         <v>38</v>
@@ -3096,13 +3093,13 @@
         <v>5</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H44" s="5" t="s">
         <v>38</v>
@@ -3119,23 +3116,23 @@
         <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>153</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="F45" s="12"/>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H45" t="s">
         <v>21</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3143,13 +3140,13 @@
         <v>5</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H46" s="5" t="s">
         <v>38</v>
@@ -3158,7 +3155,7 @@
         <v>39</v>
       </c>
       <c r="M46" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3166,34 +3163,34 @@
         <v>6</v>
       </c>
       <c r="B47" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C47" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="D47" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="E47" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="E47" s="37" t="s">
+      <c r="F47" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="F47" s="18" t="s">
-        <v>161</v>
-      </c>
       <c r="G47" s="18" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H47" s="18" t="s">
         <v>21</v>
       </c>
       <c r="J47" s="18" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K47" s="18" t="s">
         <v>66</v>
       </c>
       <c r="L47" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M47" s="18" t="s">
         <v>24</v>
@@ -3204,29 +3201,29 @@
         <v>6</v>
       </c>
       <c r="B48" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C48" s="12" t="s">
         <v>157</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="D48" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>163</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>164</v>
       </c>
       <c r="F48" s="40"/>
       <c r="G48" s="12" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H48" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J48" s="12" t="s">
+        <v>164</v>
+      </c>
+      <c r="K48" s="12" t="s">
         <v>165</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>166</v>
       </c>
       <c r="M48" s="12" t="s">
         <v>79</v>
@@ -3237,16 +3234,16 @@
         <v>6</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>158</v>
-      </c>
       <c r="D49" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H49" s="5" t="s">
         <v>38</v>
@@ -3260,16 +3257,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C50" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="D50" s="5" t="s">
-        <v>169</v>
-      </c>
       <c r="G50" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H50" s="5" t="s">
         <v>38</v>
@@ -3286,19 +3283,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D51" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E51" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="G51" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H51" s="5" t="s">
         <v>38</v>
@@ -3307,7 +3304,7 @@
         <v>39</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="M51" s="5" t="s">
         <v>79</v>
@@ -3318,16 +3315,16 @@
         <v>6</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G52" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H52" s="5" t="s">
         <v>38</v>
@@ -3344,16 +3341,16 @@
         <v>6</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G53" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H53" s="5" t="s">
         <v>38</v>
@@ -3370,28 +3367,28 @@
         <v>6</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C54" t="s">
+        <v>174</v>
+      </c>
+      <c r="D54" t="s">
         <v>175</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" t="s">
         <v>177</v>
       </c>
-      <c r="F54" t="s">
-        <v>178</v>
-      </c>
       <c r="G54" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H54" s="21" t="s">
         <v>21</v>
       </c>
       <c r="J54" s="42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M54" s="28" t="s">
         <v>50</v>
@@ -3402,25 +3399,25 @@
         <v>6</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H55" s="12" t="s">
         <v>21</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="56" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3428,19 +3425,19 @@
         <v>6</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E56" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="G56" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H56" s="5" t="s">
         <v>38</v>
@@ -3449,7 +3446,7 @@
         <v>39</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3457,13 +3454,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E57" s="6"/>
       <c r="H57" s="5" t="s">
@@ -3479,17 +3476,17 @@
         <v>7</v>
       </c>
       <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="D58" s="18" t="s">
         <v>187</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>188</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H58" t="s">
         <v>21</v>
@@ -3503,29 +3500,29 @@
         <v>7</v>
       </c>
       <c r="B59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" t="s">
         <v>186</v>
       </c>
-      <c r="C59" t="s">
-        <v>187</v>
-      </c>
       <c r="D59" t="s">
+        <v>189</v>
+      </c>
+      <c r="E59" t="s">
         <v>190</v>
-      </c>
-      <c r="E59" t="s">
-        <v>191</v>
       </c>
       <c r="F59" s="12"/>
       <c r="G59" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H59" t="s">
         <v>21</v>
       </c>
       <c r="I59" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="14.5" x14ac:dyDescent="0.35">
@@ -3533,23 +3530,23 @@
         <v>7</v>
       </c>
       <c r="B60" t="s">
+        <v>185</v>
+      </c>
+      <c r="C60" t="s">
         <v>186</v>
       </c>
-      <c r="C60" t="s">
-        <v>187</v>
-      </c>
       <c r="D60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F60" s="12"/>
       <c r="G60" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H60" t="s">
         <v>21</v>
       </c>
       <c r="I60" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M60" t="s">
         <v>24</v>
@@ -3560,29 +3557,29 @@
         <v>8</v>
       </c>
       <c r="B61" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="C61" t="s">
         <v>194</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>195</v>
-      </c>
-      <c r="D61" t="s">
-        <v>196</v>
       </c>
       <c r="E61"/>
       <c r="F61" t="s">
         <v>31</v>
       </c>
       <c r="G61" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>21</v>
       </c>
       <c r="I61" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="J61" s="18" t="s">
         <v>197</v>
-      </c>
-      <c r="J61" s="18" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="62" spans="1:13" s="12" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3590,23 +3587,23 @@
         <v>8</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="C62" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="C62" s="12" t="s">
-        <v>195</v>
-      </c>
       <c r="D62" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E62" s="6"/>
       <c r="G62" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H62" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J62" s="18" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M62" s="12" t="s">
         <v>79</v>
@@ -3617,13 +3614,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="C63" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H63" s="5" t="s">
         <v>38</v>
@@ -3632,7 +3629,7 @@
         <v>39</v>
       </c>
       <c r="J63" s="18" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="14.5" x14ac:dyDescent="0.35">
@@ -3640,18 +3637,18 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
+        <v>201</v>
+      </c>
+      <c r="C64" t="s">
         <v>202</v>
       </c>
-      <c r="C64" t="s">
+      <c r="D64" t="s">
         <v>203</v>
-      </c>
-      <c r="D64" t="s">
-        <v>204</v>
       </c>
       <c r="E64" s="39"/>
       <c r="F64" s="12"/>
       <c r="G64" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H64" t="s">
         <v>21</v>
@@ -3660,7 +3657,7 @@
         <v>33</v>
       </c>
       <c r="L64" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M64" t="s">
         <v>24</v>
@@ -3671,19 +3668,19 @@
         <v>9</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="D65" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="E65" s="5" t="s">
+      <c r="G65" s="5" t="s">
         <v>207</v>
-      </c>
-      <c r="G65" s="5" t="s">
-        <v>208</v>
       </c>
       <c r="H65" s="5" t="s">
         <v>38</v>
@@ -3692,7 +3689,7 @@
         <v>39</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="66" spans="1:14" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3700,19 +3697,19 @@
         <v>9</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C66" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="D66" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="E66" s="5" t="s">
+      <c r="G66" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="G66" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="H66" s="5" t="s">
         <v>38</v>
@@ -3721,7 +3718,7 @@
         <v>39</v>
       </c>
       <c r="N66" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="67" spans="1:14" s="29" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3729,13 +3726,13 @@
         <v>10</v>
       </c>
       <c r="B67" s="29" t="s">
+        <v>213</v>
+      </c>
+      <c r="C67" s="29" t="s">
         <v>214</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="D67" s="29" t="s">
         <v>215</v>
-      </c>
-      <c r="D67" s="29" t="s">
-        <v>216</v>
       </c>
       <c r="H67" s="5" t="s">
         <v>38</v>
@@ -3749,13 +3746,13 @@
         <v>10</v>
       </c>
       <c r="B68" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="D68" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H68" s="5" t="s">
         <v>38</v>
@@ -3769,13 +3766,13 @@
         <v>10</v>
       </c>
       <c r="B69" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C69" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="D69" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H69" s="5" t="s">
         <v>38</v>
@@ -3789,13 +3786,13 @@
         <v>10</v>
       </c>
       <c r="B70" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C70" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="D70" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H70" s="5" t="s">
         <v>38</v>
@@ -3809,13 +3806,13 @@
         <v>10</v>
       </c>
       <c r="B71" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C71" s="22" t="s">
         <v>214</v>
       </c>
-      <c r="C71" s="22" t="s">
-        <v>215</v>
-      </c>
       <c r="D71" s="22" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H71" s="5" t="s">
         <v>38</v>
@@ -3867,187 +3864,187 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" t="s">
         <v>221</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>222</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>223</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>224</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>225</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>226</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>227</v>
-      </c>
-      <c r="H1" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D2">
         <v>104.04</v>
       </c>
       <c r="E2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D3">
         <v>51.84</v>
       </c>
       <c r="E3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D6">
         <v>49</v>
       </c>
       <c r="E6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8">
         <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14" t="s">
         <v>239</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>240</v>
-      </c>
-      <c r="C14" t="s">
-        <v>241</v>
       </c>
       <c r="D14">
         <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15" t="s">
         <v>239</v>
       </c>
-      <c r="B15" t="s">
-        <v>240</v>
-      </c>
       <c r="C15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D15">
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" t="s">
         <v>239</v>
       </c>
-      <c r="B16" t="s">
-        <v>240</v>
-      </c>
       <c r="C16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D16">
         <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -4070,2524 +4067,2524 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" t="s">
         <v>245</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>246</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>247</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>248</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H1" t="s">
         <v>249</v>
-      </c>
-      <c r="F1" t="s">
-        <v>224</v>
-      </c>
-      <c r="G1" t="s">
-        <v>225</v>
-      </c>
-      <c r="H1" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B2" t="s">
         <v>251</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>252</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>253</v>
       </c>
-      <c r="D2" t="s">
-        <v>254</v>
-      </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F2">
         <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B3" t="s">
         <v>251</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>252</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>253</v>
       </c>
-      <c r="D3" t="s">
-        <v>254</v>
-      </c>
       <c r="E3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B4" t="s">
         <v>251</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>252</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>253</v>
       </c>
-      <c r="D4" t="s">
-        <v>254</v>
-      </c>
       <c r="E4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F4">
         <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>250</v>
+      </c>
+      <c r="B5" t="s">
         <v>251</v>
       </c>
-      <c r="B5" t="s">
-        <v>252</v>
-      </c>
       <c r="C5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+      <c r="E5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" t="s">
         <v>256</v>
       </c>
-      <c r="D5" t="s">
-        <v>230</v>
-      </c>
-      <c r="E5" t="s">
-        <v>230</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>257</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>258</v>
-      </c>
-      <c r="H5" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C6" t="s">
         <v>260</v>
       </c>
-      <c r="C6" t="s">
-        <v>261</v>
-      </c>
       <c r="D6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H6" t="s">
         <v>262</v>
-      </c>
-      <c r="H6" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F7" t="s">
         <v>264</v>
       </c>
-      <c r="D7" t="s">
-        <v>230</v>
-      </c>
-      <c r="E7" t="s">
-        <v>230</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
+        <v>257</v>
+      </c>
+      <c r="H7" t="s">
         <v>265</v>
-      </c>
-      <c r="G7" t="s">
-        <v>258</v>
-      </c>
-      <c r="H7" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C8" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F8" t="s">
         <v>267</v>
       </c>
-      <c r="D8" t="s">
-        <v>230</v>
-      </c>
-      <c r="E8" t="s">
-        <v>230</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
+        <v>257</v>
+      </c>
+      <c r="H8" t="s">
         <v>268</v>
-      </c>
-      <c r="G8" t="s">
-        <v>258</v>
-      </c>
-      <c r="H8" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C9" t="s">
         <v>270</v>
       </c>
-      <c r="B9" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" t="s">
-        <v>271</v>
-      </c>
       <c r="D9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F9">
         <v>400</v>
       </c>
       <c r="G9" t="s">
+        <v>271</v>
+      </c>
+      <c r="H9" t="s">
         <v>272</v>
-      </c>
-      <c r="H9" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F10" t="s">
+        <v>273</v>
+      </c>
+      <c r="G10" t="s">
+        <v>257</v>
+      </c>
+      <c r="H10" t="s">
         <v>274</v>
-      </c>
-      <c r="G10" t="s">
-        <v>258</v>
-      </c>
-      <c r="H10" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" t="s">
         <v>276</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" t="s">
+        <v>229</v>
+      </c>
+      <c r="F11" t="s">
         <v>277</v>
       </c>
-      <c r="D11" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
+        <v>257</v>
+      </c>
+      <c r="H11" t="s">
         <v>278</v>
-      </c>
-      <c r="G11" t="s">
-        <v>258</v>
-      </c>
-      <c r="H11" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" t="s">
         <v>280</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>281</v>
       </c>
-      <c r="C12" t="s">
-        <v>282</v>
-      </c>
       <c r="D12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E12" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F12">
         <v>104.04</v>
       </c>
       <c r="G12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H12" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E13" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F13">
         <v>51.84</v>
       </c>
       <c r="G13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H13" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B14" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C14" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F14">
         <v>2000</v>
       </c>
       <c r="G14" t="s">
+        <v>285</v>
+      </c>
+      <c r="H14" t="s">
         <v>286</v>
-      </c>
-      <c r="H14" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" t="s">
         <v>288</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E15" t="s">
+        <v>229</v>
+      </c>
+      <c r="F15" t="s">
         <v>289</v>
       </c>
-      <c r="D15" t="s">
-        <v>230</v>
-      </c>
-      <c r="E15" t="s">
-        <v>230</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
+        <v>257</v>
+      </c>
+      <c r="H15" t="s">
         <v>290</v>
-      </c>
-      <c r="G15" t="s">
-        <v>258</v>
-      </c>
-      <c r="H15" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" t="s">
+        <v>229</v>
+      </c>
+      <c r="E16" t="s">
+        <v>229</v>
+      </c>
+      <c r="F16" t="s">
         <v>292</v>
       </c>
-      <c r="C16" t="s">
-        <v>289</v>
-      </c>
-      <c r="D16" t="s">
-        <v>230</v>
-      </c>
-      <c r="E16" t="s">
-        <v>230</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
+        <v>257</v>
+      </c>
+      <c r="H16" t="s">
         <v>293</v>
-      </c>
-      <c r="G16" t="s">
-        <v>258</v>
-      </c>
-      <c r="H16" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>294</v>
+      </c>
+      <c r="B17" t="s">
         <v>295</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>255</v>
+      </c>
+      <c r="D17" t="s">
+        <v>229</v>
+      </c>
+      <c r="E17" t="s">
+        <v>229</v>
+      </c>
+      <c r="F17" t="s">
         <v>296</v>
       </c>
-      <c r="C17" t="s">
-        <v>256</v>
-      </c>
-      <c r="D17" t="s">
-        <v>230</v>
-      </c>
-      <c r="E17" t="s">
-        <v>230</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
+        <v>257</v>
+      </c>
+      <c r="H17" t="s">
         <v>297</v>
-      </c>
-      <c r="G17" t="s">
-        <v>258</v>
-      </c>
-      <c r="H17" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B18" t="s">
         <v>295</v>
       </c>
-      <c r="B18" t="s">
-        <v>296</v>
-      </c>
       <c r="C18" t="s">
+        <v>298</v>
+      </c>
+      <c r="D18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E18" t="s">
         <v>299</v>
       </c>
-      <c r="D18" t="s">
-        <v>254</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>300</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>301</v>
       </c>
-      <c r="G18" t="s">
+      <c r="H18" t="s">
         <v>302</v>
-      </c>
-      <c r="H18" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B19" t="s">
         <v>295</v>
       </c>
-      <c r="B19" t="s">
-        <v>296</v>
-      </c>
       <c r="C19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E19" t="s">
+        <v>303</v>
+      </c>
+      <c r="F19" t="s">
         <v>304</v>
       </c>
-      <c r="F19" t="s">
-        <v>305</v>
-      </c>
       <c r="G19" t="s">
+        <v>301</v>
+      </c>
+      <c r="H19" t="s">
         <v>302</v>
-      </c>
-      <c r="H19" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" t="s">
         <v>295</v>
       </c>
-      <c r="B20" t="s">
-        <v>296</v>
-      </c>
       <c r="C20" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G20" t="s">
+        <v>301</v>
+      </c>
+      <c r="H20" t="s">
         <v>302</v>
-      </c>
-      <c r="H20" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" t="s">
         <v>295</v>
       </c>
-      <c r="B21" t="s">
-        <v>296</v>
-      </c>
       <c r="C21" t="s">
+        <v>306</v>
+      </c>
+      <c r="D21" t="s">
         <v>307</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>308</v>
-      </c>
-      <c r="E21" t="s">
-        <v>309</v>
       </c>
       <c r="F21">
         <v>100</v>
       </c>
       <c r="G21" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>294</v>
+      </c>
+      <c r="B22" t="s">
         <v>295</v>
       </c>
-      <c r="B22" t="s">
-        <v>296</v>
-      </c>
       <c r="C22" t="s">
+        <v>306</v>
+      </c>
+      <c r="D22" t="s">
         <v>307</v>
       </c>
-      <c r="D22" t="s">
-        <v>308</v>
-      </c>
       <c r="E22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F22">
         <v>300</v>
       </c>
       <c r="G22" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>294</v>
+      </c>
+      <c r="B23" t="s">
         <v>295</v>
       </c>
-      <c r="B23" t="s">
-        <v>296</v>
-      </c>
       <c r="C23" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" t="s">
         <v>307</v>
       </c>
-      <c r="D23" t="s">
-        <v>308</v>
-      </c>
       <c r="E23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F23">
         <v>450</v>
       </c>
       <c r="G23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B24" t="s">
         <v>295</v>
       </c>
-      <c r="B24" t="s">
-        <v>296</v>
-      </c>
       <c r="C24" t="s">
+        <v>306</v>
+      </c>
+      <c r="D24" t="s">
         <v>307</v>
       </c>
-      <c r="D24" t="s">
-        <v>308</v>
-      </c>
       <c r="E24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F24">
         <v>675</v>
       </c>
       <c r="G24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>294</v>
+      </c>
+      <c r="B25" t="s">
         <v>295</v>
       </c>
-      <c r="B25" t="s">
-        <v>296</v>
-      </c>
       <c r="C25" t="s">
+        <v>306</v>
+      </c>
+      <c r="D25" t="s">
         <v>307</v>
       </c>
-      <c r="D25" t="s">
-        <v>308</v>
-      </c>
       <c r="E25" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F25">
         <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H25" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>294</v>
+      </c>
+      <c r="B26" t="s">
         <v>295</v>
       </c>
-      <c r="B26" t="s">
-        <v>296</v>
-      </c>
       <c r="C26" t="s">
+        <v>306</v>
+      </c>
+      <c r="D26" t="s">
         <v>307</v>
       </c>
-      <c r="D26" t="s">
-        <v>308</v>
-      </c>
       <c r="E26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F26">
         <v>300</v>
       </c>
       <c r="G26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H26" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>294</v>
+      </c>
+      <c r="B27" t="s">
         <v>295</v>
       </c>
-      <c r="B27" t="s">
-        <v>296</v>
-      </c>
       <c r="C27" t="s">
+        <v>306</v>
+      </c>
+      <c r="D27" t="s">
         <v>307</v>
       </c>
-      <c r="D27" t="s">
-        <v>308</v>
-      </c>
       <c r="E27" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F27">
         <v>450</v>
       </c>
       <c r="G27" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H27" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>294</v>
+      </c>
+      <c r="B28" t="s">
         <v>295</v>
       </c>
-      <c r="B28" t="s">
-        <v>296</v>
-      </c>
       <c r="C28" t="s">
+        <v>306</v>
+      </c>
+      <c r="D28" t="s">
         <v>307</v>
       </c>
-      <c r="D28" t="s">
-        <v>308</v>
-      </c>
       <c r="E28" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F28">
         <v>675</v>
       </c>
       <c r="G28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H28" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>294</v>
+      </c>
+      <c r="B29" t="s">
         <v>295</v>
       </c>
-      <c r="B29" t="s">
-        <v>296</v>
-      </c>
       <c r="C29" t="s">
+        <v>306</v>
+      </c>
+      <c r="D29" t="s">
         <v>307</v>
       </c>
-      <c r="D29" t="s">
-        <v>308</v>
-      </c>
       <c r="E29" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F29">
         <v>150</v>
       </c>
       <c r="G29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>294</v>
+      </c>
+      <c r="B30" t="s">
         <v>295</v>
       </c>
-      <c r="B30" t="s">
-        <v>296</v>
-      </c>
       <c r="C30" t="s">
+        <v>306</v>
+      </c>
+      <c r="D30" t="s">
         <v>307</v>
       </c>
-      <c r="D30" t="s">
-        <v>308</v>
-      </c>
       <c r="E30" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F30">
         <v>200</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H30" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" t="s">
         <v>295</v>
       </c>
-      <c r="B31" t="s">
-        <v>296</v>
-      </c>
       <c r="C31" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" t="s">
         <v>307</v>
       </c>
-      <c r="D31" t="s">
-        <v>308</v>
-      </c>
       <c r="E31" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F31">
         <v>300</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" t="s">
         <v>295</v>
       </c>
-      <c r="B32" t="s">
-        <v>296</v>
-      </c>
       <c r="C32" t="s">
+        <v>306</v>
+      </c>
+      <c r="D32" t="s">
         <v>307</v>
       </c>
-      <c r="D32" t="s">
-        <v>308</v>
-      </c>
       <c r="E32" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F32">
         <v>450</v>
       </c>
       <c r="G32" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>294</v>
+      </c>
+      <c r="B33" t="s">
         <v>295</v>
       </c>
-      <c r="B33" t="s">
-        <v>296</v>
-      </c>
       <c r="C33" t="s">
+        <v>306</v>
+      </c>
+      <c r="D33" t="s">
         <v>307</v>
       </c>
-      <c r="D33" t="s">
-        <v>308</v>
-      </c>
       <c r="E33" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F33">
         <v>675</v>
       </c>
       <c r="G33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>294</v>
+      </c>
+      <c r="B34" t="s">
         <v>295</v>
       </c>
-      <c r="B34" t="s">
-        <v>296</v>
-      </c>
       <c r="C34" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D34" t="s">
+        <v>307</v>
+      </c>
+      <c r="E34" t="s">
         <v>308</v>
-      </c>
-      <c r="E34" t="s">
-        <v>309</v>
       </c>
       <c r="F34">
         <v>150</v>
       </c>
       <c r="G34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H34" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>294</v>
+      </c>
+      <c r="B35" t="s">
         <v>295</v>
       </c>
-      <c r="B35" t="s">
-        <v>296</v>
-      </c>
       <c r="C35" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E35" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F35">
         <v>450</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>294</v>
+      </c>
+      <c r="B36" t="s">
         <v>295</v>
       </c>
-      <c r="B36" t="s">
-        <v>296</v>
-      </c>
       <c r="C36" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E36" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F36">
         <v>675</v>
       </c>
       <c r="G36" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H36" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>294</v>
+      </c>
+      <c r="B37" t="s">
         <v>295</v>
       </c>
-      <c r="B37" t="s">
-        <v>296</v>
-      </c>
       <c r="C37" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D37" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E37" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F37">
         <v>1000</v>
       </c>
       <c r="G37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H37" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>294</v>
+      </c>
+      <c r="B38" t="s">
         <v>295</v>
       </c>
-      <c r="B38" t="s">
-        <v>296</v>
-      </c>
       <c r="C38" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D38" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E38" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F38">
         <v>150</v>
       </c>
       <c r="G38" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H38" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>294</v>
+      </c>
+      <c r="B39" t="s">
         <v>295</v>
       </c>
-      <c r="B39" t="s">
-        <v>296</v>
-      </c>
       <c r="C39" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D39" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E39" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F39">
         <v>450</v>
       </c>
       <c r="G39" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H39" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>294</v>
+      </c>
+      <c r="B40" t="s">
         <v>295</v>
       </c>
-      <c r="B40" t="s">
-        <v>296</v>
-      </c>
       <c r="C40" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E40" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F40">
         <v>675</v>
       </c>
       <c r="G40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>294</v>
+      </c>
+      <c r="B41" t="s">
         <v>295</v>
       </c>
-      <c r="B41" t="s">
-        <v>296</v>
-      </c>
       <c r="C41" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D41" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E41" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F41">
         <v>1000</v>
       </c>
       <c r="G41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H41" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>294</v>
+      </c>
+      <c r="B42" t="s">
         <v>295</v>
       </c>
-      <c r="B42" t="s">
-        <v>296</v>
-      </c>
       <c r="C42" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D42" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E42" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F42">
         <v>225</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H42" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>294</v>
+      </c>
+      <c r="B43" t="s">
         <v>295</v>
       </c>
-      <c r="B43" t="s">
-        <v>296</v>
-      </c>
       <c r="C43" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D43" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E43" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F43">
         <v>300</v>
       </c>
       <c r="G43" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H43" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" t="s">
         <v>295</v>
       </c>
-      <c r="B44" t="s">
-        <v>296</v>
-      </c>
       <c r="C44" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F44">
         <v>450</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>294</v>
+      </c>
+      <c r="B45" t="s">
         <v>295</v>
       </c>
-      <c r="B45" t="s">
-        <v>296</v>
-      </c>
       <c r="C45" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E45" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F45">
         <v>675</v>
       </c>
       <c r="G45" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H45" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" t="s">
         <v>295</v>
       </c>
-      <c r="B46" t="s">
-        <v>296</v>
-      </c>
       <c r="C46" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E46" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F46">
         <v>1000</v>
       </c>
       <c r="G46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H46" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>294</v>
+      </c>
+      <c r="B47" t="s">
         <v>295</v>
       </c>
-      <c r="B47" t="s">
-        <v>296</v>
-      </c>
       <c r="C47" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" t="s">
+        <v>299</v>
+      </c>
+      <c r="F47" t="s">
         <v>324</v>
       </c>
-      <c r="D47" t="s">
-        <v>254</v>
-      </c>
-      <c r="E47" t="s">
-        <v>300</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="G47" t="s">
+        <v>301</v>
+      </c>
+      <c r="H47" t="s">
         <v>325</v>
-      </c>
-      <c r="G47" t="s">
-        <v>302</v>
-      </c>
-      <c r="H47" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48" t="s">
         <v>295</v>
       </c>
-      <c r="B48" t="s">
-        <v>296</v>
-      </c>
       <c r="C48" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D48" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F48" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G48" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H48" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>294</v>
+      </c>
+      <c r="B49" t="s">
         <v>295</v>
       </c>
-      <c r="B49" t="s">
-        <v>296</v>
-      </c>
       <c r="C49" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D49" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E49" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F49" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G49" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H49" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>294</v>
+      </c>
+      <c r="B50" t="s">
         <v>295</v>
       </c>
-      <c r="B50" t="s">
-        <v>296</v>
-      </c>
       <c r="C50" t="s">
+        <v>328</v>
+      </c>
+      <c r="D50" t="s">
+        <v>307</v>
+      </c>
+      <c r="E50" t="s">
         <v>329</v>
-      </c>
-      <c r="D50" t="s">
-        <v>308</v>
-      </c>
-      <c r="E50" t="s">
-        <v>330</v>
       </c>
       <c r="F50">
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>294</v>
+      </c>
+      <c r="B51" t="s">
         <v>295</v>
       </c>
-      <c r="B51" t="s">
-        <v>296</v>
-      </c>
       <c r="C51" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D51" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E51" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F51">
         <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>294</v>
+      </c>
+      <c r="B52" t="s">
         <v>295</v>
       </c>
-      <c r="B52" t="s">
-        <v>296</v>
-      </c>
       <c r="C52" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D52" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E52" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F52">
         <v>80</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H52" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" t="s">
         <v>295</v>
       </c>
-      <c r="B53" t="s">
-        <v>296</v>
-      </c>
       <c r="C53" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D53" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E53" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F53">
         <v>80</v>
       </c>
       <c r="G53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H53" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>294</v>
+      </c>
+      <c r="B54" t="s">
         <v>295</v>
       </c>
-      <c r="B54" t="s">
-        <v>296</v>
-      </c>
       <c r="C54" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D54" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E54" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F54">
         <v>115</v>
       </c>
       <c r="G54" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H54" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" t="s">
         <v>295</v>
       </c>
-      <c r="B55" t="s">
-        <v>296</v>
-      </c>
       <c r="C55" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D55" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E55" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F55">
         <v>150</v>
       </c>
       <c r="G55" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H55" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>294</v>
+      </c>
+      <c r="B56" t="s">
         <v>295</v>
       </c>
-      <c r="B56" t="s">
-        <v>296</v>
-      </c>
       <c r="C56" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D56" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E56" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F56">
         <v>150</v>
       </c>
       <c r="G56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H56" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>294</v>
+      </c>
+      <c r="B57" t="s">
         <v>295</v>
       </c>
-      <c r="B57" t="s">
-        <v>296</v>
-      </c>
       <c r="C57" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D57" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E57" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F57">
         <v>225</v>
       </c>
       <c r="G57" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H57" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>294</v>
+      </c>
+      <c r="B58" t="s">
         <v>295</v>
       </c>
-      <c r="B58" t="s">
-        <v>296</v>
-      </c>
       <c r="C58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D58" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E58" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F58">
         <v>300</v>
       </c>
       <c r="G58" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H58" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>294</v>
+      </c>
+      <c r="B59" t="s">
         <v>295</v>
       </c>
-      <c r="B59" t="s">
-        <v>296</v>
-      </c>
       <c r="C59" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D59" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F59">
         <v>80</v>
       </c>
       <c r="G59" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H59" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" t="s">
         <v>295</v>
       </c>
-      <c r="B60" t="s">
-        <v>296</v>
-      </c>
       <c r="C60" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D60" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E60" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F60">
         <v>115</v>
       </c>
       <c r="G60" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H60" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" t="s">
         <v>295</v>
       </c>
-      <c r="B61" t="s">
-        <v>296</v>
-      </c>
       <c r="C61" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D61" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E61" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F61">
         <v>150</v>
       </c>
       <c r="G61" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H61" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>294</v>
+      </c>
+      <c r="B62" t="s">
         <v>295</v>
       </c>
-      <c r="B62" t="s">
-        <v>296</v>
-      </c>
       <c r="C62" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D62" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E62" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F62">
         <v>150</v>
       </c>
       <c r="G62" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H62" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" t="s">
         <v>295</v>
       </c>
-      <c r="B63" t="s">
-        <v>296</v>
-      </c>
       <c r="C63" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D63" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E63" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F63">
         <v>225</v>
       </c>
       <c r="G63" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>294</v>
+      </c>
+      <c r="B64" t="s">
         <v>295</v>
       </c>
-      <c r="B64" t="s">
-        <v>296</v>
-      </c>
       <c r="C64" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D64" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E64" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F64">
         <v>300</v>
       </c>
       <c r="G64" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H64" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
+        <v>294</v>
+      </c>
+      <c r="B65" t="s">
         <v>295</v>
       </c>
-      <c r="B65" t="s">
-        <v>296</v>
-      </c>
       <c r="C65" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D65" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E65" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F65">
         <v>150</v>
       </c>
       <c r="G65" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H65" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
+        <v>294</v>
+      </c>
+      <c r="B66" t="s">
         <v>295</v>
       </c>
-      <c r="B66" t="s">
-        <v>296</v>
-      </c>
       <c r="C66" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D66" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E66" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F66">
         <v>225</v>
       </c>
       <c r="G66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H66" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
+        <v>294</v>
+      </c>
+      <c r="B67" t="s">
         <v>295</v>
       </c>
-      <c r="B67" t="s">
-        <v>296</v>
-      </c>
       <c r="C67" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D67" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E67" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F67">
         <v>300</v>
       </c>
       <c r="G67" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H67" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>294</v>
+      </c>
+      <c r="B68" t="s">
         <v>295</v>
       </c>
-      <c r="B68" t="s">
-        <v>296</v>
-      </c>
       <c r="C68" t="s">
+        <v>341</v>
+      </c>
+      <c r="D68" t="s">
+        <v>307</v>
+      </c>
+      <c r="E68" t="s">
+        <v>329</v>
+      </c>
+      <c r="F68" t="s">
         <v>342</v>
-      </c>
-      <c r="D68" t="s">
-        <v>308</v>
-      </c>
-      <c r="E68" t="s">
-        <v>330</v>
-      </c>
-      <c r="F68" t="s">
-        <v>343</v>
       </c>
       <c r="G68" t="s">
         <v>79</v>
       </c>
       <c r="H68" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
+        <v>294</v>
+      </c>
+      <c r="B69" t="s">
         <v>295</v>
       </c>
-      <c r="B69" t="s">
-        <v>296</v>
-      </c>
       <c r="C69" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D69" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F69" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G69" t="s">
         <v>79</v>
       </c>
       <c r="H69" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
+        <v>294</v>
+      </c>
+      <c r="B70" t="s">
         <v>295</v>
       </c>
-      <c r="B70" t="s">
-        <v>296</v>
-      </c>
       <c r="C70" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D70" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E70" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F70" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G70" t="s">
         <v>79</v>
       </c>
       <c r="H70" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
+        <v>294</v>
+      </c>
+      <c r="B71" t="s">
         <v>295</v>
       </c>
-      <c r="B71" t="s">
-        <v>296</v>
-      </c>
       <c r="C71" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D71" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E71" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F71" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G71" t="s">
         <v>79</v>
       </c>
       <c r="H71" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
+        <v>294</v>
+      </c>
+      <c r="B72" t="s">
         <v>295</v>
       </c>
-      <c r="B72" t="s">
-        <v>296</v>
-      </c>
       <c r="C72" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D72" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E72" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F72" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="G72" t="s">
         <v>79</v>
       </c>
       <c r="H72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>294</v>
+      </c>
+      <c r="B73" t="s">
         <v>295</v>
       </c>
-      <c r="B73" t="s">
-        <v>296</v>
-      </c>
       <c r="C73" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D73" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F73" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G73" t="s">
         <v>79</v>
       </c>
       <c r="H73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>294</v>
+      </c>
+      <c r="B74" t="s">
         <v>295</v>
       </c>
-      <c r="B74" t="s">
-        <v>296</v>
-      </c>
       <c r="C74" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E74" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F74" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G74" t="s">
         <v>79</v>
       </c>
       <c r="H74" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" t="s">
         <v>295</v>
       </c>
-      <c r="B75" t="s">
-        <v>296</v>
-      </c>
       <c r="C75" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D75" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E75" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F75" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G75" t="s">
         <v>79</v>
       </c>
       <c r="H75" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
+        <v>294</v>
+      </c>
+      <c r="B76" t="s">
         <v>295</v>
       </c>
-      <c r="B76" t="s">
-        <v>296</v>
-      </c>
       <c r="C76" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D76" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E76" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F76" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G76" t="s">
         <v>79</v>
       </c>
       <c r="H76" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
+        <v>351</v>
+      </c>
+      <c r="B77" t="s">
         <v>352</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>353</v>
       </c>
-      <c r="C77" t="s">
-        <v>354</v>
-      </c>
       <c r="D77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E77" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F77">
         <v>1</v>
       </c>
       <c r="G77" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H77" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B78" t="s">
+        <v>355</v>
+      </c>
+      <c r="C78" t="s">
         <v>356</v>
       </c>
-      <c r="C78" t="s">
-        <v>357</v>
-      </c>
       <c r="D78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F78">
         <v>1</v>
       </c>
       <c r="G78" t="s">
+        <v>357</v>
+      </c>
+      <c r="H78" t="s">
         <v>358</v>
-      </c>
-      <c r="H78" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B79" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C79" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E79" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F79" t="s">
+        <v>359</v>
+      </c>
+      <c r="G79" t="s">
+        <v>257</v>
+      </c>
+      <c r="H79" t="s">
         <v>360</v>
-      </c>
-      <c r="G79" t="s">
-        <v>258</v>
-      </c>
-      <c r="H79" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B80" t="s">
+        <v>361</v>
+      </c>
+      <c r="C80" t="s">
         <v>362</v>
       </c>
-      <c r="C80" t="s">
-        <v>363</v>
-      </c>
       <c r="D80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E80" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F80">
         <v>1</v>
       </c>
       <c r="G80" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H80" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
+        <v>364</v>
+      </c>
+      <c r="B81" t="s">
         <v>365</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>366</v>
       </c>
-      <c r="C81" t="s">
-        <v>367</v>
-      </c>
       <c r="D81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E81" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F81">
         <v>100</v>
       </c>
       <c r="G81" t="s">
+        <v>367</v>
+      </c>
+      <c r="H81" t="s">
         <v>368</v>
-      </c>
-      <c r="H81" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
+        <v>364</v>
+      </c>
+      <c r="B82" t="s">
         <v>365</v>
       </c>
-      <c r="B82" t="s">
-        <v>366</v>
-      </c>
       <c r="C82" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E82" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F82" t="s">
+        <v>369</v>
+      </c>
+      <c r="G82" t="s">
+        <v>257</v>
+      </c>
+      <c r="H82" t="s">
         <v>370</v>
-      </c>
-      <c r="G82" t="s">
-        <v>258</v>
-      </c>
-      <c r="H82" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B83" t="s">
+        <v>371</v>
+      </c>
+      <c r="C83" t="s">
         <v>372</v>
       </c>
-      <c r="C83" t="s">
-        <v>373</v>
-      </c>
       <c r="D83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E83" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F83">
         <v>1</v>
       </c>
       <c r="G83" t="s">
+        <v>373</v>
+      </c>
+      <c r="H83" t="s">
         <v>374</v>
-      </c>
-      <c r="H83" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B84" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C84" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E84" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F84" t="s">
+        <v>375</v>
+      </c>
+      <c r="G84" t="s">
+        <v>257</v>
+      </c>
+      <c r="H84" t="s">
         <v>376</v>
-      </c>
-      <c r="G84" t="s">
-        <v>258</v>
-      </c>
-      <c r="H84" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
+        <v>364</v>
+      </c>
+      <c r="B85" t="s">
         <v>365</v>
       </c>
-      <c r="B85" t="s">
-        <v>366</v>
-      </c>
       <c r="C85" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E85" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F85">
         <v>10</v>
       </c>
       <c r="G85" t="s">
+        <v>378</v>
+      </c>
+      <c r="H85" t="s">
         <v>379</v>
-      </c>
-      <c r="H85" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
+        <v>380</v>
+      </c>
+      <c r="B86" t="s">
         <v>381</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C86" t="s">
         <v>382</v>
       </c>
-      <c r="C86" t="s">
-        <v>383</v>
-      </c>
       <c r="D86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E86" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F86">
         <v>1</v>
       </c>
       <c r="G86" t="s">
+        <v>383</v>
+      </c>
+      <c r="H86" t="s">
         <v>384</v>
-      </c>
-      <c r="H86" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
+        <v>380</v>
+      </c>
+      <c r="B87" t="s">
         <v>381</v>
       </c>
-      <c r="B87" t="s">
-        <v>382</v>
-      </c>
       <c r="C87" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E87" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F87" t="s">
+        <v>385</v>
+      </c>
+      <c r="G87" t="s">
+        <v>257</v>
+      </c>
+      <c r="H87" t="s">
         <v>386</v>
-      </c>
-      <c r="G87" t="s">
-        <v>258</v>
-      </c>
-      <c r="H87" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B88" t="s">
+        <v>387</v>
+      </c>
+      <c r="C88" t="s">
         <v>388</v>
       </c>
-      <c r="C88" t="s">
-        <v>389</v>
-      </c>
       <c r="D88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E88" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F88">
         <v>500</v>
       </c>
       <c r="G88" t="s">
+        <v>389</v>
+      </c>
+      <c r="H88" t="s">
         <v>390</v>
-      </c>
-      <c r="H88" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B89" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C89" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E89" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F89" t="s">
+        <v>391</v>
+      </c>
+      <c r="G89" t="s">
+        <v>257</v>
+      </c>
+      <c r="H89" t="s">
         <v>392</v>
-      </c>
-      <c r="G89" t="s">
-        <v>258</v>
-      </c>
-      <c r="H89" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>393</v>
+      </c>
+      <c r="B90" t="s">
         <v>394</v>
       </c>
-      <c r="B90" t="s">
-        <v>395</v>
-      </c>
       <c r="C90" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E90" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F90">
         <v>250</v>
       </c>
       <c r="G90" t="s">
+        <v>395</v>
+      </c>
+      <c r="H90" t="s">
         <v>396</v>
-      </c>
-      <c r="H90" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B91" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C91" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E91" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F91">
         <v>200</v>
       </c>
       <c r="G91" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H91" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B92" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C92" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E92" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F92">
         <v>250</v>
       </c>
       <c r="G92" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H92" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B93" t="s">
+        <v>401</v>
+      </c>
+      <c r="C93" t="s">
+        <v>255</v>
+      </c>
+      <c r="D93" t="s">
+        <v>229</v>
+      </c>
+      <c r="E93" t="s">
+        <v>229</v>
+      </c>
+      <c r="F93" t="s">
         <v>402</v>
       </c>
-      <c r="C93" t="s">
-        <v>256</v>
-      </c>
-      <c r="D93" t="s">
-        <v>230</v>
-      </c>
-      <c r="E93" t="s">
-        <v>230</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="G93" t="s">
+        <v>257</v>
+      </c>
+      <c r="H93" t="s">
         <v>403</v>
-      </c>
-      <c r="G93" t="s">
-        <v>258</v>
-      </c>
-      <c r="H93" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B94" t="s">
+        <v>404</v>
+      </c>
+      <c r="C94" t="s">
+        <v>288</v>
+      </c>
+      <c r="D94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" t="s">
+        <v>229</v>
+      </c>
+      <c r="F94" t="s">
         <v>405</v>
       </c>
-      <c r="C94" t="s">
-        <v>289</v>
-      </c>
-      <c r="D94" t="s">
-        <v>230</v>
-      </c>
-      <c r="E94" t="s">
-        <v>230</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="G94" t="s">
+        <v>257</v>
+      </c>
+      <c r="H94" t="s">
         <v>406</v>
-      </c>
-      <c r="G94" t="s">
-        <v>258</v>
-      </c>
-      <c r="H94" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>279</v>
+      </c>
+      <c r="B95" t="s">
         <v>280</v>
       </c>
-      <c r="B95" t="s">
-        <v>281</v>
-      </c>
       <c r="C95" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E95" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F95" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G95" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H95" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B96" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D96" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E96" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F96" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G96" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H96" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C97" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D97" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E97" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F97" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="G97" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H97" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
@@ -6613,24 +6610,24 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>408</v>
+      </c>
+      <c r="D1" t="s">
         <v>409</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>410</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>411</v>
-      </c>
-      <c r="F1" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -6644,10 +6641,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -6661,10 +6658,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -6678,10 +6675,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -6695,10 +6692,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -6712,10 +6709,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -6729,7 +6726,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -6743,7 +6740,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -6757,7 +6754,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -6771,7 +6768,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -6785,7 +6782,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -6799,7 +6796,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -6813,7 +6810,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -6827,7 +6824,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -6841,7 +6838,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -6855,7 +6852,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B17">
         <v>13</v>
@@ -6869,7 +6866,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18">
         <v>16</v>
@@ -6883,7 +6880,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B19">
         <v>13</v>
@@ -6897,7 +6894,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20">
         <v>16</v>
@@ -6915,16 +6912,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="484d85e35f7b2f24491f05f08eca660b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f826ed3232af6d38e82027660e1ae8c6" ns2:_="">
     <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
@@ -7102,6 +7089,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7112,16 +7109,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA26F4-5D97-47BE-ADC1-EEDEEFE4A973}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7139,6 +7126,16 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
   <ds:schemaRefs>

--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674A5B5E-30E8-4204-95E3-B283199867A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46B126-8CE5-4EC8-A659-DCC65DD3C24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="265">
   <si>
     <t>Category</t>
   </si>
@@ -100,9 +100,6 @@
     <t>Input</t>
   </si>
   <si>
-    <t>Coverage Area (m²)</t>
-  </si>
-  <si>
     <t>NCC Specification 20 (S20C2–S20C8) / E2D3–E2D20 (class-specific) / AS 1670.1</t>
   </si>
   <si>
@@ -133,9 +130,6 @@
     <t>Manual Call Point</t>
   </si>
   <si>
-    <t>Total Quantity</t>
-  </si>
-  <si>
     <t>Fire Indicator Panels</t>
   </si>
   <si>
@@ -227,9 +221,6 @@
   </si>
   <si>
     <t>Speaker</t>
-  </si>
-  <si>
-    <t>Total Quantity,Coverage Area</t>
   </si>
   <si>
     <t xml:space="preserve">Speaker types may vary depending on the acoustic and operational requirements of the area.
@@ -288,9 +279,6 @@
     <t>Emergency Luminaire</t>
   </si>
   <si>
-    <t>Total Quantity,Grid Spacing,Coverage Area</t>
-  </si>
-  <si>
     <t>NCC E4D2 / E4D3 / AS/NZS 2293.1</t>
   </si>
   <si>
@@ -529,9 +517,6 @@
   </si>
   <si>
     <t>galvanised mild steel</t>
-  </si>
-  <si>
-    <t>Total Quantity,Formula</t>
   </si>
   <si>
     <t>NCC Part E1 Specification 17 /  Refer to AS 2118.1:2017 Clause 7.10 for sprinkler pipework material requirements</t>
@@ -848,6 +833,9 @@
   </si>
   <si>
     <t>number_of_storey * ROUNDUP(floor_area_per_storey / extinguisher_coverage_area)</t>
+  </si>
+  <si>
+    <t>Coverage Area,Grid Spacing</t>
   </si>
 </sst>
 </file>
@@ -1371,14 +1359,14 @@
         <v>19</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="L2" s="11" t="s">
         <v>21</v>
-      </c>
-      <c r="L2" s="11" t="s">
-        <v>22</v>
       </c>
       <c r="M2" s="11"/>
     </row>
@@ -1393,28 +1381,28 @@
         <v>14</v>
       </c>
       <c r="D3" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F3" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>25</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>26</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1428,22 +1416,19 @@
         <v>14</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>29</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>30</v>
       </c>
       <c r="H4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="L4" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1457,25 +1442,22 @@
         <v>14</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" s="11">
         <v>1</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="K5" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1489,16 +1471,16 @@
         <v>14</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1512,16 +1494,16 @@
         <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1535,16 +1517,16 @@
         <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1558,16 +1540,16 @@
         <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1581,16 +1563,16 @@
         <v>14</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1601,25 +1583,25 @@
         <v>13</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="G11" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>45</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>19</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>20</v>
+        <v>264</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1630,22 +1612,19 @@
         <v>13</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="L12" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1656,22 +1635,22 @@
         <v>13</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1682,22 +1661,22 @@
         <v>13</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1708,22 +1687,22 @@
         <v>13</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1734,26 +1713,26 @@
         <v>13</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M16" s="1"/>
     </row>
@@ -1762,31 +1741,28 @@
         <v>2</v>
       </c>
       <c r="B17" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>56</v>
       </c>
       <c r="F17" s="16">
         <v>1</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H17" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="I17" s="16" t="s">
-        <v>31</v>
-      </c>
       <c r="K17" s="16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L17" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="16" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1794,34 +1770,34 @@
         <v>2</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="G18" s="16" t="s">
         <v>60</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G18" s="16" t="s">
-        <v>62</v>
       </c>
       <c r="H18" s="16" t="s">
         <v>19</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1829,25 +1805,25 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1855,33 +1831,33 @@
         <v>2</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H20" s="16" t="s">
         <v>19</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>63</v>
+        <v>264</v>
       </c>
       <c r="J20" s="16"/>
       <c r="K20" s="16" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M20" s="16"/>
     </row>
@@ -1890,34 +1866,34 @@
         <v>2</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="L21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1925,25 +1901,25 @@
         <v>2</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1951,28 +1927,28 @@
         <v>3</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>81</v>
       </c>
       <c r="H23" s="11" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="K23" s="11" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -1980,34 +1956,31 @@
         <v>3</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G24" s="11" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H24" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I24" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="K24" s="11" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="18" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2015,22 +1988,22 @@
         <v>4</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="H25" s="16" t="s">
         <v>19</v>
@@ -2038,10 +2011,10 @@
       <c r="I25" s="16"/>
       <c r="J25" s="16"/>
       <c r="K25" s="16" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M25" s="16"/>
     </row>
@@ -2050,25 +2023,25 @@
         <v>4</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="16" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2076,31 +2049,31 @@
         <v>4</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2108,33 +2081,31 @@
         <v>4</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M28" s="1"/>
     </row>
@@ -2143,28 +2114,28 @@
         <v>5</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L29" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M29" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2172,28 +2143,28 @@
         <v>5</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G30" s="11" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M30" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2201,28 +2172,28 @@
         <v>5</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L31" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M31" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2230,28 +2201,28 @@
         <v>5</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M32" s="11" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2259,25 +2230,25 @@
         <v>5</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="L33" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2285,25 +2256,25 @@
         <v>5</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C34" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="D34" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>124</v>
-      </c>
       <c r="G34" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2311,25 +2282,25 @@
         <v>5</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2337,22 +2308,22 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2360,25 +2331,25 @@
         <v>5</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2386,22 +2357,22 @@
         <v>5</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2409,28 +2380,28 @@
         <v>5</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="K39" s="11" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L39" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2438,22 +2409,22 @@
         <v>5</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L40" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2461,25 +2432,25 @@
         <v>5</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C41" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="G41" s="11" t="s">
         <v>142</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>146</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L41" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2487,22 +2458,22 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="43" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2510,22 +2481,22 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2533,22 +2504,22 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2556,22 +2527,22 @@
         <v>5</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2579,22 +2550,22 @@
         <v>5</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2602,35 +2573,35 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
+        <v>151</v>
+      </c>
+      <c r="C47" t="s">
+        <v>152</v>
+      </c>
+      <c r="D47" t="s">
+        <v>153</v>
+      </c>
+      <c r="E47" t="s">
+        <v>154</v>
+      </c>
+      <c r="F47" t="s">
         <v>155</v>
       </c>
-      <c r="C47" t="s">
-        <v>156</v>
-      </c>
-      <c r="D47" t="s">
-        <v>157</v>
-      </c>
-      <c r="E47" t="s">
-        <v>158</v>
-      </c>
-      <c r="F47" t="s">
-        <v>159</v>
-      </c>
       <c r="G47" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>82</v>
+        <v>264</v>
       </c>
       <c r="J47"/>
       <c r="K47" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="L47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M47"/>
     </row>
@@ -2639,33 +2610,31 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C48" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D48" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E48" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
       </c>
-      <c r="I48" t="s">
-        <v>163</v>
-      </c>
+      <c r="I48"/>
       <c r="J48"/>
       <c r="K48" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M48"/>
     </row>
@@ -2674,22 +2643,22 @@
         <v>6</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2697,25 +2666,25 @@
         <v>6</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2723,31 +2692,31 @@
         <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2755,25 +2724,25 @@
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D52" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="G52" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="53" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2781,25 +2750,25 @@
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:13" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.4">
@@ -2807,22 +2776,22 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C54" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D54" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="E54" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="F54" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="H54" t="s">
         <v>19</v>
@@ -2830,10 +2799,10 @@
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="L54" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M54"/>
     </row>
@@ -2842,20 +2811,20 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C55" t="s">
+        <v>168</v>
+      </c>
+      <c r="D55" t="s">
         <v>173</v>
-      </c>
-      <c r="D55" t="s">
-        <v>178</v>
       </c>
       <c r="E55"/>
       <c r="F55" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G55" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H55" t="s">
         <v>19</v>
@@ -2871,28 +2840,28 @@
         <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2900,19 +2869,19 @@
         <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2920,22 +2889,22 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L58" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="59" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2943,28 +2912,28 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="E59" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>184</v>
-      </c>
-      <c r="D59" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="E59" s="11" t="s">
-        <v>188</v>
-      </c>
       <c r="G59" s="11" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2972,25 +2941,25 @@
         <v>7</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L60" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:13" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2998,30 +2967,30 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D61" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E61"/>
       <c r="F61" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="H61" t="s">
         <v>19</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="K61" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="L61"/>
       <c r="M61"/>
@@ -3031,18 +3000,18 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
+        <v>186</v>
+      </c>
+      <c r="C62" t="s">
+        <v>187</v>
+      </c>
+      <c r="D62" t="s">
         <v>191</v>
-      </c>
-      <c r="C62" t="s">
-        <v>192</v>
-      </c>
-      <c r="D62" t="s">
-        <v>196</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H62" t="s">
         <v>19</v>
@@ -3050,10 +3019,10 @@
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L62" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="M62"/>
     </row>
@@ -3062,22 +3031,22 @@
         <v>8</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3085,26 +3054,23 @@
         <v>9</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="E64" s="15"/>
       <c r="G64" s="11" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I64" s="11" t="s">
-        <v>31</v>
-      </c>
       <c r="L64" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3112,28 +3078,28 @@
         <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="H65" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3141,25 +3107,25 @@
         <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67" spans="1:13" s="6" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3167,23 +3133,23 @@
         <v>10</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
       <c r="G67" s="1"/>
       <c r="H67" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -3194,19 +3160,19 @@
         <v>10</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="69" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3214,19 +3180,19 @@
         <v>10</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="70" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3234,19 +3200,19 @@
         <v>10</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>215</v>
-      </c>
       <c r="H70" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3254,23 +3220,23 @@
         <v>10</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C71" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>211</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I71" s="1"/>
       <c r="J71" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -3322,1718 +3288,1718 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F1" t="s">
         <v>217</v>
       </c>
-      <c r="B1" t="s">
+      <c r="G1" t="s">
         <v>218</v>
       </c>
-      <c r="C1" t="s">
+      <c r="H1" t="s">
         <v>219</v>
       </c>
-      <c r="D1" t="s">
+      <c r="I1" t="s">
         <v>220</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" t="s">
         <v>221</v>
-      </c>
-      <c r="F1" t="s">
-        <v>222</v>
-      </c>
-      <c r="G1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H1" t="s">
-        <v>224</v>
-      </c>
-      <c r="I1" t="s">
-        <v>225</v>
-      </c>
-      <c r="J1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H2">
         <v>104.04</v>
       </c>
       <c r="I2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H3">
         <v>51.84</v>
       </c>
       <c r="I3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G4" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H4">
         <v>250</v>
       </c>
       <c r="I4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G6" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H6">
         <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H7">
         <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G8" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B10" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C10" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G10" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H10">
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J10" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G11" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H11">
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J11" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>231</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
         <v>236</v>
       </c>
-      <c r="B12" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" t="s">
-        <v>241</v>
-      </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="G12" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H12">
         <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J12" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B14" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C14" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D14" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E14" t="s">
+        <v>236</v>
+      </c>
+      <c r="F14" t="s">
+        <v>240</v>
+      </c>
+      <c r="G14" t="s">
         <v>241</v>
-      </c>
-      <c r="F14" t="s">
-        <v>245</v>
-      </c>
-      <c r="G14" t="s">
-        <v>246</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J14" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B15" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" t="s">
+        <v>236</v>
+      </c>
+      <c r="F15" t="s">
+        <v>240</v>
+      </c>
+      <c r="G15" t="s">
         <v>243</v>
-      </c>
-      <c r="C15" t="s">
-        <v>244</v>
-      </c>
-      <c r="D15" t="s">
-        <v>237</v>
-      </c>
-      <c r="E15" t="s">
-        <v>241</v>
-      </c>
-      <c r="F15" t="s">
-        <v>245</v>
-      </c>
-      <c r="G15" t="s">
-        <v>248</v>
       </c>
       <c r="H15">
         <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J15" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" t="s">
+        <v>232</v>
+      </c>
+      <c r="E16" t="s">
+        <v>236</v>
+      </c>
+      <c r="F16" t="s">
+        <v>240</v>
+      </c>
+      <c r="G16" t="s">
         <v>244</v>
-      </c>
-      <c r="D16" t="s">
-        <v>237</v>
-      </c>
-      <c r="E16" t="s">
-        <v>241</v>
-      </c>
-      <c r="F16" t="s">
-        <v>245</v>
-      </c>
-      <c r="G16" t="s">
-        <v>249</v>
       </c>
       <c r="H16">
         <v>450</v>
       </c>
       <c r="I16" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J16" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C17" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D17" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E17" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F17" t="s">
+        <v>240</v>
+      </c>
+      <c r="G17" t="s">
         <v>245</v>
-      </c>
-      <c r="G17" t="s">
-        <v>250</v>
       </c>
       <c r="H17">
         <v>675</v>
       </c>
       <c r="I17" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J17" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B18" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C18" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D18" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E18" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F18" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G18" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H18">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J18" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B19" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C19" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D19" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E19" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F19" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G19" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H19">
         <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J19" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B20" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C20" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D20" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E20" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F20" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G20" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H20">
         <v>80</v>
       </c>
       <c r="I20" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J20" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B22" t="s">
+        <v>238</v>
+      </c>
+      <c r="C22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" t="s">
+        <v>232</v>
+      </c>
+      <c r="E22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" t="s">
+        <v>240</v>
+      </c>
+      <c r="G22" t="s">
         <v>243</v>
-      </c>
-      <c r="C22" t="s">
-        <v>244</v>
-      </c>
-      <c r="D22" t="s">
-        <v>237</v>
-      </c>
-      <c r="E22" t="s">
-        <v>240</v>
-      </c>
-      <c r="F22" t="s">
-        <v>245</v>
-      </c>
-      <c r="G22" t="s">
-        <v>248</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J22" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B23" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>232</v>
+      </c>
+      <c r="E23" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" t="s">
+        <v>240</v>
+      </c>
+      <c r="G23" t="s">
         <v>244</v>
-      </c>
-      <c r="D23" t="s">
-        <v>237</v>
-      </c>
-      <c r="E23" t="s">
-        <v>240</v>
-      </c>
-      <c r="F23" t="s">
-        <v>245</v>
-      </c>
-      <c r="G23" t="s">
-        <v>249</v>
       </c>
       <c r="H23">
         <v>300</v>
       </c>
       <c r="I23" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J23" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C24" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E24" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" t="s">
         <v>240</v>
       </c>
-      <c r="F24" t="s">
+      <c r="G24" t="s">
         <v>245</v>
-      </c>
-      <c r="G24" t="s">
-        <v>250</v>
       </c>
       <c r="H24">
         <v>450</v>
       </c>
       <c r="I24" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J24" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B25" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C25" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D25" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E25" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" t="s">
         <v>240</v>
       </c>
-      <c r="F25" t="s">
-        <v>245</v>
-      </c>
       <c r="G25" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H25">
         <v>675</v>
       </c>
       <c r="I25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J25" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C26" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E26" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" t="s">
         <v>240</v>
       </c>
-      <c r="F26" t="s">
-        <v>245</v>
-      </c>
       <c r="G26" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J26" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B27" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D27" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E27" t="s">
+        <v>235</v>
+      </c>
+      <c r="F27" t="s">
         <v>240</v>
       </c>
-      <c r="F27" t="s">
-        <v>245</v>
-      </c>
       <c r="G27" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H27">
         <v>115</v>
       </c>
       <c r="I27" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J27" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B28" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E28" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" t="s">
         <v>240</v>
       </c>
-      <c r="F28" t="s">
-        <v>245</v>
-      </c>
       <c r="G28" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H28">
         <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J28" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B30" t="s">
+        <v>238</v>
+      </c>
+      <c r="C30" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" t="s">
+        <v>232</v>
+      </c>
+      <c r="E30" t="s">
+        <v>233</v>
+      </c>
+      <c r="F30" t="s">
+        <v>240</v>
+      </c>
+      <c r="G30" t="s">
         <v>243</v>
-      </c>
-      <c r="C30" t="s">
-        <v>244</v>
-      </c>
-      <c r="D30" t="s">
-        <v>237</v>
-      </c>
-      <c r="E30" t="s">
-        <v>238</v>
-      </c>
-      <c r="F30" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" t="s">
-        <v>248</v>
       </c>
       <c r="H30">
         <v>150</v>
       </c>
       <c r="I30" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J30" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B31" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C31" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" t="s">
+        <v>232</v>
+      </c>
+      <c r="E31" t="s">
+        <v>233</v>
+      </c>
+      <c r="F31" t="s">
+        <v>240</v>
+      </c>
+      <c r="G31" t="s">
         <v>244</v>
-      </c>
-      <c r="D31" t="s">
-        <v>237</v>
-      </c>
-      <c r="E31" t="s">
-        <v>238</v>
-      </c>
-      <c r="F31" t="s">
-        <v>245</v>
-      </c>
-      <c r="G31" t="s">
-        <v>249</v>
       </c>
       <c r="H31">
         <v>200</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J31" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B32" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C32" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D32" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E32" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F32" t="s">
+        <v>240</v>
+      </c>
+      <c r="G32" t="s">
         <v>245</v>
-      </c>
-      <c r="G32" t="s">
-        <v>250</v>
       </c>
       <c r="H32">
         <v>300</v>
       </c>
       <c r="I32" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J32" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B33" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C33" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D33" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E33" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F33" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G33" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H33">
         <v>450</v>
       </c>
       <c r="I33" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J33" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C34" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D34" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E34" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F34" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G34" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H34">
         <v>675</v>
       </c>
       <c r="I34" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J34" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B35" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C35" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D35" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E35" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F35" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G35" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H35">
         <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J35" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C36" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D36" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E36" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F36" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G36" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="H36">
         <v>225</v>
       </c>
       <c r="I36" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B37" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C37" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D37" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E37" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F37" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G37" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H37">
         <v>300</v>
       </c>
       <c r="I37" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J37" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B39" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C39" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D39" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E39" t="s">
+        <v>236</v>
+      </c>
+      <c r="F39" t="s">
+        <v>240</v>
+      </c>
+      <c r="G39" t="s">
         <v>241</v>
-      </c>
-      <c r="F39" t="s">
-        <v>245</v>
-      </c>
-      <c r="G39" t="s">
-        <v>246</v>
       </c>
       <c r="H39">
         <v>150</v>
       </c>
       <c r="I39" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J39" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B40" t="s">
+        <v>238</v>
+      </c>
+      <c r="C40" t="s">
+        <v>256</v>
+      </c>
+      <c r="D40" t="s">
+        <v>232</v>
+      </c>
+      <c r="E40" t="s">
+        <v>236</v>
+      </c>
+      <c r="F40" t="s">
+        <v>240</v>
+      </c>
+      <c r="G40" t="s">
         <v>243</v>
-      </c>
-      <c r="C40" t="s">
-        <v>261</v>
-      </c>
-      <c r="D40" t="s">
-        <v>237</v>
-      </c>
-      <c r="E40" t="s">
-        <v>241</v>
-      </c>
-      <c r="F40" t="s">
-        <v>245</v>
-      </c>
-      <c r="G40" t="s">
-        <v>248</v>
       </c>
       <c r="H40">
         <v>450</v>
       </c>
       <c r="I40" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J40" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B41" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C41" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D41" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E41" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F41" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G41" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H41">
         <v>675</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J41" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D42" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E42" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F42" t="s">
+        <v>240</v>
+      </c>
+      <c r="G42" t="s">
         <v>245</v>
-      </c>
-      <c r="G42" t="s">
-        <v>250</v>
       </c>
       <c r="H42">
         <v>1000</v>
       </c>
       <c r="I42" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J42" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C43" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D43" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E43" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F43" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G43" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="H43">
         <v>80</v>
       </c>
       <c r="I43" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J43" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B44" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D44" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E44" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F44" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G44" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="H44">
         <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J44" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C45" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D45" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E45" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F45" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G45" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H45">
         <v>150</v>
       </c>
       <c r="I45" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J45" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C47" t="s">
+        <v>256</v>
+      </c>
+      <c r="D47" t="s">
+        <v>232</v>
+      </c>
+      <c r="E47" t="s">
+        <v>235</v>
+      </c>
+      <c r="F47" t="s">
+        <v>240</v>
+      </c>
+      <c r="G47" t="s">
         <v>243</v>
-      </c>
-      <c r="C47" t="s">
-        <v>261</v>
-      </c>
-      <c r="D47" t="s">
-        <v>237</v>
-      </c>
-      <c r="E47" t="s">
-        <v>240</v>
-      </c>
-      <c r="F47" t="s">
-        <v>245</v>
-      </c>
-      <c r="G47" t="s">
-        <v>248</v>
       </c>
       <c r="H47">
         <v>150</v>
       </c>
       <c r="I47" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J47" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B48" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C48" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D48" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E48" t="s">
+        <v>235</v>
+      </c>
+      <c r="F48" t="s">
         <v>240</v>
       </c>
-      <c r="F48" t="s">
-        <v>245</v>
-      </c>
       <c r="G48" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H48">
         <v>450</v>
       </c>
       <c r="I48" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J48" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C49" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D49" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E49" t="s">
+        <v>235</v>
+      </c>
+      <c r="F49" t="s">
         <v>240</v>
       </c>
-      <c r="F49" t="s">
+      <c r="G49" t="s">
         <v>245</v>
-      </c>
-      <c r="G49" t="s">
-        <v>250</v>
       </c>
       <c r="H49">
         <v>675</v>
       </c>
       <c r="I49" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J49" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B50" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C50" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D50" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E50" t="s">
+        <v>235</v>
+      </c>
+      <c r="F50" t="s">
         <v>240</v>
       </c>
-      <c r="F50" t="s">
-        <v>245</v>
-      </c>
       <c r="G50" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H50">
         <v>1000</v>
       </c>
       <c r="I50" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J50" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B51" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D51" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E51" t="s">
+        <v>235</v>
+      </c>
+      <c r="F51" t="s">
         <v>240</v>
       </c>
-      <c r="F51" t="s">
-        <v>245</v>
-      </c>
       <c r="G51" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="H51">
         <v>150</v>
       </c>
       <c r="I51" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J51" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C52" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D52" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E52" t="s">
+        <v>235</v>
+      </c>
+      <c r="F52" t="s">
         <v>240</v>
       </c>
-      <c r="F52" t="s">
-        <v>245</v>
-      </c>
       <c r="G52" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H52">
         <v>225</v>
       </c>
       <c r="I52" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J52" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B53" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E53" t="s">
+        <v>235</v>
+      </c>
+      <c r="F53" t="s">
         <v>240</v>
       </c>
-      <c r="F53" t="s">
-        <v>245</v>
-      </c>
       <c r="G53" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H53">
         <v>300</v>
       </c>
       <c r="I53" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J53" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B55" t="s">
+        <v>238</v>
+      </c>
+      <c r="C55" t="s">
+        <v>256</v>
+      </c>
+      <c r="D55" t="s">
+        <v>232</v>
+      </c>
+      <c r="E55" t="s">
+        <v>233</v>
+      </c>
+      <c r="F55" t="s">
+        <v>240</v>
+      </c>
+      <c r="G55" t="s">
         <v>243</v>
-      </c>
-      <c r="C55" t="s">
-        <v>261</v>
-      </c>
-      <c r="D55" t="s">
-        <v>237</v>
-      </c>
-      <c r="E55" t="s">
-        <v>238</v>
-      </c>
-      <c r="F55" t="s">
-        <v>245</v>
-      </c>
-      <c r="G55" t="s">
-        <v>248</v>
       </c>
       <c r="H55">
         <v>225</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J55" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C56" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D56" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E56" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F56" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G56" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="H56">
         <v>300</v>
       </c>
       <c r="I56" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J56" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B57" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C57" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D57" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E57" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F57" t="s">
+        <v>240</v>
+      </c>
+      <c r="G57" t="s">
         <v>245</v>
-      </c>
-      <c r="G57" t="s">
-        <v>250</v>
       </c>
       <c r="H57">
         <v>450</v>
       </c>
       <c r="I57" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J57" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B58" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C58" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D58" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E58" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F58" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G58" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="H58">
         <v>675</v>
       </c>
       <c r="I58" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J58" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B59" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C59" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D59" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E59" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F59" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G59" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H59">
         <v>1000</v>
       </c>
       <c r="I59" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J59" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B60" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C60" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E60" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F60" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G60" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="H60">
         <v>150</v>
       </c>
       <c r="I60" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J60" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B61" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C61" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D61" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E61" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F61" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G61" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="H61">
         <v>225</v>
       </c>
       <c r="I61" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J61" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B62" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C62" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D62" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E62" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F62" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G62" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="H62">
         <v>300</v>
       </c>
       <c r="I62" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="J62" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5059,24 +5025,24 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="E1" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F1" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5090,10 +5056,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5107,10 +5073,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5124,10 +5090,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5141,10 +5107,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5158,10 +5124,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5175,7 +5141,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5189,7 +5155,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5203,7 +5169,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5217,7 +5183,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5231,7 +5197,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5245,7 +5211,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5259,7 +5225,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5273,7 +5239,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -5287,7 +5253,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -5301,7 +5267,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>30</v>
@@ -5315,7 +5281,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C18">
         <v>60</v>
@@ -5329,7 +5295,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C19">
         <v>90</v>
@@ -5343,7 +5309,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C20">
         <v>120</v>
@@ -5361,25 +5327,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="484d85e35f7b2f24491f05f08eca660b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f826ed3232af6d38e82027660e1ae8c6" ns2:_="">
     <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
@@ -5557,10 +5504,39 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA26F4-5D97-47BE-ADC1-EEDEEFE4A973}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -5576,19 +5552,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA26F4-5D97-47BE-ADC1-EEDEEFE4A973}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/database/databases/Standards_Calc_Database_Finalised.xlsx
+++ b/database/databases/Standards_Calc_Database_Finalised.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\JFC-Embodied-Carbon-App\database\databases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC46B126-8CE5-4EC8-A659-DCC65DD3C24D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025C7300-5B24-45CD-8129-C85456AA6CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="264">
   <si>
     <t>Category</t>
   </si>
@@ -328,9 +328,6 @@
   </si>
   <si>
     <t>19 mm hose reel, 25 mm hose reel</t>
-  </si>
-  <si>
-    <t>Hose reel , Cabinet, Fire Hose Reel, Hose reel valve</t>
   </si>
   <si>
     <t>NCC E1D3(2) / E1D3(1)(a) exemption Cl 2,3,5 / AS 1221</t>
@@ -1359,7 +1356,7 @@
         <v>19</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J2" s="11"/>
       <c r="K2" s="11" t="s">
@@ -1396,7 +1393,7 @@
         <v>19</v>
       </c>
       <c r="I3" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K3" s="11" t="s">
         <v>26</v>
@@ -1598,7 +1595,7 @@
         <v>19</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="L11" s="11" t="s">
         <v>21</v>
@@ -1791,7 +1788,7 @@
         <v>19</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>61</v>
@@ -1850,7 +1847,7 @@
         <v>19</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J20" s="16"/>
       <c r="K20" s="16" t="s">
@@ -1884,7 +1881,7 @@
         <v>34</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J21" s="1" t="s">
         <v>35</v>
@@ -1942,7 +1939,7 @@
         <v>19</v>
       </c>
       <c r="I23" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K23" s="11" t="s">
         <v>79</v>
@@ -2000,7 +1997,7 @@
         <v>88</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G25" s="16" t="s">
         <v>87</v>
@@ -2064,16 +2061,16 @@
         <v>28</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H27" s="16" t="s">
         <v>19</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="L27" s="16" t="s">
         <v>97</v>
-      </c>
-      <c r="L27" s="16" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2087,14 +2084,14 @@
         <v>93</v>
       </c>
       <c r="D28" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="F28" s="1"/>
       <c r="G28" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>34</v>
@@ -2102,7 +2099,7 @@
       <c r="I28" s="1"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L28" s="1" t="s">
         <v>74</v>
@@ -2114,28 +2111,28 @@
         <v>5</v>
       </c>
       <c r="B29" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="D29" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="G29" s="11" t="s">
         <v>105</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>106</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L29" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="M29" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="M29" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2143,28 +2140,28 @@
         <v>5</v>
       </c>
       <c r="B30" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="D30" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>111</v>
       </c>
       <c r="H30" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L30" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="M30" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="M30" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2172,28 +2169,28 @@
         <v>5</v>
       </c>
       <c r="B31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="D31" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>112</v>
-      </c>
-      <c r="G31" s="11" t="s">
-        <v>113</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L31" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="M31" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="M31" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2201,28 +2198,28 @@
         <v>5</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="D32" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>114</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>115</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L32" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="M32" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="M32" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2230,22 +2227,22 @@
         <v>5</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C33" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="D33" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="G33" s="11" t="s">
         <v>117</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>118</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K33" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L33" s="11" t="s">
         <v>21</v>
@@ -2256,25 +2253,25 @@
         <v>5</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D34" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G34" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="H34" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K34" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="35" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2282,25 +2279,25 @@
         <v>5</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D35" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="G35" s="11" t="s">
         <v>123</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>124</v>
       </c>
       <c r="H35" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K35" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L35" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2308,13 +2305,13 @@
         <v>5</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>34</v>
@@ -2323,7 +2320,7 @@
         <v>35</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2331,25 +2328,25 @@
         <v>5</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D37" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>128</v>
-      </c>
-      <c r="G37" s="11" t="s">
-        <v>129</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K37" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L37" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2357,22 +2354,22 @@
         <v>5</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D38" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G38" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L38" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2380,25 +2377,25 @@
         <v>5</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C39" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="D39" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="G39" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G39" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J39" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="K39" s="11" t="s">
         <v>136</v>
-      </c>
-      <c r="K39" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="L39" s="11" t="s">
         <v>21</v>
@@ -2409,16 +2406,16 @@
         <v>5</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C40" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="D40" s="11" t="s">
+      <c r="G40" s="11" t="s">
         <v>139</v>
-      </c>
-      <c r="G40" s="11" t="s">
-        <v>140</v>
       </c>
       <c r="H40" s="11" t="s">
         <v>19</v>
@@ -2432,22 +2429,22 @@
         <v>5</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G41" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="G41" s="11" t="s">
-        <v>142</v>
       </c>
       <c r="H41" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J41" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L41" s="11" t="s">
         <v>21</v>
@@ -2458,13 +2455,13 @@
         <v>5</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H42" s="1" t="s">
         <v>34</v>
@@ -2481,13 +2478,13 @@
         <v>5</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>34</v>
@@ -2504,13 +2501,13 @@
         <v>5</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H44" s="1" t="s">
         <v>34</v>
@@ -2527,22 +2524,22 @@
         <v>5</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="G45" s="11" t="s">
         <v>148</v>
-      </c>
-      <c r="G45" s="11" t="s">
-        <v>149</v>
       </c>
       <c r="H45" s="11" t="s">
         <v>19</v>
       </c>
       <c r="L45" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2550,13 +2547,13 @@
         <v>5</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H46" s="1" t="s">
         <v>34</v>
@@ -2565,7 +2562,7 @@
         <v>35</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:13" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2573,32 +2570,32 @@
         <v>6</v>
       </c>
       <c r="B47" t="s">
+        <v>150</v>
+      </c>
+      <c r="C47" t="s">
         <v>151</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>152</v>
       </c>
-      <c r="D47" t="s">
+      <c r="E47" t="s">
         <v>153</v>
       </c>
-      <c r="E47" t="s">
+      <c r="F47" t="s">
         <v>154</v>
       </c>
-      <c r="F47" t="s">
-        <v>155</v>
-      </c>
       <c r="G47" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H47" t="s">
         <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J47"/>
       <c r="K47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L47" t="s">
         <v>21</v>
@@ -2610,20 +2607,20 @@
         <v>6</v>
       </c>
       <c r="B48" t="s">
+        <v>150</v>
+      </c>
+      <c r="C48" t="s">
         <v>151</v>
       </c>
-      <c r="C48" t="s">
-        <v>152</v>
-      </c>
       <c r="D48" t="s">
+        <v>156</v>
+      </c>
+      <c r="E48" t="s">
         <v>157</v>
-      </c>
-      <c r="E48" t="s">
-        <v>158</v>
       </c>
       <c r="F48" s="9"/>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H48" t="s">
         <v>19</v>
@@ -2631,7 +2628,7 @@
       <c r="I48"/>
       <c r="J48"/>
       <c r="K48" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="L48" t="s">
         <v>74</v>
@@ -2643,16 +2640,16 @@
         <v>6</v>
       </c>
       <c r="B49" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C49" s="1" t="s">
-        <v>152</v>
-      </c>
       <c r="D49" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H49" s="1" t="s">
         <v>34</v>
@@ -2666,16 +2663,16 @@
         <v>6</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="G50" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>34</v>
@@ -2692,19 +2689,19 @@
         <v>6</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D51" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="E51" s="1" t="s">
-        <v>164</v>
-      </c>
       <c r="G51" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H51" s="1" t="s">
         <v>34</v>
@@ -2713,7 +2710,7 @@
         <v>35</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>74</v>
@@ -2724,16 +2721,16 @@
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H52" s="1" t="s">
         <v>34</v>
@@ -2750,16 +2747,16 @@
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>34</v>
@@ -2776,22 +2773,22 @@
         <v>6</v>
       </c>
       <c r="B54" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C54" t="s">
+        <v>167</v>
+      </c>
+      <c r="D54" t="s">
         <v>168</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>169</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" t="s">
         <v>170</v>
       </c>
-      <c r="F54" t="s">
-        <v>171</v>
-      </c>
       <c r="G54" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H54" t="s">
         <v>19</v>
@@ -2799,7 +2796,7 @@
       <c r="I54"/>
       <c r="J54"/>
       <c r="K54" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="L54" t="s">
         <v>46</v>
@@ -2811,20 +2808,20 @@
         <v>6</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E55"/>
       <c r="F55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="G55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H55" t="s">
         <v>19</v>
@@ -2840,19 +2837,19 @@
         <v>6</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D56" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="E56" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H56" s="1" t="s">
         <v>34</v>
@@ -2861,7 +2858,7 @@
         <v>35</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2869,13 +2866,13 @@
         <v>6</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H57" s="1" t="s">
         <v>34</v>
@@ -2889,16 +2886,16 @@
         <v>7</v>
       </c>
       <c r="B58" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C58" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="D58" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="G58" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="G58" s="11" t="s">
-        <v>181</v>
       </c>
       <c r="H58" s="11" t="s">
         <v>19</v>
@@ -2912,28 +2909,28 @@
         <v>7</v>
       </c>
       <c r="B59" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C59" s="11" t="s">
-        <v>179</v>
-      </c>
       <c r="D59" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E59" s="11" t="s">
-        <v>183</v>
-      </c>
       <c r="G59" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H59" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="L59" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -2941,22 +2938,22 @@
         <v>7</v>
       </c>
       <c r="B60" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="C60" s="11" t="s">
-        <v>179</v>
-      </c>
       <c r="D60" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H60" s="11" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L60" s="11" t="s">
         <v>21</v>
@@ -2967,30 +2964,30 @@
         <v>8</v>
       </c>
       <c r="B61" t="s">
+        <v>185</v>
+      </c>
+      <c r="C61" t="s">
         <v>186</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
         <v>187</v>
-      </c>
-      <c r="D61" t="s">
-        <v>188</v>
       </c>
       <c r="E61"/>
       <c r="F61" t="s">
         <v>28</v>
       </c>
       <c r="G61" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H61" t="s">
         <v>19</v>
       </c>
       <c r="I61"/>
       <c r="J61" t="s">
+        <v>188</v>
+      </c>
+      <c r="K61" t="s">
         <v>189</v>
-      </c>
-      <c r="K61" t="s">
-        <v>190</v>
       </c>
       <c r="L61"/>
       <c r="M61"/>
@@ -3000,18 +2997,18 @@
         <v>8</v>
       </c>
       <c r="B62" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" t="s">
         <v>186</v>
       </c>
-      <c r="C62" t="s">
-        <v>187</v>
-      </c>
       <c r="D62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E62"/>
       <c r="F62"/>
       <c r="G62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H62" t="s">
         <v>19</v>
@@ -3019,7 +3016,7 @@
       <c r="I62"/>
       <c r="J62"/>
       <c r="K62" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L62" t="s">
         <v>74</v>
@@ -3031,13 +3028,13 @@
         <v>8</v>
       </c>
       <c r="B63" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="C63" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="D63" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H63" s="1" t="s">
         <v>34</v>
@@ -3046,7 +3043,7 @@
         <v>35</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="64" spans="1:13" s="11" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3054,17 +3051,17 @@
         <v>9</v>
       </c>
       <c r="B64" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C64" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="D64" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>196</v>
       </c>
       <c r="E64" s="15"/>
       <c r="G64" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H64" s="11" t="s">
         <v>19</v>
@@ -3078,19 +3075,19 @@
         <v>9</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C65" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="D65" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="G65" s="1" t="s">
         <v>199</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>200</v>
       </c>
       <c r="H65" s="1" t="s">
         <v>34</v>
@@ -3099,7 +3096,7 @@
         <v>35</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="66" spans="1:13" s="1" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
@@ -3107,19 +3104,19 @@
         <v>9</v>
       </c>
       <c r="B66" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C66" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="D66" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="G66" s="1" t="s">
         <v>203</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>34</v>
@@ -3133,13 +3130,13 @@
         <v>10</v>
       </c>
       <c r="B67" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C67" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="D67" s="1" t="s">
         <v>206</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>207</v>
       </c>
       <c r="E67" s="1"/>
       <c r="F67" s="1"/>
@@ -3160,13 +3157,13 @@
         <v>10</v>
       </c>
       <c r="B68" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C68" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C68" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="D68" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H68" s="1" t="s">
         <v>34</v>
@@ -3180,13 +3177,13 @@
         <v>10</v>
       </c>
       <c r="B69" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C69" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="D69" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H69" s="1" t="s">
         <v>34</v>
@@ -3200,13 +3197,13 @@
         <v>10</v>
       </c>
       <c r="B70" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C70" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C70" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="D70" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H70" s="1" t="s">
         <v>34</v>
@@ -3220,13 +3217,13 @@
         <v>10</v>
       </c>
       <c r="B71" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C71" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="D71" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -3288,1718 +3285,1718 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" t="s">
         <v>212</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>213</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>214</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>215</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>216</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>217</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>218</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>219</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>220</v>
-      </c>
-      <c r="J1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" t="s">
         <v>222</v>
       </c>
-      <c r="B2" t="s">
-        <v>223</v>
-      </c>
       <c r="C2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H2">
         <v>104.04</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H3">
         <v>51.84</v>
       </c>
       <c r="I3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H4">
         <v>250</v>
       </c>
       <c r="I4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H6">
         <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H7">
         <v>49</v>
       </c>
       <c r="I7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G8" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H8">
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B10" t="s">
         <v>231</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>232</v>
       </c>
-      <c r="C10" t="s">
-        <v>233</v>
-      </c>
       <c r="D10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H10">
         <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>230</v>
+      </c>
+      <c r="B11" t="s">
         <v>231</v>
       </c>
-      <c r="B11" t="s">
-        <v>232</v>
-      </c>
       <c r="C11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H11">
         <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" t="s">
         <v>231</v>
       </c>
-      <c r="B12" t="s">
-        <v>232</v>
-      </c>
       <c r="C12" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H12">
         <v>21</v>
       </c>
       <c r="I12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B14" t="s">
         <v>237</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" t="s">
         <v>238</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" t="s">
         <v>239</v>
       </c>
-      <c r="D14" t="s">
-        <v>232</v>
-      </c>
-      <c r="E14" t="s">
-        <v>236</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>240</v>
-      </c>
-      <c r="G14" t="s">
-        <v>241</v>
       </c>
       <c r="H14">
         <v>100</v>
       </c>
       <c r="I14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" t="s">
         <v>237</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>238</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>231</v>
+      </c>
+      <c r="E15" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" t="s">
         <v>239</v>
       </c>
-      <c r="D15" t="s">
-        <v>232</v>
-      </c>
-      <c r="E15" t="s">
-        <v>236</v>
-      </c>
-      <c r="F15" t="s">
-        <v>240</v>
-      </c>
       <c r="G15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H15">
         <v>300</v>
       </c>
       <c r="I15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B16" t="s">
         <v>237</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>238</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
+        <v>231</v>
+      </c>
+      <c r="E16" t="s">
+        <v>235</v>
+      </c>
+      <c r="F16" t="s">
         <v>239</v>
       </c>
-      <c r="D16" t="s">
-        <v>232</v>
-      </c>
-      <c r="E16" t="s">
-        <v>236</v>
-      </c>
-      <c r="F16" t="s">
-        <v>240</v>
-      </c>
       <c r="G16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H16">
         <v>450</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" t="s">
         <v>237</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>238</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>231</v>
+      </c>
+      <c r="E17" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" t="s">
         <v>239</v>
       </c>
-      <c r="D17" t="s">
-        <v>232</v>
-      </c>
-      <c r="E17" t="s">
-        <v>236</v>
-      </c>
-      <c r="F17" t="s">
-        <v>240</v>
-      </c>
       <c r="G17" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H17">
         <v>675</v>
       </c>
       <c r="I17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" t="s">
         <v>237</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>238</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
+        <v>231</v>
+      </c>
+      <c r="E18" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" t="s">
         <v>239</v>
       </c>
-      <c r="D18" t="s">
-        <v>232</v>
-      </c>
-      <c r="E18" t="s">
-        <v>236</v>
-      </c>
-      <c r="F18" t="s">
-        <v>240</v>
-      </c>
       <c r="G18" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H18">
         <v>15</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>236</v>
+      </c>
+      <c r="B19" t="s">
         <v>237</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>238</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" t="s">
         <v>239</v>
       </c>
-      <c r="D19" t="s">
-        <v>232</v>
-      </c>
-      <c r="E19" t="s">
-        <v>236</v>
-      </c>
-      <c r="F19" t="s">
-        <v>240</v>
-      </c>
       <c r="G19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H19">
         <v>45</v>
       </c>
       <c r="I19" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B20" t="s">
         <v>237</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>238</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
+        <v>231</v>
+      </c>
+      <c r="E20" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" t="s">
         <v>239</v>
       </c>
-      <c r="D20" t="s">
-        <v>232</v>
-      </c>
-      <c r="E20" t="s">
-        <v>236</v>
-      </c>
-      <c r="F20" t="s">
-        <v>240</v>
-      </c>
       <c r="G20" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H20">
         <v>80</v>
       </c>
       <c r="I20" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J20" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" t="s">
         <v>237</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>238</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>231</v>
+      </c>
+      <c r="E22" t="s">
+        <v>234</v>
+      </c>
+      <c r="F22" t="s">
         <v>239</v>
       </c>
-      <c r="D22" t="s">
-        <v>232</v>
-      </c>
-      <c r="E22" t="s">
-        <v>235</v>
-      </c>
-      <c r="F22" t="s">
-        <v>240</v>
-      </c>
       <c r="G22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H22">
         <v>100</v>
       </c>
       <c r="I22" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>236</v>
+      </c>
+      <c r="B23" t="s">
         <v>237</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>238</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
+        <v>231</v>
+      </c>
+      <c r="E23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F23" t="s">
         <v>239</v>
       </c>
-      <c r="D23" t="s">
-        <v>232</v>
-      </c>
-      <c r="E23" t="s">
-        <v>235</v>
-      </c>
-      <c r="F23" t="s">
-        <v>240</v>
-      </c>
       <c r="G23" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H23">
         <v>300</v>
       </c>
       <c r="I23" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J23" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" t="s">
         <v>237</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>238</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>231</v>
+      </c>
+      <c r="E24" t="s">
+        <v>234</v>
+      </c>
+      <c r="F24" t="s">
         <v>239</v>
       </c>
-      <c r="D24" t="s">
-        <v>232</v>
-      </c>
-      <c r="E24" t="s">
-        <v>235</v>
-      </c>
-      <c r="F24" t="s">
-        <v>240</v>
-      </c>
       <c r="G24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H24">
         <v>450</v>
       </c>
       <c r="I24" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
+        <v>236</v>
+      </c>
+      <c r="B25" t="s">
         <v>237</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>238</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
+        <v>231</v>
+      </c>
+      <c r="E25" t="s">
+        <v>234</v>
+      </c>
+      <c r="F25" t="s">
         <v>239</v>
       </c>
-      <c r="D25" t="s">
-        <v>232</v>
-      </c>
-      <c r="E25" t="s">
-        <v>235</v>
-      </c>
-      <c r="F25" t="s">
-        <v>240</v>
-      </c>
       <c r="G25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H25">
         <v>675</v>
       </c>
       <c r="I25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J25" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
+        <v>236</v>
+      </c>
+      <c r="B26" t="s">
         <v>237</v>
       </c>
-      <c r="B26" t="s">
+      <c r="C26" t="s">
         <v>238</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E26" t="s">
+        <v>234</v>
+      </c>
+      <c r="F26" t="s">
         <v>239</v>
       </c>
-      <c r="D26" t="s">
-        <v>232</v>
-      </c>
-      <c r="E26" t="s">
-        <v>235</v>
-      </c>
-      <c r="F26" t="s">
-        <v>240</v>
-      </c>
       <c r="G26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H26">
         <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
+        <v>236</v>
+      </c>
+      <c r="B27" t="s">
         <v>237</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>238</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
+        <v>231</v>
+      </c>
+      <c r="E27" t="s">
+        <v>234</v>
+      </c>
+      <c r="F27" t="s">
         <v>239</v>
       </c>
-      <c r="D27" t="s">
-        <v>232</v>
-      </c>
-      <c r="E27" t="s">
-        <v>235</v>
-      </c>
-      <c r="F27" t="s">
-        <v>240</v>
-      </c>
       <c r="G27" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H27">
         <v>115</v>
       </c>
       <c r="I27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>236</v>
+      </c>
+      <c r="B28" t="s">
         <v>237</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>238</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>231</v>
+      </c>
+      <c r="E28" t="s">
+        <v>234</v>
+      </c>
+      <c r="F28" t="s">
         <v>239</v>
       </c>
-      <c r="D28" t="s">
-        <v>232</v>
-      </c>
-      <c r="E28" t="s">
-        <v>235</v>
-      </c>
-      <c r="F28" t="s">
-        <v>240</v>
-      </c>
       <c r="G28" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H28">
         <v>150</v>
       </c>
       <c r="I28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J28" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>236</v>
+      </c>
+      <c r="B30" t="s">
         <v>237</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>238</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
+        <v>231</v>
+      </c>
+      <c r="E30" t="s">
+        <v>232</v>
+      </c>
+      <c r="F30" t="s">
         <v>239</v>
       </c>
-      <c r="D30" t="s">
-        <v>232</v>
-      </c>
-      <c r="E30" t="s">
-        <v>233</v>
-      </c>
-      <c r="F30" t="s">
-        <v>240</v>
-      </c>
       <c r="G30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H30">
         <v>150</v>
       </c>
       <c r="I30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
+        <v>236</v>
+      </c>
+      <c r="B31" t="s">
         <v>237</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>238</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" t="s">
+        <v>232</v>
+      </c>
+      <c r="F31" t="s">
         <v>239</v>
       </c>
-      <c r="D31" t="s">
-        <v>232</v>
-      </c>
-      <c r="E31" t="s">
-        <v>233</v>
-      </c>
-      <c r="F31" t="s">
-        <v>240</v>
-      </c>
       <c r="G31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H31">
         <v>200</v>
       </c>
       <c r="I31" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>236</v>
+      </c>
+      <c r="B32" t="s">
         <v>237</v>
       </c>
-      <c r="B32" t="s">
+      <c r="C32" t="s">
         <v>238</v>
       </c>
-      <c r="C32" t="s">
+      <c r="D32" t="s">
+        <v>231</v>
+      </c>
+      <c r="E32" t="s">
+        <v>232</v>
+      </c>
+      <c r="F32" t="s">
         <v>239</v>
       </c>
-      <c r="D32" t="s">
-        <v>232</v>
-      </c>
-      <c r="E32" t="s">
-        <v>233</v>
-      </c>
-      <c r="F32" t="s">
-        <v>240</v>
-      </c>
       <c r="G32" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H32">
         <v>300</v>
       </c>
       <c r="I32" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J32" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" t="s">
         <v>237</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C33" t="s">
         <v>238</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
+        <v>231</v>
+      </c>
+      <c r="E33" t="s">
+        <v>232</v>
+      </c>
+      <c r="F33" t="s">
         <v>239</v>
       </c>
-      <c r="D33" t="s">
-        <v>232</v>
-      </c>
-      <c r="E33" t="s">
-        <v>233</v>
-      </c>
-      <c r="F33" t="s">
-        <v>240</v>
-      </c>
       <c r="G33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H33">
         <v>450</v>
       </c>
       <c r="I33" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J33" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>236</v>
+      </c>
+      <c r="B34" t="s">
         <v>237</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>238</v>
       </c>
-      <c r="C34" t="s">
+      <c r="D34" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" t="s">
+        <v>232</v>
+      </c>
+      <c r="F34" t="s">
         <v>239</v>
       </c>
-      <c r="D34" t="s">
-        <v>232</v>
-      </c>
-      <c r="E34" t="s">
-        <v>233</v>
-      </c>
-      <c r="F34" t="s">
-        <v>240</v>
-      </c>
       <c r="G34" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H34">
         <v>675</v>
       </c>
       <c r="I34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J34" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
+        <v>236</v>
+      </c>
+      <c r="B35" t="s">
         <v>237</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>238</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" t="s">
+        <v>231</v>
+      </c>
+      <c r="E35" t="s">
+        <v>232</v>
+      </c>
+      <c r="F35" t="s">
         <v>239</v>
       </c>
-      <c r="D35" t="s">
-        <v>232</v>
-      </c>
-      <c r="E35" t="s">
-        <v>233</v>
-      </c>
-      <c r="F35" t="s">
-        <v>240</v>
-      </c>
       <c r="G35" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H35">
         <v>150</v>
       </c>
       <c r="I35" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B36" t="s">
         <v>237</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>238</v>
       </c>
-      <c r="C36" t="s">
+      <c r="D36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E36" t="s">
+        <v>232</v>
+      </c>
+      <c r="F36" t="s">
         <v>239</v>
       </c>
-      <c r="D36" t="s">
-        <v>232</v>
-      </c>
-      <c r="E36" t="s">
-        <v>233</v>
-      </c>
-      <c r="F36" t="s">
-        <v>240</v>
-      </c>
       <c r="G36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H36">
         <v>225</v>
       </c>
       <c r="I36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J36" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" t="s">
         <v>237</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>238</v>
       </c>
-      <c r="C37" t="s">
+      <c r="D37" t="s">
+        <v>231</v>
+      </c>
+      <c r="E37" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" t="s">
         <v>239</v>
       </c>
-      <c r="D37" t="s">
-        <v>232</v>
-      </c>
-      <c r="E37" t="s">
-        <v>233</v>
-      </c>
-      <c r="F37" t="s">
-        <v>240</v>
-      </c>
       <c r="G37" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H37">
         <v>300</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J37" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>236</v>
+      </c>
+      <c r="B39" t="s">
         <v>237</v>
       </c>
-      <c r="B39" t="s">
-        <v>238</v>
-      </c>
       <c r="C39" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E39" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F39" t="s">
+        <v>239</v>
+      </c>
+      <c r="G39" t="s">
         <v>240</v>
-      </c>
-      <c r="G39" t="s">
-        <v>241</v>
       </c>
       <c r="H39">
         <v>150</v>
       </c>
       <c r="I39" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J39" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>236</v>
+      </c>
+      <c r="B40" t="s">
         <v>237</v>
       </c>
-      <c r="B40" t="s">
-        <v>238</v>
-      </c>
       <c r="C40" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H40">
         <v>450</v>
       </c>
       <c r="I40" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" t="s">
         <v>237</v>
       </c>
-      <c r="B41" t="s">
-        <v>238</v>
-      </c>
       <c r="C41" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D41" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E41" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G41" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H41">
         <v>675</v>
       </c>
       <c r="I41" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J41" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>236</v>
+      </c>
+      <c r="B42" t="s">
         <v>237</v>
       </c>
-      <c r="B42" t="s">
-        <v>238</v>
-      </c>
       <c r="C42" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D42" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E42" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F42" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G42" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H42">
         <v>1000</v>
       </c>
       <c r="I42" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J42" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
+        <v>236</v>
+      </c>
+      <c r="B43" t="s">
         <v>237</v>
       </c>
-      <c r="B43" t="s">
-        <v>238</v>
-      </c>
       <c r="C43" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D43" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E43" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F43" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G43" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H43">
         <v>80</v>
       </c>
       <c r="I43" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>236</v>
+      </c>
+      <c r="B44" t="s">
         <v>237</v>
       </c>
-      <c r="B44" t="s">
-        <v>238</v>
-      </c>
       <c r="C44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E44" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F44" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H44">
         <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J44" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>236</v>
+      </c>
+      <c r="B45" t="s">
         <v>237</v>
       </c>
-      <c r="B45" t="s">
-        <v>238</v>
-      </c>
       <c r="C45" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D45" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E45" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F45" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G45" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H45">
         <v>150</v>
       </c>
       <c r="I45" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B47" t="s">
         <v>237</v>
       </c>
-      <c r="B47" t="s">
-        <v>238</v>
-      </c>
       <c r="C47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D47" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E47" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F47" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G47" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H47">
         <v>150</v>
       </c>
       <c r="I47" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J47" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>236</v>
+      </c>
+      <c r="B48" t="s">
         <v>237</v>
       </c>
-      <c r="B48" t="s">
-        <v>238</v>
-      </c>
       <c r="C48" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D48" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E48" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F48" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H48">
         <v>450</v>
       </c>
       <c r="I48" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J48" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>236</v>
+      </c>
+      <c r="B49" t="s">
         <v>237</v>
       </c>
-      <c r="B49" t="s">
-        <v>238</v>
-      </c>
       <c r="C49" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E49" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F49" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H49">
         <v>675</v>
       </c>
       <c r="I49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J49" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
+        <v>236</v>
+      </c>
+      <c r="B50" t="s">
         <v>237</v>
       </c>
-      <c r="B50" t="s">
-        <v>238</v>
-      </c>
       <c r="C50" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D50" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G50" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H50">
         <v>1000</v>
       </c>
       <c r="I50" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J50" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
+        <v>236</v>
+      </c>
+      <c r="B51" t="s">
         <v>237</v>
       </c>
-      <c r="B51" t="s">
-        <v>238</v>
-      </c>
       <c r="C51" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E51" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F51" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G51" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H51">
         <v>150</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J51" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" t="s">
         <v>237</v>
       </c>
-      <c r="B52" t="s">
-        <v>238</v>
-      </c>
       <c r="C52" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D52" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E52" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F52" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G52" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H52">
         <v>225</v>
       </c>
       <c r="I52" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" t="s">
         <v>237</v>
       </c>
-      <c r="B53" t="s">
-        <v>238</v>
-      </c>
       <c r="C53" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E53" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F53" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G53" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H53">
         <v>300</v>
       </c>
       <c r="I53" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J53" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" t="s">
         <v>237</v>
       </c>
-      <c r="B55" t="s">
-        <v>238</v>
-      </c>
       <c r="C55" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D55" t="s">
+        <v>231</v>
+      </c>
+      <c r="E55" t="s">
         <v>232</v>
       </c>
-      <c r="E55" t="s">
-        <v>233</v>
-      </c>
       <c r="F55" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G55" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H55">
         <v>225</v>
       </c>
       <c r="I55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J55" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" t="s">
         <v>237</v>
       </c>
-      <c r="B56" t="s">
-        <v>238</v>
-      </c>
       <c r="C56" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D56" t="s">
+        <v>231</v>
+      </c>
+      <c r="E56" t="s">
         <v>232</v>
       </c>
-      <c r="E56" t="s">
-        <v>233</v>
-      </c>
       <c r="F56" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G56" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H56">
         <v>300</v>
       </c>
       <c r="I56" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J56" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>236</v>
+      </c>
+      <c r="B57" t="s">
         <v>237</v>
       </c>
-      <c r="B57" t="s">
-        <v>238</v>
-      </c>
       <c r="C57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D57" t="s">
+        <v>231</v>
+      </c>
+      <c r="E57" t="s">
         <v>232</v>
       </c>
-      <c r="E57" t="s">
-        <v>233</v>
-      </c>
       <c r="F57" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G57" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H57">
         <v>450</v>
       </c>
       <c r="I57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J57" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
+        <v>236</v>
+      </c>
+      <c r="B58" t="s">
         <v>237</v>
       </c>
-      <c r="B58" t="s">
-        <v>238</v>
-      </c>
       <c r="C58" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D58" t="s">
+        <v>231</v>
+      </c>
+      <c r="E58" t="s">
         <v>232</v>
       </c>
-      <c r="E58" t="s">
-        <v>233</v>
-      </c>
       <c r="F58" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G58" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H58">
         <v>675</v>
       </c>
       <c r="I58" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J58" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>236</v>
+      </c>
+      <c r="B59" t="s">
         <v>237</v>
       </c>
-      <c r="B59" t="s">
-        <v>238</v>
-      </c>
       <c r="C59" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D59" t="s">
+        <v>231</v>
+      </c>
+      <c r="E59" t="s">
         <v>232</v>
       </c>
-      <c r="E59" t="s">
-        <v>233</v>
-      </c>
       <c r="F59" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G59" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H59">
         <v>1000</v>
       </c>
       <c r="I59" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J59" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" t="s">
         <v>237</v>
       </c>
-      <c r="B60" t="s">
-        <v>238</v>
-      </c>
       <c r="C60" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D60" t="s">
+        <v>231</v>
+      </c>
+      <c r="E60" t="s">
         <v>232</v>
       </c>
-      <c r="E60" t="s">
-        <v>233</v>
-      </c>
       <c r="F60" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G60" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H60">
         <v>150</v>
       </c>
       <c r="I60" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J60" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
+        <v>236</v>
+      </c>
+      <c r="B61" t="s">
         <v>237</v>
       </c>
-      <c r="B61" t="s">
-        <v>238</v>
-      </c>
       <c r="C61" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D61" t="s">
+        <v>231</v>
+      </c>
+      <c r="E61" t="s">
         <v>232</v>
       </c>
-      <c r="E61" t="s">
-        <v>233</v>
-      </c>
       <c r="F61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G61" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H61">
         <v>225</v>
       </c>
       <c r="I61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J61" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" t="s">
         <v>237</v>
       </c>
-      <c r="B62" t="s">
-        <v>238</v>
-      </c>
       <c r="C62" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D62" t="s">
+        <v>231</v>
+      </c>
+      <c r="E62" t="s">
         <v>232</v>
       </c>
-      <c r="E62" t="s">
-        <v>233</v>
-      </c>
       <c r="F62" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G62" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H62">
         <v>300</v>
       </c>
       <c r="I62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J62" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -5025,24 +5022,24 @@
         <v>4</v>
       </c>
       <c r="C1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1" t="s">
         <v>258</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>260</v>
-      </c>
-      <c r="F1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C2">
         <v>30</v>
@@ -5056,10 +5053,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -5073,10 +5070,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C4">
         <v>90</v>
@@ -5090,10 +5087,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C5">
         <v>120</v>
@@ -5107,10 +5104,10 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C6">
         <v>180</v>
@@ -5124,10 +5121,10 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C7">
         <v>240</v>
@@ -5141,7 +5138,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C8">
         <v>30</v>
@@ -5155,7 +5152,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9">
         <v>60</v>
@@ -5169,7 +5166,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>90</v>
@@ -5183,7 +5180,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C11">
         <v>120</v>
@@ -5197,7 +5194,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12">
         <v>180</v>
@@ -5211,7 +5208,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C13">
         <v>240</v>
@@ -5225,7 +5222,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C14">
         <v>60</v>
@@ -5239,7 +5236,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C15">
         <v>90</v>
@@ -5253,7 +5250,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C16">
         <v>120</v>
@@ -5267,7 +5264,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17">
         <v>30</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C18">
         <v>60</v>
@@ -5295,7 +5292,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C19">
         <v>90</v>
@@ -5309,7 +5306,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C20">
         <v>120</v>
@@ -5327,6 +5324,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E9B12C2B262A7D41BAA1C1A05186961E" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="484d85e35f7b2f24491f05f08eca660b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9a4568ba-f362-4e84-99d7-dc60d25416b3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f826ed3232af6d38e82027660e1ae8c6" ns2:_="">
     <xsd:import namespace="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
@@ -5504,26 +5520,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9a4568ba-f362-4e84-99d7-dc60d25416b3">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F1FA26F4-5D97-47BE-ADC1-EEDEEFE4A973}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5539,22 +5554,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{58E57473-BAD3-4CDA-A67F-19CDC21767EF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9a4568ba-f362-4e84-99d7-dc60d25416b3"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8ED54FA-4DB1-4C56-A86D-28FB7FDDBA5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>